--- a/Excel/new_jobsnew.xlsx
+++ b/Excel/new_jobsnew.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1034,7 +1034,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>greenhouse|databricks|8520024002</t>
+          <t>greenhouse|stripe|7540441</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,53 +1044,53 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>databricks</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8520024002</t>
+          <t>7540441</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Insurance)</t>
+          <t>Credit Risk Analyst Commercial Underwriter, West Coast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Georgia; Illinois; Massachusetts; New York; North Carolina</t>
+          <t>Chicago, US-Remote, Canada-Remote</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8520024002</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7540441</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>FEQ327R7 While candidates in the listed location(s) are encouraged to apply for this role, exceptionally well-qualified candidates in other East Coast locations will also be considered. Mission Solutions Architects at Databricks lead the growth of the Databricks Data Intelligence Platform. As a team, we have expertise in cloud platforms, data engineering, data analytics, and data science, machine learning, and AI. As a member of our team, you will exercise and grow your expertise in those areas, using open source projects such as Apache Spark™, Delta Lake, and MLflow. This is a customer-facing role, where you will work with customers, your teammates, the product team, our post-sales team,s and partners, to identify use cases for Databricks, develop architectures and solutions using our platform, and guide customers through the implementation, to accomplish meaningful outcomes for their businesses. In this process, you will build relationships with our customers, identify and cultivate champions, and establish yourself as a trusted advisor. You will report to a Field Engineering Manager within the Financial Services team at Databricks. The impact you will have : Partner with the sales team to help customers understand how Databricks can help solve their business problems Provide technical leadership for customers to evaluate and adopt Databricks Consult on big data architecture, execute proof of concepts for strategic customer projects, and validate integrations with cloud services and other 3rd party applications Build and present reference architectures, how-tos, and demonstrate applications for customers Become an expert in, and promote open source projects (Apache Spark™, Delta Lake, MLflow, and Unity Catalog) across developer communities through meetups, conferences, and webinars Travel to meet with customers in your territory What we look for : 7+ years in a customer-facing pre-sales role, or consulting role - preferably working with big-data technologies to solve data engineering and big-data analytical challenges Experience designing and architecting distributed data systems Comfortable programming in, and debugging, at least one of: Python, SQL, Scala, Java, or R Experience working with global system integrators, consulting organizations, or financial services technology, or financial services data providers is a positive differentiator Experience building solutions with public cloud providers such as AWS, Azure, or GCP Experience with Data Engineering technologies ( Ex: Spark, Hadoop, Kafka ) Experience with Data Warehousing technologies ( Ex: SQL, OLTP/OLAP/DSS ) Undergraduate degree or higher in an engineering or mathematics discipline such as Computer Science, Applied Mathematics, Electrical Engineering, etc.) Pay Range Transparency Databricks is committed to fair and equitable compensation practices. The pay range(s) for this role is listed below and represents the expected salary range for non-commissionable roles or on-target earnings for commissionable roles. Actual compensation packages are based on several factors that are unique to each candidate, including but not limited to job-related skills, depth of experience, relevant certifications and training, and specific work location. Based on the factors above, Databricks anticipates utilizing the full width of the range. The total compensation package for this position may also include eligibility for annual performance bonus, equity, and the benefits listed above. For more information regarding which range your location is in visit our page here . Local Pay Range $180,000 — $247,500 USD About Databricks Databricks is the data and AI company. More than 10,000 organizations worldwide — including Comcast, Condé Nast, Grammarly, and over 50% of the Fortune 500 — rely on the Databricks Data Intelligence Platform to unify and democratize data, analytics and AI. Databricks is headquartered in San Francisco, with offices around the globe and was founded by the original creators of Lakehouse, Apache Spark™, Delta Lake and MLflow. To learn more, follow Databricks on Twitter , LinkedIn and Facebook . Benefits At Databricks, we strive to provide comprehensive benefits and perks that meet the needs of all of our employees. For specific details on the benefits offered in your region click here . Our Commitment to Diversity and Inclusion At Databricks, we are committed to fostering a diverse and inclusive culture where everyone can excel. We take great care to ensure that our hiring practices are inclusive and meet equal employment opportunity standards. Individuals looking for employment at Databricks are considered without regard to age, color, disability, ethnicity, family or marital status, gender identity or expression, language, national origin, physical and mental ability, political affiliation, race, religion, sexual orientation, socio-economic status, veteran status, and other protected characteristics. Compliance If access to export-controlled technology or source code is required for performance of job duties, it is within Employer's discretion whether to apply for a U.S. government license for such positions, and Employer may decline to proceed with an applicant on this basis alone.</t>
+          <t>Who we are About Stripe Stripe is a financial infrastructure platform for businesses. Millions of companies—from the world's largest enterprises to the most ambitious startups—use Stripe to accept payments, grow their revenue, and accelerate new business opportunities. Our mission is to increase the GDP of the internet, and we have a staggering amount of work ahead. That means you have an unprecedented opportunity to put the global economy within everyone's reach while doing the most important work of your career. About the team The Credit team protects Stripe by managing the end-to-end risk of our largest and most complex users. We leverage deep underwriting expertise and data-driven stress heuristics to make informed decisions at every stage of the user lifecycle—from onboarding to loss recovery. Our goal is to enable Stripe's growth by making confident, calibrated decisions on our highest-exposure users. What you’ll do Stripe handles billions of dollars every year for businesses around the world, and the Risk team plays a critical role in the company's financial and partnership success. As a Credit Risk Analyst Commercial Underwriter on the North America Strategy Risk team, you'll underwrite and manage a portfolio of our largest and fastest-growing businesses to facilitate growth objectives while minimizing credit risk. This is a high-impact role that involves strong cross-functional partnership with Sales, Legal, Treasury, and Finance. This role is assigned to West Coast hours, with a high preference for candidates in the Pacific time zone. Responsibilities Work directly with our top merchants, from successful venture-backed startups to well-established institutions, to evaluate their business models and financial statements Provide tailored credit risk recommendations that mitigate Stripe exposure, while facilitating partner company growth Help manage the portfolio by developing a deep understanding of risk across industries, geographies, and operating models Deliver insights to support senior management decisions, ranging from onboarding strategies to merchant pricing analysis Support the refinement of tools and processes to help the team deliver on key performance indicators, such as credit loss targets or portfolio coverage metrics Work with internal and external partners to support merchants around the world Who you are We're looking for someone who meets the minimum requirements to be considered for the role. If you meet these requirements, you are encouraged to apply. The preferred qualifications are a bonus, not a requirement. Minimum requirements 5+ years of relevant experience with knowledge of commercial credit underwriting, financial risk modeling, and cash flow forecasting Bachelor's degree in Finance, Economics, Statistics, or other related fields Strong knowledge of accounting principles and comfort evaluating financial statements and business models across a range of industries Ability to transform business and financial data into cohesive narratives that outline potential credit risks and present dynamic mitigation strategies Strong written, verbal, and problem-solving skills Attention to detail while managing priorities in a fast-paced environment Ability to comfortably interact with the CFOs and CEOs of our top merchants Deep empathy for entrepreneurs running a business, and motivation to solve problems to empower them Preferred qualifications Strong technical expertise, including demonstrated experience with SQL Strong data visualization skills and a passion for data and analysis Experience working in tech, or other fast-paced, high-growth environments</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>greenhouse|databricks|8570023002</t>
+          <t>greenhouse|stripe|7612192</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1100,53 +1100,53 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>databricks</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8570023002</t>
+          <t>7612192</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
+          <t>Credit Risk Analyst, North American Underwriter</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t xml:space="preserve">Toronto, Remote-Canada </t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8570023002</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7612192</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>FEQ327R455 - DNB FEQ327R257 - Emerging FEQ327R204 - FinS As a Specialist Solutions Architect (SSA) - Data Engineering and Warehousing , you will guide customers through cloud data engineering transformations across a wide variety of use cases. In this customer-facing role, you will collaborate with and support Solutions Architects. This requires hands-on production experience with large-scale data engineering technologies and lakehouse architecture. The SSA teams help customers navigate evaluations and successfully plan production for their business intelligence workloads while aligning their technical roadmap with the Databricks Data Intelligence Platform. As a deep go-to expert reporting to the Specialist Field Engineering Manager, you will continue to strengthen your technical skills through mentorship, continuous learning, and internal training programs. In this role, you will establish yourself as a leader in the data engineering and warehousing specialty. The impact you will have: Provide technical leadership to guide strategic customers to successful implementations on big data projects and large-scale data warehousing workloads. Prove the value of the Databricks Intelligence Platform for customer workloads by architecting production workloads, including end-to-end pipeline load performance testing and optimization. Architect production-level data pipelines, including end-to-end pipeline load performance testing and optimization. Become a technical expert in an area such as data lake technology, big data streaming, or big data ingestion and workflows. Assist Solution Architects with more advanced aspects of the technical sale, including custom proof of concept content, estimating workload sizing, and custom architectures. Provide tutorials and training to improve community adoption (including hackathons and conference presentations). Contribute to the Databricks Community. What we look for: 5+ years of experience in a technical role with deep expertise across the following areas: Software / Data Engineering: Hands-on experience with data ingestion, streaming technologies (e.g., Spark Streaming, Kafka), performance tuning, troubleshooting, and debugging Spark or other big data solutions. Data Applications Engineering: Experience building data-driven use cases, such as risk modeling, fraud detection, and customer lifetime value (LTV). Data Warehousing: Advanced query tuning, troubleshooting, data governance, and debugging MPP data warehouses or big data solutions. Experience migrating workloads from EDW systems (e.g., traditional SQL, Redshift, Snowflake, Synapse, EMR) across OLAP &amp; OLTP workloads. Data Observability: Experience with SIEM tools (e.g., Splunk, Elastic, Sentinel), telemetry/high-velocity log ingestion, and anomaly detection. Proven track record of maintaining, scaling, and extending production data systems to evolve with complex business needs. Deep expertise across multiple core data engineering domains, including: Designing and scaling cost-efficient, high-performance data workloads (ETL/ELT, analytics) in cloud environments. Building and migrating large-scale data pipelines, including batch, CDC (Change Data Capture), and streaming ingestion. Migrating on-premises or Hadoop-based data systems to modern cloud platforms (AWS, Azure, GCP). Developing and managing modern lakehouse and warehouse systems, including Delta Lake technologies, data modeling, governance, and BI integration. Production programming experience in SQL and at least one of the following: Python, Scala, or Java. Strong familiarity with cloud infrastructure providers (AWS, Azure, or GCP) is highly desirable. Degree or Equivalent: Bachelor's degree in Computer Science, Information Systems, Engineering, or equivalent professional experience. [Preferred] Prior customer-facing experience in a pre-sales or post-sales technical role. Ability to meet expectations for technical training and role-specific milestones within 6 months of hire. Willingness to travel up to 30% as needed. Pay Range Transparency Databricks is committed to fair and equitable compensation practices. The pay range(s) for this role is listed below and represents the expected salary range for non-commissionable roles or on-target earnings for commissionable roles. Actual compensation packages are based on several factors that are unique to each candidate, including but not limited to job-related skills, depth of experience, relevant certifications and training, and specific work location. Based on the factors above, Databricks anticipates utilizing the full width of the range. The total compensation package for this position may also include eligibility for annual performance bonus, equity, and the benefits listed above. For more information regarding which range your location is in visit our page here . Local Pay Range $180,000 — $247,500 USD About Databricks Databricks is the data and AI company. More than 10,000 organizations worldwide — including Comcast, Condé Nast, Grammarly, and over 50% of the Fortune 500 — rely on the Databricks Data Intelligence Platform to unify and democratize data, analytics and AI. Databricks is headquartered in San Francisco, with offices around the globe and was founded by the original creators of Lakehouse, Apache Spark™, Delta Lake and MLflow. To learn more, follow Databricks on Twitter , LinkedIn and Facebook . Benefits At Databricks, we strive to provide comprehensive benefits and perks that meet the needs of all of our employees. For specific details on the benefits offered in your region click here . Our Commitment to Diversity and Inclusion At Databricks, we are committed to fostering a diverse and inclusive culture where everyone can excel. We take great care to ensure that our hiring practices are inclusive and meet equal employment opportunity standards. Individuals looking for employment at Databricks are considered without regard to age, color, disability, ethnicity, family or marital status, gender identity or expression, language, national origin, physical and mental ability, political affiliation, race, religion, sexual orientation, socio-economic status, veteran status, and other protected characteristics. Compliance If access to export-controlled technology or source code is required for performance of job duties, it is within Employer's discretion whether to apply for a U.S. government license for such positions, and Employer may decline to proceed with an applicant on this basis alone.</t>
+          <t>Who we are About Stripe Stripe is a financial infrastructure platform for businesses. Millions of companies—from the world's largest enterprises to the most ambitious startups—use Stripe to accept payments, grow their revenue, and accelerate new business opportunities. Our mission is to increase the GDP of the internet, and we have a staggering amount of work ahead. That means you have an unprecedented opportunity to put the global economy within everyone's reach while doing the most important work of your career. About the team The Credit team protects Stripe by managing the end-to-end risk of our largest and most complex users. We leverage deep underwriting expertise and data-driven stress heuristics to make informed decisions at every stage of the user lifecycle—from onboarding to loss recovery. Our goal is to enable Stripe’s growth by making confident, calibrated decisions on our highest-exposure users. What you’ll do Stripe handles billions of dollars every year for businesses around the world, and the Risk team plays a critical role in the company’s financial and partnership success. As a Credit Analyst Underwriter on the North America Strategy Risk team, you will underwrite and manage a portfolio of our largest and fastest growing businesses in order to facilitate Stripe’s growth objectives while minimizing Stripe’s credit risk. This is a high impact role that involves strong cross-functional partnership with Sales, Legal, Treasury, and Finance. Responsibilities Work directly with our top merchants, from successful venture-backed startups to well-established institutions, to evaluate their business models and financial statements. Provide tailored credit risk recommendations that mitigate Stripe's exposure, while facilitating partner company growth. Help manage the portfolio by developing a deep understanding of risk across industries, geographies, and operating models. Deliver insights to support senior management decisions, ranging from onboarding strategies to merchant pricing analysis. Support the refinement of tools and processes to help the team deliver on key performance indicators, such as credit loss targets or portfolio coverage metrics. Work with internal and external partners to support merchants around the world. Who you are We're looking for someone who meets the minimum requirements to be considered for the role. If you meet these requirements, you are encouraged to apply. The preferred qualifications are a bonus, not a requirement. Minimum requirements 3+ years of relevant experience with knowledge of commercial credit underwriting, financial risk modeling, and cash flow forecasting Bachelor's degree in Finance, Economics, Statistics, or other related fields Strong knowledge of accounting principles and comfort evaluating financial statements and business models across a range of industries Ability to transform business and financial data into cohesive narratives that outline potential credit risks and present dynamic mitigation strategies Strong written, verbal, and analytical skills Attention to detail while managing priorities in a fast-paced environment Ability to comfortably interact with the CFOs and CEOs of our top merchants Deep empathy for entrepreneurs running a business and motivation to solve problems to empower them Preferred qualifications Strong technical expertise, including demonstrated experience with SQL Strong data visualization skills and a passion for data and analysis Experience working in tech or other fast-paced, high-growth environments</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>greenhouse|databricks|8568122002</t>
+          <t>greenhouse|stripe|8044686</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1156,53 +1156,53 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>databricks</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8568122002</t>
+          <t>8044686</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
+          <t>Credit Risk Strategy and Analytics</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t xml:space="preserve">Remote </t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8568122002</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8044686</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>FEQ327R204 As a Sr. Specialist Solutions Architect (SSA) - Data Engineering and Warehousing , you will guide customers through cloud data engineering transformations across a wide variety of use cases. In this customer-facing role, you will collaborate with and support Solutions Architects. This requires hands-on production experience with large-scale data engineering technologies and lakehouse architecture. The SSA teams help customers navigate evaluations and successfully plan production for their business intelligence workloads while aligning their technical roadmap with the Databricks Data Intelligence Platform. As a deep go-to expert reporting to the Specialist Field Engineering Manager, you will continue to strengthen your technical skills through mentorship, continuous learning, and internal training programs. In this role, you will establish yourself as a leader in the data engineering and warehousing specialty. The impact you will have: Provide technical leadership to guide strategic customers to successful implementations on big data projects and large-scale data warehousing workloads. Prove the value of the Databricks Intelligence Platform for customer workloads by architecting production workloads, including end-to-end pipeline load performance testing and optimization. Architect production-level data pipelines, including end-to-end pipeline load performance testing and optimization. Become a technical expert in an area such as data lake technology, big data streaming, or big data ingestion and workflows. Assist Solution Architects with more advanced aspects of the technical sale, including custom proof of concept content, estimating workload sizing, and custom architectures. Provide tutorials and training to improve community adoption (including hackathons and conference presentations). Contribute to the Databricks Community. What we look for: 8+ years of experience in a technical role with deep expertise across the following areas: Software / Data Engineering: Hands-on experience with data ingestion, streaming technologies (e.g., Spark Streaming, Kafka), performance tuning, troubleshooting, and debugging Spark or other big data solutions. Data Applications Engineering: Experience building data-driven use cases, such as risk modeling, fraud detection, and customer lifetime value (LTV). Data Warehousing: Advanced query tuning, troubleshooting, data governance, and debugging MPP data warehouses or big data solutions. Experience migrating workloads from EDW systems (e.g., traditional SQL, Redshift, Snowflake, Synapse, EMR) across OLAP &amp; OLTP workloads. Data Observability: Experience with SIEM tools (e.g., Splunk, Elastic, Sentinel), telemetry/high-velocity log ingestion, and anomaly detection. Proven track record of maintaining, scaling, and extending production data systems to evolve with complex business needs. Deep expertise across multiple core data engineering domains, including: Designing and scaling cost-efficient, high-performance data workloads (ETL/ELT, analytics) in cloud environments. Building and migrating large-scale data pipelines, including batch, CDC (Change Data Capture), and streaming ingestion. Migrating on-premises or Hadoop-based data systems to modern cloud platforms (AWS, Azure, GCP). Developing and managing modern lakehouse and warehouse systems, including Delta Lake technologies, data modeling, governance, and BI integration. Production programming experience in SQL and at least one of the following: Python, Scala, or Java. Strong familiarity with cloud infrastructure providers (AWS, Azure, or GCP) is highly desirable. Degree or Equivalent: Bachelor's degree in Computer Science, Information Systems, Engineering, or equivalent professional experience. 3+ years of customer-facing experience in a pre-sales or post-sales technical role. Ability to meet expectations for technical training and role-specific milestones within 6 months of hire. Willingness to travel up to 30% as needed. Pay Range Transparency Databricks is committed to fair and equitable compensation practices. The pay range(s) for this role is listed below and represents the expected salary range for non-commissionable roles or on-target earnings for commissionable roles. Actual compensation packages are based on several factors that are unique to each candidate, including but not limited to job-related skills, depth of experience, relevant certifications and training, and specific work location. Based on the factors above, Databricks anticipates utilizing the full width of the range. The total compensation package for this position may also include eligibility for annual performance bonus, equity, and the benefits listed above. For more information regarding which range your location is in visit our page here . Local Pay Range $219,100 — $301,300 USD About Databricks Databricks is the data and AI company. More than 10,000 organizations worldwide — including Comcast, Condé Nast, Grammarly, and over 50% of the Fortune 500 — rely on the Databricks Data Intelligence Platform to unify and democratize data, analytics and AI. Databricks is headquartered in San Francisco, with offices around the globe and was founded by the original creators of Lakehouse, Apache Spark™, Delta Lake and MLflow. To learn more, follow Databricks on Twitter , LinkedIn and Facebook . Benefits At Databricks, we strive to provide comprehensive benefits and perks that meet the needs of all of our employees. For specific details on the benefits offered in your region click here . Our Commitment to Diversity and Inclusion At Databricks, we are committed to fostering a diverse and inclusive culture where everyone can excel. We take great care to ensure that our hiring practices are inclusive and meet equal employment opportunity standards. Individuals looking for employment at Databricks are considered without regard to age, color, disability, ethnicity, family or marital status, gender identity or expression, language, national origin, physical and mental ability, political affiliation, race, religion, sexual orientation, socio-economic status, veteran status, and other protected characteristics. Compliance If access to export-controlled technology or source code is required for performance of job duties, it is within Employer's discretion whether to apply for a U.S. government license for such positions, and Employer may decline to proceed with an applicant on this basis alone.</t>
+          <t>Who we are About Stripe Stripe is a financial infrastructure platform for businesses. Millions of companies—from the world’s largest enterprises to the most ambitious startups—use Stripe to accept payments, grow their revenue, and accelerate new business opportunities. Our mission is to increase the GDP of the internet, and we have a staggering amount of work ahead. That means you have an unprecedented opportunity to put the global economy within everyone’s reach while doing the most important work of your career. About the team The Capital team is responsible for managing the end-to-end risk strategy for Stripe's lending product. The team is based in the US and Canada, and is composed of curious, driven, and analytical individuals who are passionate about using their skills to shape the future of Stripe. We partner closely with Stripe's engineering, data science, product, and servicing teams to leverage existing platforms, integrate industry best practices, and develop novel solutions to evaluate and manage credit risk. If you are interested in joining a fast-growing organization and applying your experience to shape the future of Stripe, we encourage you to apply. What you’ll do As a key member of the Capital team, you will have the opportunity to shape the future of Stripe's credit policy by driving meaningful changes to the risk and underwriting framework. You will leverage Stripe's vast data assets to formulate your recommendations and work closely with our partners and, where applicable, leverage third-party data. We are a small and lean team, which means you will have the autonomy and the responsibility to manage end-to-end risk initiatives. Responsibilities Architect and implement credit policies based on Stripe's proprietary data and selected industry data to target, price, and size capital products. Utilize your analytical and technical skills to provide credit risk recommendations, deliver insights, and support strategic business decisions. Collaborate with cross-functional teams, such as Product, Data Science, Engineering, and Capital Markets to shape new product development across different geographies and industries. Incorporate third-party data, including bureau, bank account, financial statements, and less traditional data, into our credit assessment. Analyze account activity and monitor portfolio trends to identify opportunities for Stripe to reduce potential credit losses. Help scale risk processes by working with partners to design and optimize outsourced workflows. Who you are We’re looking for someone who meets the minimum requirements to be considered for the role. If you meet these requirements, you are encouraged to apply. The preferred qualifications are a bonus, not a requirement. Minimum requirements 5+ years of experience in credit analysis and underwriting. Bachelor's degree in finance, economics, statistics, or a related field. Experience in risk management, financial lending, or core credit risk management function. Strong analytical skills and a rigorous, data-driven approach to problem-solving. Experience working with both internal and external stakeholders and the ability to closely. manage expectations and deliverables in a timely manner. Ability to thrive in an unstructured and fast-moving organization. Strong technical expertise, including SQL, excel, google sheets. Self-starter who can work independently. Preferred qualifications Experience with quantitative tools such as Python, R, or Stata. Master's degree in finance, economics, statistics, or a related field. Superior communication and relationship management skills. Experience with credit scoring models. Experience working with machine learning teams. Ability to communicate results clearly with a focus on driving impact.</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>greenhouse|stripe|7540441</t>
+          <t>greenhouse|stripe|7739207</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1222,17 +1222,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7540441</t>
+          <t>7739207</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Credit Risk Analyst Commercial Underwriter, West Coast</t>
+          <t>Sales Compensation Analytics &amp; Systems Specialist</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chicago, US-Remote, Canada-Remote</t>
+          <t>CHI, SF, NYC, SEA, US Remote</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7540441</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7739207</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Who we are About Stripe Stripe is a financial infrastructure platform for businesses. Millions of companies—from the world's largest enterprises to the most ambitious startups—use Stripe to accept payments, grow their revenue, and accelerate new business opportunities. Our mission is to increase the GDP of the internet, and we have a staggering amount of work ahead. That means you have an unprecedented opportunity to put the global economy within everyone's reach while doing the most important work of your career. About the team The Credit team protects Stripe by managing the end-to-end risk of our largest and most complex users. We leverage deep underwriting expertise and data-driven stress heuristics to make informed decisions at every stage of the user lifecycle—from onboarding to loss recovery. Our goal is to enable Stripe's growth by making confident, calibrated decisions on our highest-exposure users. What you’ll do Stripe handles billions of dollars every year for businesses around the world, and the Risk team plays a critical role in the company's financial and partnership success. As a Credit Risk Analyst Commercial Underwriter on the North America Strategy Risk team, you'll underwrite and manage a portfolio of our largest and fastest-growing businesses to facilitate growth objectives while minimizing credit risk. This is a high-impact role that involves strong cross-functional partnership with Sales, Legal, Treasury, and Finance. This role is assigned to West Coast hours, with a high preference for candidates in the Pacific time zone. Responsibilities Work directly with our top merchants, from successful venture-backed startups to well-established institutions, to evaluate their business models and financial statements Provide tailored credit risk recommendations that mitigate Stripe exposure, while facilitating partner company growth Help manage the portfolio by developing a deep understanding of risk across industries, geographies, and operating models Deliver insights to support senior management decisions, ranging from onboarding strategies to merchant pricing analysis Support the refinement of tools and processes to help the team deliver on key performance indicators, such as credit loss targets or portfolio coverage metrics Work with internal and external partners to support merchants around the world Who you are We're looking for someone who meets the minimum requirements to be considered for the role. If you meet these requirements, you are encouraged to apply. The preferred qualifications are a bonus, not a requirement. Minimum requirements 5+ years of relevant experience with knowledge of commercial credit underwriting, financial risk modeling, and cash flow forecasting Bachelor's degree in Finance, Economics, Statistics, or other related fields Strong knowledge of accounting principles and comfort evaluating financial statements and business models across a range of industries Ability to transform business and financial data into cohesive narratives that outline potential credit risks and present dynamic mitigation strategies Strong written, verbal, and problem-solving skills Attention to detail while managing priorities in a fast-paced environment Ability to comfortably interact with the CFOs and CEOs of our top merchants Deep empathy for entrepreneurs running a business, and motivation to solve problems to empower them Preferred qualifications Strong technical expertise, including demonstrated experience with SQL Strong data visualization skills and a passion for data and analysis Experience working in tech, or other fast-paced, high-growth environments</t>
+          <t>Who we are About Stripe Stripe is a financial infrastructure platform for businesses. Millions of companies—from the world's largest enterprises to the most ambitious startups—use Stripe to accept payments, grow their revenue, and accelerate new business opportunities. Our mission is to increase the GDP of the internet, and we have a staggering amount of work ahead. That means you have an unprecedented opportunity to put the global economy within everyone's reach while doing the most important work of your career. About the team The Sales Compensation team at Stripe is responsible for the overall compensation strategy, design, and payment administration for the global sales organization. We ensure that Stripe's objectives align with the compensation program and that our sales teams are paid accurately and on time. We provide thought leadership for the go-to-market initiatives so that performance and compensation are effectively correlated. The Sales Compensation team partners closely with the revenue-generating and support functions across Stripe to support the success of our go-to-market efforts. What you'll do In this role, you'll digest critical data sets of our sales performance and correlation to variable compensation. The objective is to provide advanced analytics that translate raw trends into a compelling business narrative, synthesizing the strategic implications, quantifying the business impact, and prescribing actionable next steps to shape compensation strategies for our fast-growing sales force. As Stripe's sales teams and commercial strategy grow in size and complexity, this information is required to ensure we have industry-leading compensation mechanisms to motivate and reward our world-class sales organization. An equally important component of your role is supporting the enhancement and use of our Incentive Compensation Management (ICM) tool. You'll work closely with our experienced product expert to ensure we use our ICM to its maximum capacity for compensation calculations and reporting. You'll be equally passionate about data analytics and excel as a program management partner for a compensation system. You'll need experience working with significant autonomy to design an analytics framework for compensation performance measurement, as well as part of a team to support compensation calculations. You bring proven leverage of analytics and quantitative data to calculate and validate compensation. You also bring resilience and the ability to both partner and lead in cross-functional situations. This role is based out of Stripe's South San Francisco, Chicago, or New York City offices. Responsibilities • Monthly measurement of sales force quota attainment at varying degrees of granularity • Monthly forecasting of compensation to target based on monthly quota attainment analysis • Conduct deep-dive analysis to uncover the root causes of disconnects between the performance and compensation correlation. Provide the context on why it is happening and propose specific solutions to align performance with compensation • Provide reporting, with analysis and recommendations, monthly and quarterly to senior business leadership • Support system administration for the quarterly compensation cycle • Ensure the accurate and timely compensation each quarter to the entire sales force through the ICM • Build and maintain reporting dashboards for use at the individual, management, and executive levels Who you are We're looking for someone who meets the minimum requirements to be considered for the role. If you meet these requirements, you are encouraged to apply. The preferred qualifications are a bonus, not a requirement. Minimum requirements • 4+ years of experience in a Sales Compensation or Sales Operations role • BS or BA in Business, Data Science, Economics, Finance, Math, or Statistics • Experience using a commercial Incentive Compensation Management tool (e.g. Callidus, Captivate IQ, Varicent, Xactly) • Demonstrated data analytics expertise with proven results of optimizing sales results • Strong logic, problem-solving, and spreadsheet modeling skills Preferred qualifications • MBA or applicable master's degree (e.g. Finance, Data Science, etc.) • Sales compensation design experience</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1258,7 +1258,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>greenhouse|stripe|7612192</t>
+          <t>greenhouse|stripe|7826761</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1278,17 +1278,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7612192</t>
+          <t>7826761</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Credit Risk Analyst, North American Underwriter</t>
+          <t>Software Engineer, Security Analytics Infrastructure</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toronto, Remote-Canada </t>
+          <t>US - Remote</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1299,12 +1299,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7612192</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7826761</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Who we are About Stripe Stripe is a financial infrastructure platform for businesses. Millions of companies—from the world's largest enterprises to the most ambitious startups—use Stripe to accept payments, grow their revenue, and accelerate new business opportunities. Our mission is to increase the GDP of the internet, and we have a staggering amount of work ahead. That means you have an unprecedented opportunity to put the global economy within everyone's reach while doing the most important work of your career. About the team The Credit team protects Stripe by managing the end-to-end risk of our largest and most complex users. We leverage deep underwriting expertise and data-driven stress heuristics to make informed decisions at every stage of the user lifecycle—from onboarding to loss recovery. Our goal is to enable Stripe’s growth by making confident, calibrated decisions on our highest-exposure users. What you’ll do Stripe handles billions of dollars every year for businesses around the world, and the Risk team plays a critical role in the company’s financial and partnership success. As a Credit Analyst Underwriter on the North America Strategy Risk team, you will underwrite and manage a portfolio of our largest and fastest growing businesses in order to facilitate Stripe’s growth objectives while minimizing Stripe’s credit risk. This is a high impact role that involves strong cross-functional partnership with Sales, Legal, Treasury, and Finance. Responsibilities Work directly with our top merchants, from successful venture-backed startups to well-established institutions, to evaluate their business models and financial statements. Provide tailored credit risk recommendations that mitigate Stripe's exposure, while facilitating partner company growth. Help manage the portfolio by developing a deep understanding of risk across industries, geographies, and operating models. Deliver insights to support senior management decisions, ranging from onboarding strategies to merchant pricing analysis. Support the refinement of tools and processes to help the team deliver on key performance indicators, such as credit loss targets or portfolio coverage metrics. Work with internal and external partners to support merchants around the world. Who you are We're looking for someone who meets the minimum requirements to be considered for the role. If you meet these requirements, you are encouraged to apply. The preferred qualifications are a bonus, not a requirement. Minimum requirements 3+ years of relevant experience with knowledge of commercial credit underwriting, financial risk modeling, and cash flow forecasting Bachelor's degree in Finance, Economics, Statistics, or other related fields Strong knowledge of accounting principles and comfort evaluating financial statements and business models across a range of industries Ability to transform business and financial data into cohesive narratives that outline potential credit risks and present dynamic mitigation strategies Strong written, verbal, and analytical skills Attention to detail while managing priorities in a fast-paced environment Ability to comfortably interact with the CFOs and CEOs of our top merchants Deep empathy for entrepreneurs running a business and motivation to solve problems to empower them Preferred qualifications Strong technical expertise, including demonstrated experience with SQL Strong data visualization skills and a passion for data and analysis Experience working in tech or other fast-paced, high-growth environments</t>
+          <t>Who we are About Stripe Stripe is a financial infrastructure platform for businesses. Millions of companies—from the world's largest enterprises to the most ambitious startups—use Stripe to accept payments, grow their revenue, and accelerate new business opportunities. Our mission is to increase the GDP of the internet, and we have a staggering amount of work ahead. That means you have an unprecedented opportunity to put the global economy within everyone's reach while doing the most important work of your career. About the team In this role, you'd join Stripe's Security Analytics Infrastructure team. Our mission is to enable Stripe's detection and response by generating, centralizing, and organizing security data through simple, reliable pipelines and providing a platform of core security systems. We also undertake experimental, bespoke projects that close Stripe‑specific security gaps and accelerate outcomes for our partner teams. What you'll do As a Software Engineer on this team, you'll use your blend of security and software engineering expertise to build and support our key services including a SIEM, SOAR, endpoint detection and response, server observability, threat intel platform, and AI infrastructure. You'll work closely with partner teams working in multiple program areas of cyber defense, including cyber intelligence, threat detection, vulnerability management, secure devices, and compliance. Overall, you'll help ensure that we have the right data in the right place at the right time for our users. Responsibilities • Build and maintain services and dataflows related to our security analytics platform • Collaborate with other teams to drive improvements to processes our platform supports • Continuously improve our security posture, processes, and tools Who you are We're looking for someone who meets the minimum requirements to be considered for the role. If you meet these requirements, you are encouraged to apply. The preferred qualifications are a bonus, not a requirement. Minimum requirements • 5+ years software engineering experience in a high-stakes production environment • Significant experience in applying software engineering in the cybersecurity field • Experience in applying AI tooling in this space (e.g. Claude Code, agent-based approaches, etc.) • Empathy, strong communication skills, and a deep respect for the power of collaboration • Excellent problem-solving skills and attention to detail • High standards for code quality and a constructive attitude to help others raise the bar Preferred qualifications • Go and Python experience • An ability to think creatively and holistically about reducing risk in a complex environment • Previous experience in a regulated industry (e.g., financial services, healthcare)</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1314,37 +1314,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>greenhouse|stripe|8044686</t>
+          <t>workday|allstate|/job/remote---remote/data-scientist-associate-manager---remote_r31115-1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Allstate</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>stripe</t>
+          <t>allstate/wd5/allstate_careers</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8044686</t>
+          <t>/job/Remote---Remote/Data-Scientist-Associate-Manager---Remote_R31115-1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Credit Risk Strategy and Analytics</t>
+          <t>Data Scientist Associate Manager - Remote</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote </t>
+          <t>Remote - Remote</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1355,238 +1355,214 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8044686</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Who we are About Stripe Stripe is a financial infrastructure platform for businesses. Millions of companies—from the world’s largest enterprises to the most ambitious startups—use Stripe to accept payments, grow their revenue, and accelerate new business opportunities. Our mission is to increase the GDP of the internet, and we have a staggering amount of work ahead. That means you have an unprecedented opportunity to put the global economy within everyone’s reach while doing the most important work of your career. About the team The Capital team is responsible for managing the end-to-end risk strategy for Stripe's lending product. The team is based in the US and Canada, and is composed of curious, driven, and analytical individuals who are passionate about using their skills to shape the future of Stripe. We partner closely with Stripe's engineering, data science, product, and servicing teams to leverage existing platforms, integrate industry best practices, and develop novel solutions to evaluate and manage credit risk. If you are interested in joining a fast-growing organization and applying your experience to shape the future of Stripe, we encourage you to apply. What you’ll do As a key member of the Capital team, you will have the opportunity to shape the future of Stripe's credit policy by driving meaningful changes to the risk and underwriting framework. You will leverage Stripe's vast data assets to formulate your recommendations and work closely with our partners and, where applicable, leverage third-party data. We are a small and lean team, which means you will have the autonomy and the responsibility to manage end-to-end risk initiatives. Responsibilities Architect and implement credit policies based on Stripe's proprietary data and selected industry data to target, price, and size capital products. Utilize your analytical and technical skills to provide credit risk recommendations, deliver insights, and support strategic business decisions. Collaborate with cross-functional teams, such as Product, Data Science, Engineering, and Capital Markets to shape new product development across different geographies and industries. Incorporate third-party data, including bureau, bank account, financial statements, and less traditional data, into our credit assessment. Analyze account activity and monitor portfolio trends to identify opportunities for Stripe to reduce potential credit losses. Help scale risk processes by working with partners to design and optimize outsourced workflows. Who you are We’re looking for someone who meets the minimum requirements to be considered for the role. If you meet these requirements, you are encouraged to apply. The preferred qualifications are a bonus, not a requirement. Minimum requirements 5+ years of experience in credit analysis and underwriting. Bachelor's degree in finance, economics, statistics, or a related field. Experience in risk management, financial lending, or core credit risk management function. Strong analytical skills and a rigorous, data-driven approach to problem-solving. Experience working with both internal and external stakeholders and the ability to closely. manage expectations and deliverables in a timely manner. Ability to thrive in an unstructured and fast-moving organization. Strong technical expertise, including SQL, excel, google sheets. Self-starter who can work independently. Preferred qualifications Experience with quantitative tools such as Python, R, or Stata. Master's degree in finance, economics, statistics, or a related field. Superior communication and relationship management skills. Experience with credit scoring models. Experience working with machine learning teams. Ability to communicate results clearly with a focus on driving impact.</t>
-        </is>
-      </c>
+          <t>https://allstate.wd5.myworkdayjobs.com/en-US/allstate_careers/job/Remote---Remote/Data-Scientist-Associate-Manager---Remote_R31115-1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>greenhouse|stripe|8052468</t>
+          <t>workday|allstate|/job/remote---remote/business-intelligence-and-data-analytics-consultant-ii---remote_r32407</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Allstate</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>stripe</t>
+          <t>allstate/wd5/allstate_careers</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8052468</t>
+          <t>/job/Remote---Remote/Business-Intelligence-and-Data-Analytics-Consultant-II---Remote_R32407</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Credit Risk Strategy and Analytics</t>
+          <t>Business Intelligence and Data Analytics Consultant II - Remote</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">United States </t>
+          <t>Remote - Remote</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8052468</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Who we are About Stripe Stripe is a financial infrastructure platform for businesses. Millions of companies—from the world’s largest enterprises to the most ambitious startups—use Stripe to accept payments, grow their revenue, and accelerate new business opportunities. Our mission is to increase the GDP of the internet, and we have a staggering amount of work ahead. That means you have an unprecedented opportunity to put the global economy within everyone’s reach while doing the most important work of your career. About the team The Capital team is responsible for managing the end-to-end risk strategy for Stripe's lending product. The team is based in the US and Canada, and is composed of curious, driven, and analytical individuals who are passionate about using their skills to shape the future of Stripe. We partner closely with Stripe's engineering, data science, product, and servicing teams to leverage existing platforms, integrate industry best practices, and develop novel solutions to evaluate and manage credit risk. If you are interested in joining a fast-growing organization and applying your experience to shape the future of Stripe, we encourage you to apply. What you’ll do As a key member of the Capital team, you will have the opportunity to shape the future of Stripe's credit policy by driving meaningful changes to the risk and underwriting framework. You will leverage Stripe's vast data assets to formulate your recommendations and work closely with our partners and, where applicable, leverage third-party data. We are a small and lean team, which means you will have the autonomy and the responsibility to manage end-to-end risk initiatives. Responsibilities Architect and implement credit policies based on Stripe's proprietary data and selected industry data to target, price, and size capital products. Utilize your analytical and technical skills to provide credit risk recommendations, deliver insights, and support strategic business decisions. Collaborate with cross-functional teams, such as Product, Data Science, Engineering, and Capital Markets to shape new product development across different geographies and industries. Incorporate third-party data, including bureau, bank account, financial statements, and less traditional data, into our credit assessment. Analyze account activity and monitor portfolio trends to identify opportunities for Stripe to reduce potential credit losses. Help scale risk processes by working with partners to design and optimize outsourced workflows. Who you are We’re looking for someone who meets the minimum requirements to be considered for the role. If you meet these requirements, you are encouraged to apply. The preferred qualifications are a bonus, not a requirement. Minimum requirements 5+ years of experience in credit analysis and underwriting. Bachelor's degree in finance, economics, statistics, or a related field. Experience in risk management, financial lending, or core credit risk management function. Strong analytical skills and a rigorous, data-driven approach to problem-solving. Experience working with both internal and external stakeholders and the ability to closely. manage expectations and deliverables in a timely manner. Ability to thrive in an unstructured and fast-moving organization. Strong technical expertise, including SQL, excel, google sheets. Self-starter who can work independently. Preferred qualifications Experience with quantitative tools such as Python, R, or Stata. Master's degree in finance, economics, statistics, or a related field. Superior communication and relationship management skills. Experience with credit scoring models. Experience working with machine learning teams. Ability to communicate results clearly with a focus on driving impact.</t>
-        </is>
-      </c>
+          <t>https://allstate.wd5.myworkdayjobs.com/en-US/allstate_careers/job/Remote---Remote/Business-Intelligence-and-Data-Analytics-Consultant-II---Remote_R32407</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>greenhouse|stripe|7376419</t>
+          <t>workday|centene|/job/remote-mo/data-analyst-iii_1642364-1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>stripe</t>
+          <t>centene/wd5/Centene_External</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7376419</t>
+          <t>/job/Remote-MO/Data-Analyst-III_1642364-1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Data Analyst - Economic Insights &amp; Communications</t>
+          <t>Data Analyst III</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>8 Locations</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7376419</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Who we are About Stripe Stripe is a financial infrastructure platform for businesses. Millions of companies - from the world’s largest enterprises to the most ambitious startups - use Stripe to accept payments, grow their revenue, and accelerate new business opportunities. Our mission is to increase the GDP of the internet, and we have a staggering amount of work ahead. That means you have an unprecedented opportunity to put the global economy within everyone's reach while doing the most important work of your career. About the team We’re looking for an experienced data analyst to deepen understanding around the economic impact Stripe is having globally. You will be part of a community of analysts and data scientists on the Go-to-Market Analytics team, and you will partner with Stripe’s Communications teams to build and protect Stripe’s brand and influence across the world. What you’ll do This person will bridge Economic Insights and how we Communicate them with the broader public. Stripe has a unique view of the world, with real-time insight into changing trends, industries, and cross-border commerce. The Data Analyst, Economic Insights &amp; Communication role will focus on constructing and analyzing data, built upon robust data pipelines and a strong data architecture, to demonstrate how Stripe enables broad and often surprising economic growth. This role will help tease out novel economic insights from Stripe data to tell stories about how pockets of the economy are evolving, and how Stripe is advancing economic opportunity and increasing the GDP of the internet. Responsibilities Partner with the Communications teams to imagine, scope, and lead research projects that bring to life different facets of Stripe’s economic impact Publish findings both internally and externally Generate hypotheses, rapidly test them against Stripe data, and proactively share the most interesting nuggets Design, implement and maintain data pipelines and dashboards to generate insights from Stripe internal and external public data sources Define and monitor key economic impact metrics Go deep on understanding business drivers, user segments, cohorts and macroeconomic trends Partner closely with Communications teams to identify and analyze key trends and produce social posts, blogs, reports, briefings and campaign content leveraging Stripe data Who you are We're looking for someone who meets the minimum requirements to be considered for the role. If you meet these requirements, you are encouraged to apply. The preferred qualifications are a bonus, not a requirement. Minimum requirements 3+ years of experience in analytical roles working with large datasets Bachelor’s degree in Statistics, Economics, Mathematics, Engineering, Sciences or a related quantitative field Proficiency in SQL and Python and experience building and maintaining data pipelines using a distributed data framework Experience building self-serve dashboards or other scalable analytical tools for partner teams Experience developing data-informed narratives and visualizations for external publication Preferred qualifications Master’s degree in Statistics, Economics, Mathematics, Engineering, Sciences or a related quantitative field and/or experience in working on data analytics in the tech field Experience working with institutions that are respected by policymakers and the wider public for their economic insight Familiarity with survey design and analysis</t>
-        </is>
-      </c>
+          <t>https://centene.wd5.myworkdayjobs.com/en-US/Centene_External/job/Remote-MO/Data-Analyst-III_1642364-1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>greenhouse|stripe|7952048</t>
+          <t>workday|prog leasing|/job/utah/data-scientist--remote-_jr101816-1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Prog Leasing</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>stripe</t>
+          <t>progleasing/wd5/ProgLeasingCareers</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7952048</t>
+          <t>/job/Utah/Data-Scientist--Remote-_JR101816-1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Capital Underwriting</t>
+          <t>Data Scientist (Remote)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Utah</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7952048</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Who we are About Stripe Stripe is a financial infrastructure platform for businesses. Millions of companies—from the world’s largest enterprises to the most ambitious startups—use Stripe to accept payments, grow their revenue, and accelerate new business opportunities. Our mission is to increase the GDP of the internet, and we have a staggering amount of work ahead. That means you have an unprecedented opportunity to put the global economy within everyone’s reach while doing the most important work of your career. About the team Stripe Capital provides access to fast, flexible financing to small-and-medium businesses on Stripe to accelerate their growth, and we lent over $1B in 2024. Businesses use the funds for marketing, team growth, geographic expansion, working capital, new equipment purchases, and much more. Machine learning is core to Stripe Capital’s business—we use information about businesses from their activity within and outside of Stripe and our models to automatically underwrite uniquely tailored financing offers to their needs, which banks are often unable to do. We are doing so through models with an established performance history, data infrastructure that is Stripe scale, and a strong feedback loop that includes explainability, anomaly detection and a risk portfolio management layer. We're an end-to-end team going from ideas to models to shipping in production. What you’ll do As a machine learning engineer for Stripe Capital, you'll be responsible for designing, building, training, evaluating, deploying, and owning ML models in production with the goals of providing financing opportunities to as many users as possible while satisfying financial performance goals. You'll work closely with software engineers, data scientists, product managers, and risk managers to operate Stripe’s ML powered systems, features, and products. You'll also contribute to and influence ML architecture at Stripe and be a part of a larger ML community. Responsibilities Design state-of-the-art ML models and large scale ML systems for underwriting and portfolio management for Stripe Capital based on ML principles, domain knowledge, risk, regulatory and engineering constraints Design systems to speed up the time from idea to deployment of new models Experiment and iterate on ML models (using tools such as PyTorch and TensorFlow) to achieve key business goals and drive efficiency Develop pipelines and automated processes to train and evaluate models in offline and online environments Integrate ML models into production systems and ensure their scalability and reliability Collaborate with product and strategy partners to propose, prioritize, and implement new product features Engage with the latest developments in ML/AI and take calculated risks in transforming innovative ML ideas into productionized solutions Who you are We are looking for ML Engineers who are passionate about building ML systems that touch the lives of millions. You have experience developing efficient feature pipelines, building advanced ML models, and deploying them to production. You are comfortable with ambiguity, love to take initiative, have a bias towards action, and thrive in a collaborative environment. We’re looking for someone who can bring new ideas to the table on building models able to push the state of the art at Stripe, especially within the regulatory and operational constraints of a financing business. Minimum requirements 5+ years of industry experience building and shipping ML systems in production Proficient with ML libraries and frameworks such as PyTorch, TensorFlow, XGBoost, as well as Spark Hands-on experience in designing, training, and evaluating machine learning models Hands-on experience in productionizing and deploying models at scale Hands-on experience in orchestrating complicated data pipelines and efficiently leveraging large-scale datasets Preferred qualifications MS/PhD degree in ML/AI or related field (e.g. math, physics, statistics) Proven track record of building and deploying ML systems that have effectively solved ambiguous business problems Experience in adversarial domains such as Lending, Trading, Fraud Experience with Deep Learning including the latest architectures such as transformers, test-time compute, reinforcement learning</t>
-        </is>
-      </c>
+          <t>https://progleasing.wd5.myworkdayjobs.com/en-US/ProgLeasingCareers/job/Utah/Data-Scientist--Remote-_JR101816-1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>greenhouse|stripe|7739207</t>
+          <t>workday|prog leasing|/job/senior-data-analyst--hybrid---atlanta--ha-_jr101798</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Prog Leasing</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>stripe</t>
+          <t>progleasing/wd5/ProgLeasingCareers</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>7739207</t>
+          <t>/job/Senior-Data-Analyst--Hybrid---Atlanta--HA-_JR101798</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sales Compensation Analytics &amp; Systems Specialist</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>CHI, SF, NYC, SEA, US Remote</t>
-        </is>
-      </c>
+          <t>Senior Data Analyst (Hybrid - Atlanta, GA)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7739207</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Who we are About Stripe Stripe is a financial infrastructure platform for businesses. Millions of companies—from the world's largest enterprises to the most ambitious startups—use Stripe to accept payments, grow their revenue, and accelerate new business opportunities. Our mission is to increase the GDP of the internet, and we have a staggering amount of work ahead. That means you have an unprecedented opportunity to put the global economy within everyone's reach while doing the most important work of your career. About the team The Sales Compensation team at Stripe is responsible for the overall compensation strategy, design, and payment administration for the global sales organization. We ensure that Stripe's objectives align with the compensation program and that our sales teams are paid accurately and on time. We provide thought leadership for the go-to-market initiatives so that performance and compensation are effectively correlated. The Sales Compensation team partners closely with the revenue-generating and support functions across Stripe to support the success of our go-to-market efforts. What you'll do In this role, you'll digest critical data sets of our sales performance and correlation to variable compensation. The objective is to provide advanced analytics that translate raw trends into a compelling business narrative, synthesizing the strategic implications, quantifying the business impact, and prescribing actionable next steps to shape compensation strategies for our fast-growing sales force. As Stripe's sales teams and commercial strategy grow in size and complexity, this information is required to ensure we have industry-leading compensation mechanisms to motivate and reward our world-class sales organization. An equally important component of your role is supporting the enhancement and use of our Incentive Compensation Management (ICM) tool. You'll work closely with our experienced product expert to ensure we use our ICM to its maximum capacity for compensation calculations and reporting. You'll be equally passionate about data analytics and excel as a program management partner for a compensation system. You'll need experience working with significant autonomy to design an analytics framework for compensation performance measurement, as well as part of a team to support compensation calculations. You bring proven leverage of analytics and quantitative data to calculate and validate compensation. You also bring resilience and the ability to both partner and lead in cross-functional situations. This role is based out of Stripe's South San Francisco, Chicago, or New York City offices. Responsibilities • Monthly measurement of sales force quota attainment at varying degrees of granularity • Monthly forecasting of compensation to target based on monthly quota attainment analysis • Conduct deep-dive analysis to uncover the root causes of disconnects between the performance and compensation correlation. Provide the context on why it is happening and propose specific solutions to align performance with compensation • Provide reporting, with analysis and recommendations, monthly and quarterly to senior business leadership • Support system administration for the quarterly compensation cycle • Ensure the accurate and timely compensation each quarter to the entire sales force through the ICM • Build and maintain reporting dashboards for use at the individual, management, and executive levels Who you are We're looking for someone who meets the minimum requirements to be considered for the role. If you meet these requirements, you are encouraged to apply. The preferred qualifications are a bonus, not a requirement. Minimum requirements • 4+ years of experience in a Sales Compensation or Sales Operations role • BS or BA in Business, Data Science, Economics, Finance, Math, or Statistics • Experience using a commercial Incentive Compensation Management tool (e.g. Callidus, Captivate IQ, Varicent, Xactly) • Demonstrated data analytics expertise with proven results of optimizing sales results • Strong logic, problem-solving, and spreadsheet modeling skills Preferred qualifications • MBA or applicable master's degree (e.g. Finance, Data Science, etc.) • Sales compensation design experience</t>
-        </is>
-      </c>
+          <t>https://progleasing.wd5.myworkdayjobs.com/en-US/ProgLeasingCareers/job/Senior-Data-Analyst--Hybrid---Atlanta--HA-_JR101798</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>1</v>
       </c>
@@ -1594,7 +1570,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>greenhouse|stripe|7826761</t>
+          <t>greenhouse|coinbase|7942306</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1604,27 +1580,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>stripe</t>
+          <t>coinbase</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7826761</t>
+          <t>7942306</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Software Engineer, Security Analytics Infrastructure</t>
+          <t>AMLCO &amp; Senior Compliance Associate</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>US - Remote</t>
+          <t>Remote - Cyprus</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1635,12 +1611,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7826761</t>
+          <t>https://www.coinbase.com/careers/positions/7942306?gh_jid=7942306</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Who we are About Stripe Stripe is a financial infrastructure platform for businesses. Millions of companies—from the world's largest enterprises to the most ambitious startups—use Stripe to accept payments, grow their revenue, and accelerate new business opportunities. Our mission is to increase the GDP of the internet, and we have a staggering amount of work ahead. That means you have an unprecedented opportunity to put the global economy within everyone's reach while doing the most important work of your career. About the team In this role, you'd join Stripe's Security Analytics Infrastructure team. Our mission is to enable Stripe's detection and response by generating, centralizing, and organizing security data through simple, reliable pipelines and providing a platform of core security systems. We also undertake experimental, bespoke projects that close Stripe‑specific security gaps and accelerate outcomes for our partner teams. What you'll do As a Software Engineer on this team, you'll use your blend of security and software engineering expertise to build and support our key services including a SIEM, SOAR, endpoint detection and response, server observability, threat intel platform, and AI infrastructure. You'll work closely with partner teams working in multiple program areas of cyber defense, including cyber intelligence, threat detection, vulnerability management, secure devices, and compliance. Overall, you'll help ensure that we have the right data in the right place at the right time for our users. Responsibilities • Build and maintain services and dataflows related to our security analytics platform • Collaborate with other teams to drive improvements to processes our platform supports • Continuously improve our security posture, processes, and tools Who you are We're looking for someone who meets the minimum requirements to be considered for the role. If you meet these requirements, you are encouraged to apply. The preferred qualifications are a bonus, not a requirement. Minimum requirements • 5+ years software engineering experience in a high-stakes production environment • Significant experience in applying software engineering in the cybersecurity field • Experience in applying AI tooling in this space (e.g. Claude Code, agent-based approaches, etc.) • Empathy, strong communication skills, and a deep respect for the power of collaboration • Excellent problem-solving skills and attention to detail • High standards for code quality and a constructive attitude to help others raise the bar Preferred qualifications • Go and Python experience • An ability to think creatively and holistically about reducing risk in a complex environment • Previous experience in a regulated industry (e.g., financial services, healthcare)</t>
+          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . As the AMLCO &amp; Senior Compliance Associate for Coinbase's Cyprus MiFID entity, you'll own Financial Crime Compliance (AML/CFT) while supporting the Head of Compliance in building and running the broader compliance program. The Compliance team ensures our Cyprus operations meet CySEC and EU regulatory expectations across AML/CFT, MiFID conduct, Market Abuse, and data protection, enabling the business to scale safely. You'll combine formal AMLCO responsibilities with hands-on second-line oversight of risk assessment, monitoring, policy governance, training, and regulatory engagement. Hybrid Role: Please expect to be remote 4 days per week and in-office on Wednesdays. What you'll do: Own all AMLCO deliverables for the Cyprus MiFID entity, including the Annual AMLCO Report, AML Risk Assessment, and periodic financial crime compliance reporting to senior management and the Board. Lead second-line monitoring and testing across AML/CFT and broader conduct/compliance areas, documenting results, findings, and remediation actions for internal governance bodies. Drive regulatory engagement with CySEC, the FIU, and competent authorities, coordinating responses to information requests, inspections, and thematic reviews. Partner with first-line teams to assess the effectiveness of onboarding, KYC/EDD, sanctions screening, transaction monitoring, and STR/SAR reporting controls, escalating gaps and driving remediation. Build and maintain local compliance and AML/CFT policies, procedures, and frameworks aligned with EU/Cyprus requirements (MiFID II, AMLD, MiCA) and group-level standards. Support the Head of Compliance with day-to-day oversight, governance preparation, and key projects, serving as deputy during periods of absence. Required Skills and Experience: 4-6 years in compliance roles within Cyprus-regulated financial services, with direct AML/CFT and MiFID investment services exposure, including at least 2 years in senior-level positions. CySEC Advanced and CySEC AML certifications held. Demonstrated experience preparing AMLCO deliverables (Annual Reports, AML Risk Assessments) and executing second-line monitoring/testing programs. Proven track record engaging with CySEC, the FIU, or external auditors through inspections, thematic reviews, or regulatory reporting cycles. Hands-on experience drafting compliance policies and operating or overseeing AML/CFT frameworks within EU-regulated entities. Fluency in English required; Greek language proficiency is a strong plus. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Req ID: P76940 #LI-Remote Pay Transparency Notice: The target annual base salary for this position can range as detailed below. Total compensation may also include equity and bonus eligibility and benefits (including medical, dental, and vision). Annual base salary range (excluding equity and bonus): €64.100 — €64.100 EUR Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -1650,7 +1626,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>greenhouse|stripe|7921649</t>
+          <t>greenhouse|coinbase|8020892</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1660,2921 +1636,825 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>stripe</t>
+          <t>coinbase</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7921649</t>
+          <t>8020892</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Staff Data Analyst</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Remote - USA</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7921649</t>
+          <t>https://www.coinbase.com/careers/positions/8020892?gh_jid=8020892</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Who we are About Stripe Stripe is a financial infrastructure platform for businesses. Millions of companies—from the world’s largest enterprises to the most ambitious startups—use Stripe to accept payments, grow their revenue, and accelerate new business opportunities. Our mission is to increase the GDP of the internet, and we have a staggering amount of work ahead. That means you have an unprecedented opportunity to put the global economy within everyone’s reach while doing the most important work of your career. About the team The Risk Data Science team builds the data foundations, models, and measurement frameworks that power Stripe's risk and product decisions — from underwriting and reserves to merchant interventions and enablements. We're at an inflection point: as Stripe increasingly offers risk capabilities as a product to platforms and users, we need a data leader to shape how we build, measure, and evolve our risk data strategy across the What you’ll do We are looking for an experienced data analyst to drive the data strategy for our risk as a product offering. Define the metrics, data products, and analytical frameworks needed as Stripe brings risk capabilities to platforms and connected accounts at scale. Partner with Product, Engineering, and Risk leadership to ensure data investments align with the product roadmap. You will design metrics, pipelines, and data products that serve as the analytical backbone for risk decisioning. You will own the definition, reliability, and visibility of our most important risk metrics. Establish a canonical set of north star and operational metrics and ensure they are trustworthy, well-documented, and consistently surfaced to the right audiences. Build and maintain the infrastructure that keeps these metrics accurate as our data and product landscape evolves, including clear ownership, alerting on regressions, and scalable pipelines that reduce the cost of keeping insights current. You will also own and evolve Stripe's risk experimentation strategy by defining what we test, how we measure, and how we learn. Ensure we can rigorously evaluate the impact of changes to risk policies, merchant journeys, and risk models across diverse merchant populations. Finally, you will mentor and raise the bar for the Data Analysts on the team. Set technical and strategic standards. Guide junior and senior analysts on how to frame ambiguous problems, structure analyses for maximum impact, and communicate findings to senior stakeholders. Who you are We’re looking for someone who meets the minimum requirements to be considered for the role. If you meet these requirements, you are encouraged to apply. The preferred qualifications are a bonus, not a requirement. Minimum requirements 10+ years in Data Analytics, Data Science, or related roles Track record of defining and driving data strategy across multiple teams — not just executing on a roadmap, but shaping it Experience designing experimentation frameworks or measurement strategies for complex, multi-variant systems (e.g., risk policies, pricing, marketplace dynamics) Deep expertise in SQL; proficiency in Python Strong ability to translate ambiguous business problems into structured analytical approaches and communicate findings to executive stakeholders Experience building and scaling data products (metrics frameworks, pipelines, dashboards) that become operational infrastructure, not one-off analyses Demonstrated ability to influence without authority across engineering, product, and business teams Proficiency with AI tools to accelerate model development, analysis and coding Preferred qualifications Master’s degree in Mathematics, Statistics, Economics, Engineering, or a related technical field Experience in risk, trust &amp; safety, or related domains and understanding of risk in the Fintech space Experience building data for platform/product offerings where data is part of the product surface, not just internal analytics Familiarity with causal inference and A/B testing in non-standard environments (e.g., where randomization is constrained by risk considerations)</t>
+          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . Analytics Engineer - Compliance Data As an Analytics Engineer on the Compliance Data team within Platform , you'll build and maintain the production-grade data foundations that every regulatory obligation at Coinbase depends on. This team owns the Compliance Data Mart (CDM), Coinbase's canonical source of truth for user, transaction, and compliance data. You'll own the full lifecycle of data models and pipelines that downstream reporting, analytics, and AI workflows all build on, while also delivering accurate, timely data when regulators come calling. What you'll do: Own end-to-end development of production-grade data models and pipelines at the core of the CDM, covering user, transaction, and compliance data across retail and institutional product lines, from architecture through deployment and maintenance. Build data quality checks, data contracts, validation logic, and monitoring that protect data integrity before issues propagate to downstream reports or workflows. Partner with upstream engineering teams to fix data gaps and absorb product changes at the source, taking accountability for data issues anywhere in the stack rather than passing them downstream. Support live regulatory exams, audits, and ad hoc regulator requests with accurate, timely data, balancing time-sensitive reactive work with long-term foundational projects. Automate recurring manual workflows into scalable pipelines and self-serve tooling, enabling downstream teams and AI agents to answer their own questions. Required Skills and Experience: 2+ years of experience building and maintaining production data pipelines and data models, with strong proficiency in SQL, Python, dbt, and a modern warehouse platform (Snowflake, Databricks, or similar). Track record implementing data quality frameworks including data contracts, validation logic, reconciliation, and monitoring to catch issues before they reach downstream reports. Experience supporting time-sensitive, high-stakes data needs (regulatory exams, audits, or financial reporting) where accuracy and timeliness are non-negotiable. Demonstrated ability to turn tribal knowledge and recurring manual workflows into durable, documented infrastructure. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Job ID: P77413 Pay Transparency Notice: Base salary varies by location (see range below). Total compensation may also include equity and bonus eligibility, and benefits (medical, dental, vision, 401(k)). Annual base salary range (excluding equity and bonus): $152,405 — $179,300 USD Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>workday|usaa|/job/san-antonio-home-office-iiiii/data-scientist-lead---ai-ml_r0115805</t>
+          <t>greenhouse|coinbase|8024880</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
+          <t>coinbase</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>/job/San-Antonio-Home-Office-IIIII/Data-Scientist-Lead---AI-ML_R0115805</t>
+          <t>8024880</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Data Scientist Lead - Model Development</t>
+          <t>Analytics Engineer, GFCO Analytics</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>6 Locations</t>
+          <t>Remote - USA</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/San-Antonio-Home-Office-IIIII/Data-Scientist-Lead---AI-ML_R0115805</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>https://www.coinbase.com/careers/positions/8024880?gh_jid=8024880</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . We're hiring an Analytics Engineer to join the GFCO Analytics Engineering team and build the data foundations that power customer experience and compliance operations at Coinbase. You'll own end-to-end data pipelines, develop trusted metrics, and enable CX stakeholders to make faster, better decisions with clean, reliable data. This is a high-impact role where you'll directly influence how we serve and protect our customers while scaling our analytics capabilities. What you'll do: Own the design, build, and maintenance of data models and pipelines that support CX operations, compliance reporting, and customer insights, ensuring data is accurate, timely, and well-documented. Partner with CX Operations, Compliance, and Product teams to translate business needs into data requirements and deliver self-serve analytics solutions that reduce manual effort. Build and maintain dashboards, metrics, and reporting tools that give CX leaders visibility into performance, customer trends, and compliance health. Drive data quality and governance within the CX data domain by implementing testing, monitoring, and documentation standards that ensure stakeholder trust in the data. Identify opportunities to automate recurring data workflows and reporting processes, shifting the team from reactive requests toward scalable, self-serve solutions. Collaborate with broader Data Engineering and Analytics teams to align on best practices, share learnings, and contribute to Coinbase's overall data infrastructure. Required Skills and Experience: 3+ years of experience in analytics engineering, data engineering, or a related data role, with hands-on experience building and maintaining data pipelines and models. Proficiency in SQL and experience with modern data stack tools such as dbt, Airflow, and cloud data warehouses (Snowflake, Databricks, or similar). Experience with data modeling concepts (dimensional modeling, star/snowflake schemas) and building trusted, well-documented data products. Familiarity with BI/visualization tools (Looker, Tableau, or similar) and experience building dashboards and self-serve analytics solutions. Track record of partnering with non-technical stakeholders to translate business needs into data solutions, particularly in customer experience, operations, or compliance domains. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Pay Transparency Notice: Base salary varies by location (see range below). Total compensation may also include equity and bonus eligibility, and benefits (medical, dental, vision, 401(k)). Annual base salary range (excluding equity and bonus): $152,405 — $179,300 USD Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
+        </is>
+      </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>workday|usaa|/job/san-antonio-home-office-i/p-c-analytics-product-development-manager--auto-telematics-_r0119126</t>
+          <t>greenhouse|coinbase|8031260</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
+          <t>coinbase</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>/job/San-Antonio-Home-Office-I/P-C-Analytics-Product-Development-Manager--Auto-Telematics-_R0119126</t>
+          <t>8031260</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>P&amp;C Analytics Product Development Manager (Auto Telematics)</t>
+          <t>Machine Learning Engineer, CX Intelligence</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>6 Locations</t>
+          <t>Remote - Brazil</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/San-Antonio-Home-Office-I/P-C-Analytics-Product-Development-Manager--Auto-Telematics-_R0119126</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>https://www.coinbase.com/careers/positions/8031260?gh_jid=8031260</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . The CX Intelligence Engineering team, part of Coinbase's Enterprise Applications and Architecture org, builds the multi-agent platform powering Coinbase Chat, Help Center, and agent tooling. As a Machine Learning Engineer on this team, you'll design and scale the agentic systems that automate complex customer support workflows, connecting LLMs with internal APIs and tools to deliver fast, accurate, and compliant AI-powered experiences for millions of customers. What you'll do: Architect multi-agent systems using advanced orchestration frameworks (LangGraph, Google ADK) to automate complex customer support procedures end-to-end. Build and scale integrations using Model Context Protocol (MCP) to connect LLMs with internal Coinbase APIs, databases, and third-party tooling. Develop automated "LLM-as-a-judge" evaluation pipelines to monitor, measure, and improve the performance of non-deterministic AI agents in production. Implement RAG, fine-tuning, and prompt engineering techniques to ensure chatbot responses are grounded, accurate, and compliant with Coinbase policies. Ship production-ready Python services that are resilient, low-latency, and capable of handling Coinbase-scale traffic across asynchronous microservices. Partner with Conversation Design and Product to translate complex business logic into executable agent procedures within the decentralized architecture. Required Skills and Experience: 3+ years building and scaling ML/AI systems in production, with demonstrated experience implementing agentic "Loop" or "ReAct" based systems where AI takes actions autonomously. Deep understanding of the LLM lifecycle including context window management, token optimization, structured output parsing (Pydantic, JSON mode), and multi-agent orchestration frameworks (LangGraph, Google ADK, or similar). Strong proficiency in Python with hands-on experience in microservices architecture, asynchronous programming, high-throughput APIs, and vector databases (Pinecone, Weaviate, or equivalent). Demonstrated ability to explain model behaviors and technical trade-offs to non-technical stakeholders across CX, Legal, and Product teams. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Job ID: P77545 Pay Transparency Notice: The target annual base salary for this position can range as detailed below. Total compensation may also include equity and bonus eligibility and benefits (including medical, dental, and vision). Annual base salary range (excluding equity and bonus): R$347.900 — R$347.900 BRL Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
+        </is>
+      </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>workday|usaa|/job/san-antonio-home-office-i/director--decision-science-analytics_r0117151</t>
+          <t>greenhouse|coinbase|7984814</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
+          <t>coinbase</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>/job/San-Antonio-Home-Office-I/Director--Decision-Science-Analytics_R0117151</t>
+          <t>7984814</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Director, Decision Science Analytics</t>
+          <t>Payments Risk Analyst II</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6 Locations</t>
+          <t>Remote - USA</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/San-Antonio-Home-Office-I/Director--Decision-Science-Analytics_R0117151</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>https://www.coinbase.com/careers/positions/7984814?gh_jid=7984814</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . Payments Risk Analyst II As a Payments Risk Analyst II on the Risk &amp; Fraud team within the Consumer &amp; Business group, you'll own the identification and mitigation of fraud risk across Coinbase's fiat payment rails, protecting the company's bottom line and millions of customers without degrading the user experience. You'll join a team that is modernizing its risk controls and building next-generation fraud prevention systems, giving you the opportunity to shape how we protect customers at scale across one of crypto's highest-volume retail platforms. What you'll do: Own end-to-end risk controls for ACH payments, scaling fraud prevention processes to keep pace with business expansion. Drive detection and mitigation of fraudulent deposit activity by implementing targeting logic against bad actors and high-risk behavior. Lead quantitative analysis of fraud performance, measuring rule precision and recall, assessing the financial impact of decisions, and surfacing tradeoffs to leadership with clear, data-backed recommendations. Partner cross-functionally with Product, Growth, Data Science, Risk ML, and Engineering to develop and iterate on risk management strategies, including the transition from heuristic rules to model-driven and synchronous friction controls. Execute investigations into anomalous customer and transaction behavior, proactively identifying monitoring gaps and closing them before they become losses. Required Skills and Experience: 4+ years of experience in risk, fraud, or payments operations, with at least 2 years focused on payments fraud prevention in a fintech, e-commerce, or financial services environment. 2+ years of hands-on experience querying and analyzing large datasets using SQL, with the ability to independently scope and execute analytics projects end-to-end. Demonstrated experience using identity-provider data and fraud-detection tooling to implement and tune risk controls. Proven ability to measure the financial impact of fraud decisions and communicate findings to senior leadership and cross-functional stakeholders. Demonstrated working knowledge of ACH payment processing and applicable NACHA rules. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Pay Transparency Notice: Base salary varies by location (see range below). Total compensation may also include equity and bonus eligibility, and benefits (medical, dental, vision, 401(k)). Annual base salary range (excluding equity and bonus): $135,320 — $159,200 USD Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
+        </is>
+      </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>workday|usaa|/job/san-antonio-home-office-i/director--decision-science-analytics---omni-channel---digital-claims-analytics_r0118626</t>
+          <t>greenhouse|coinbase|7736521</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
+          <t>coinbase</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>/job/San-Antonio-Home-Office-I/Director--Decision-Science-Analytics---Omni-Channel---Digital-Claims-Analytics_R0118626</t>
+          <t>7736521</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Director, Decision Science Analytics – Omni Channel &amp; Digital Claims Analytics</t>
+          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>7 Locations</t>
+          <t>Remote - USA</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/San-Antonio-Home-Office-I/Director--Decision-Science-Analytics---Omni-Channel---Digital-Claims-Analytics_R0118626</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>https://www.coinbase.com/careers/positions/7736521?gh_jid=7736521</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . Senior Analytics Engineer As a Senior Analytics Engineer on the Platform team, you'll build the scalable data models and pipelines that power analytics, experimentation, and decision-making across Coinbase. Our Analytics Engineering team transforms raw data into trusted, well-modeled sources that stakeholders across Product, Engineering, and Data Science rely on daily. You'll own end-to-end data solutions for specific business domains, turning complex data flows into clean, reusable frameworks that unlock commercial value at scale. What you'll do: Own end-to-end data modeling for assigned business domains, from understanding source system data flows through designing modular, reusable models (star/snowflake schemas) that serve as the single source of truth for downstream teams. Build and optimize ETL/ELT pipelines using modern tools like dbt and Airflow, ensuring data quality, reliability, and performance at scale across Snowflake or similar warehouse architectures. Partner with Engineering, Product, and Data Science teams to identify data gaps, define requirements, and deliver data products that directly enable experimentation, ad hoc analysis, and business metric optimization. Develop scalable abstractions and frameworks (UDFs, Python packages, internal data apps) that multiply the efficiency of other data teams and reduce time-to-insight across the organization. Design and deliver dashboards and visualization layers using tools like Looker or Tableau, translating complex data into clear, actionable views for cross-functional stakeholders. Required Skills and Experience: 5+ years in analytics engineering or data engineering with demonstrated expertise in designing modular data models and building production ETL/ELT pipelines using dbt, Airflow, or similar. Advanced SQL proficiency for complex transformations and query optimization, plus intermediate-to-advanced Python for scripting, automation, and building scalable frameworks (OOP experience preferred). Production experience with modern data warehouse architectures (Snowflake, Databricks) including performance tuning, data quality monitoring, and version-controlled development workflows (GitHub, CI/CD). Proven track record delivering data solutions that generated measurable business impact, with the ability to independently build domain expertise and communicate technical trade-offs to Product, Engineering, and business stakeholders. Experience with prompt engineering for LLMs (e.g., GPT), including designing and optimizing prompts for internal tooling and automation use cases. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Pay Transparency Notice: Base salary varies by location (see range below). Total compensation may also include equity and bonus eligibility, and benefits (medical, dental, vision, 401(k)). Annual base salary range (excluding equity and bonus): $180,370 — $212,200 USD Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
+        </is>
+      </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>workday|usaa|/job/san-antonio-home-office-i/actuarial-analyst-ii--intermediate----forecasting-analytics_r0118072</t>
+          <t>greenhouse|coinbase|8009392</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
+          <t>coinbase</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>/job/San-Antonio-Home-Office-I/Actuarial-Analyst-II--Intermediate----Forecasting-Analytics_R0118072</t>
+          <t>8009392</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Actuarial Analyst II (Intermediate) – Forecasting Analytics</t>
+          <t>Senior Data Scientist, CX Analytics</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>7 Locations</t>
+          <t>Remote - USA</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/San-Antonio-Home-Office-I/Actuarial-Analyst-II--Intermediate----Forecasting-Analytics_R0118072</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>https://www.coinbase.com/careers/positions/8009392?gh_jid=8009392</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . As a Senior Data Scientist on the CX Consumer Analytics team, you will serve as the foundational link between CX operations and top-line financial impact, owning the revenue calibration models, experimentation frameworks, and behavioral intelligence that connect every customer support interaction to Coinbase's asset accumulation flywheel. You will partner closely with CX Analytics Engineers, Program Managers, and Product teams to translate complex operational and behavioral data into defensible, executive-ready insights that drive measurable improvements in retention, product adoption, and automation quality. What you'll do: Own and evolve CX's Downstream Impact of Support (DSI) revenue calibration models, translating support interaction data into quantified revenue signals. Design and execute causal inference frameworks and experiments to measure the incremental impact of CX programs (Concierge, Proactive Outreach, automation interventions) on customer retention and product engagement. Build and maintain LLM-powered classification pipelines for CX contact taxonomy, customer friction detection, and issue attribution, partnering with Analytics Engineers to productionize models into CX's governed Source of Truth infrastructure. Partner with CX Program Managers and Product teams to define segmentation models and behavioral signals that enable personalized experiences and improve business outcomes. Maintain a high bar for statistical rigor across CX's analytics function, ensuring experimentation, causal analyses, and model outputs meet the standards required for executive reporting and regulatory defensibility. Required Skills and Experience: A BA/BS in a quantitative field (e.g., Statistics, Mathematics, Computer Science, Economics) with 5+ years of relevant experience, or a PhD in a quantitative field with 3+ years of relevant experience. Demonstrated experience building revenue attribution or causal impact models and driving data science projects through ambiguous problem spaces in a consumer-facing or operational analytics context. Practical expertise applying statistical concepts including A/B testing, causal inference, and ML to real-world business problems, with a high bar for production-grade accuracy and evaluation rigor. Experience designing and deploying LLM-based classification or NLP pipelines for operational or customer-facing use cases. Ability to influence cross-functional stakeholders by synthesizing complex model outputs into clear, actionable narratives for executive and product audiences. Demonstrates the ability to responsibly use generative AI tools and copilots (e.g., LibreChat, Gemini, Glean) in daily workflows, continuously learn as tools evolve, and apply human‑in‑the‑loop practices to deliver business‑ready outputs and drive measurable improvements in efficiency, cost, and quality. Pay Transparency Notice: Base salary varies by location (see range below). Total compensation may also include equity and bonus eligibility, and benefits (medical, dental, vision, 401(k)). Annual base salary range (excluding equity and bonus): $180,370 — $212,000 USD Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
+        </is>
+      </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>workday|usaa|/job/san-antonio-home-office-i/climate-scientist-senior---p-c-climate-risk---exposure-analytics_r0118347</t>
+          <t>greenhouse|coinbase|7739592</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
+          <t>coinbase</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>/job/San-Antonio-Home-Office-I/Climate-Scientist-Senior---P-C-Climate-Risk---Exposure-Analytics_R0118347</t>
+          <t>7739592</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Climate Scientist Senior – P&amp;C Climate Risk &amp; Exposure Analytics</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>San Antonio Home Office I</t>
+          <t>Remote - India</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/San-Antonio-Home-Office-I/Climate-Scientist-Senior---P-C-Climate-Risk---Exposure-Analytics_R0118347</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>https://www.coinbase.com/careers/positions/7739592?gh_jid=7739592</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . The CX Intelligence team is part of Coinbase’s Enterprise Applications and Architecture org and builds the customer-facing and internal CX experiences that connect the Help Center, chatbots (CBCB), and agent workflows. The team owns the multi-agent platform which powers coinbase chat, Help Center and agent tooling surfaces, partnering closely with Conversation Design, CX, and other Engg teams to deliver secure, compliant, and scalable AI-powered support. Our work provides the trusted and accurate automated and agent-assisted experiences—helping customers get answers faster while enabling human agents to resolve cases more effectively. We are hiring an IC5 Machine Learning Engineer to drive the evolution of our conversational ecosystem by building a seamless hybrid vendor-internal chatbot experience. You will lead the design and implementation of a sophisticated unified orchestration layer that coordinates interactions between vendor AI, internal multi-agent systems, and human participants. This role is pivotal in managing complex state transitions, context sharing, and intent routing across a distributed environment. You’ll thrive here if you enjoy high ownership, architecting complex hand-off logic between disparate LLM frameworks, and building reliable AI-enabled products that are fast, measurable, and scalable. What you'll do: Architect and deploy the orchestration layer that manages state transitions, context sharing, and intent routing across vendor and internal LLM frameworks in a distributed conversational environment. Build production-grade Python services that bridge advanced ML/AI research with reliable, measurable customer-facing products. Lead end-to-end project execution for complex ML initiatives, managing priorities, technical trade-offs, and cross-functional dependencies from design through delivery. Establish best practices for system design, coding standards, and AI/ML development workflows across the team. Mentor engineers on architectural integrity and modern AI/ML patterns, raising the technical bar for the broader team. Conduct design reviews to ensure every feature meets Coinbase's standards for security, scalability, and performance. Required Skills and Experience: 5+ years of professional experience in machine learning and software engineering, with a track record of shipping production-grade ML services at scale. Hands-on expertise building with modern AI architectures (LLMs, deep learning) and the generative AI ecosystem, including frameworks such as LangGraph, LangSmith, Google ADK, Vertex AI, or AWS Bedrock. Deep proficiency in Python with demonstrated ability to write clean, maintainable, highly-tested production code. Specialized knowledge in at least one domain: NLP, information retrieval, computer vision, or advanced statistical modeling. Proven ability to write technical design documents and present ML system architectures to cross-functional stakeholders, translating complex technical concepts for non-technical audiences. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Demonstrates the ability to responsibly use generative AI tools and copilots (e.g., LibreChat, Gemini, Glean) in daily workflows, continuously learn as tools evolve, and apply human‑in‑the‑loop practices to deliver business‑ready outputs and drive measurable improvements in efficiency, cost, and quality. Pay Transparency Notice: The target annual base salary for this position can range as detailed below. Total compensation may also include equity and bonus eligibility and benefits (including medical, dental, and vision). Annual base salary range (excluding equity and bonus): ₹6,612,600 — ₹6,612,600 INR Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
+        </is>
+      </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>workday|usaa|/job/san-antonio-home-office-i/lead-graph-data-scientist---identity-analytics_r0118883</t>
+          <t>greenhouse|coinbase|8008569</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
+          <t>coinbase</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>/job/San-Antonio-Home-Office-I/Lead-Graph-Data-Scientist---Identity-Analytics_R0118883</t>
+          <t>8008569</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lead Graph Data Scientist - Identity Analytics</t>
+          <t>Senior Machine Learning Engineer, CX Intelligence</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>6 Locations</t>
+          <t>Remote - Brazil</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/San-Antonio-Home-Office-I/Lead-Graph-Data-Scientist---Identity-Analytics_R0118883</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>https://www.coinbase.com/careers/positions/8008569?gh_jid=8008569</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . As a Machine Learning Engineer on the CX Intelligence team within Enterprise Applications and Architecture, you'll build the AI-powered conversational systems that connect Coinbase's Help Center, chatbots, and agent workflows. The team owns the multi-agent platform powering Coinbase Chat and agent tooling, partnering with Conversation Design, CX, and Engineering to deliver secure, scalable automated support. You'll lead the design and implementation of a unified orchestration layer that coordinates interactions between vendor AI, internal multi-agent systems, and human participants, directly improving how millions of customers get help. What you'll do: Architect and deploy the orchestration layer that manages state transitions, context sharing, and intent routing across vendor and internal LLM frameworks in a distributed conversational environment. Build production-grade Python services that bridge advanced ML/AI research with reliable, measurable customer-facing products. Lead end-to-end project execution for complex ML initiatives, managing priorities, technical trade-offs, and cross-functional dependencies from design through delivery. Establish best practices for system design, coding standards, and AI/ML development workflows across the team. Mentor engineers on architectural integrity and modern AI/ML patterns, raising the technical bar for the broader team. Conduct design reviews to ensure every feature meets Coinbase's standards for security, scalability, and performance. Required Skills and Experience: 5+ years of professional experience in machine learning and software engineering, with a track record of shipping production-grade ML services at scale. Hands-on expertise building with modern AI architectures (LLMs, deep learning) and the generative AI ecosystem, including frameworks such as LangGraph, LangSmith, Google ADK, Vertex AI, or AWS Bedrock. Deep proficiency in Python with demonstrated ability to write clean, maintainable, highly-tested production code. Specialized knowledge in at least one domain: NLP, information retrieval, computer vision, or advanced statistical modeling. Proven ability to write technical design documents and present ML system architectures to cross-functional stakeholders, translating complex technical concepts for non-technical audiences. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Pay Transparency Notice: The target annual base salary for this position can range as detailed below. Total compensation may also include equity and bonus eligibility and benefits (including medical, dental, and vision). Annual base salary range (excluding equity and bonus): R$455.500 — R$455.500 BRL Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
+        </is>
+      </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>workday|usaa|/job/san-antonio-home-office-i/data-scientist-senior_r0118568</t>
+          <t>greenhouse|coinbase|8008047</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
+          <t>coinbase</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>/job/San-Antonio-Home-Office-I/Data-Scientist-Senior_R0118568</t>
+          <t>8008047</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Data Scientist Senior</t>
+          <t>Senior Program Manager, Contracts &amp; Analytics</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6 Locations</t>
+          <t>Remote - USA</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/San-Antonio-Home-Office-I/Data-Scientist-Senior_R0118568</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>https://www.coinbase.com/careers/positions/8008047?gh_jid=8008047</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . As a Senior Program Manager, Contracts &amp; Analytics, you'll join Coinbase's Legal Operations team to own the strategic direction, in-house build roadmap, and ongoing optimization of our Contract Lifecycle Management (CLM) ecosystem. This role goes beyond configuration - you'll define what gets built, set the technical vision for contracting workflows, and drive AI enablement across the team. You'll serve as a strategic partner to Institutional Sales, Enterprise Architecture, and Engineering, ensuring Coinbase's contracting infrastructure scales with the business and delivers measurable speed, compliance, and insight improvements. What you'll do: Own the CLM technology roadmap and backlog, setting strategic direction for what to build, integrate, or optimize across Ironclad, Evisort, Salesforce, and emerging tools, and translating that vision into a prioritized delivery plan. Lead in-house builds and workflow development that extend beyond standard SaaS configuration, partnering with Enterprise Architecture and Engineering to design scalable, integrated contracting solutions. Drive AI enablement for the Legal Operations team by identifying high-impact automation opportunities, standing up proof of concepts (e.g., N8N, Workato, Claude, Glean), and facilitating trainings, office hours, and adoption programs that raise the team's AI fluency. Develop and manage the comprehensive contracts reporting framework and system of record for all agreements, including data extraction, metadata integrity, and data models that surface actionable insights to Institutional Sales and Legal leadership. Communicate roadmap enhancements, program outcomes, and strategic recommendations to senior stakeholders, ensuring cross-functional alignment on contracting priorities and technology investments. Lead large, cross-functional contracts initiatives end-to-end, managing dependencies across Legal, Sales, Engineering, and Compliance, and delivering on time and within scope. Required Skills and Experience: 8+ years of program or project management experience within Legal Operations, contract management, or a technology-driven operations function, with a track record of setting strategic direction for tooling and workflows, not just executing on them. Demonstrated experience owning a technology roadmap and backlog, including prioritizing build-vs-buy decisions, scoping in-house development work, and partnering with engineering and architecture teams to deliver integrated solutions. Expert-level, hands-on experience with Contract Lifecycle Management (CLM) systems (Ironclad required), including workflow design, template management, reporting, and integration planning with platforms like Salesforce. Proven ability to drive AI and automation adoption within a team, including evaluating tools, building proof of concepts, and leading enablement programs that result in measurable workflow improvements. Working knowledge of legal technology and AI-driven contract review tools (e.g., Evisort), with experience in data extraction, metadata management, and building reporting frameworks that serve as the system of record for agreements. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Postion ID: P77368 #LI-Remote Pay Transparency Notice: Base salary varies by location (see range below). Total compensation may also include equity and bonus eligibility, and benefits (medical, dental, vision, 401(k)). Annual base salary range (excluding equity and bonus): $148,835 — $175,100 USD Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
+        </is>
+      </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>workday|usaa|/job/tampa-crosstown/licensed-p-c-insurance-professional---sales-and-service--signing-bonus-_r0117494</t>
+          <t>greenhouse|coinbase|7891045</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
+          <t>coinbase</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>/job/Tampa-Crosstown/Licensed-P-C-Insurance-Professional---Sales-and-Service--Signing-Bonus-_R0117494</t>
+          <t>7891045</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Licensed P&amp;C Insurance Professional - Sales and Service (Signing Bonus)</t>
+          <t>Staff Machine Learning Engineer(Platform - Identity)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2 Locations</t>
+          <t>Remote - USA</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/Tampa-Crosstown/Licensed-P-C-Insurance-Professional---Sales-and-Service--Signing-Bonus-_R0117494</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>https://www.coinbase.com/careers/positions/7891045?gh_jid=7891045</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . Staff Machine Learning Engineer, Identity Verification As a Staff Machine Learning Engineer on the Identity Verification team within the Platform group, you'll own the ML systems that determine whether a person, document, and capture session are legitimate. Every signup, account recovery, and high-risk action at Coinbase depends on these models. You'll lead the technical strategy for IDV ML end-to-end, from architecture through production enforcement, protecting the integrity of millions of accounts. What you'll do: Own the full IDV ML stack, including document authenticity models, 1:1 and 1:N face-match, liveness detection, presentation-attack detection, and deepfake/injection detection from feature pipeline through threshold tuning and production enforcement. Build identity-graph systems using GNNs that cluster accounts sharing biometric, device, and document signals to detect synthetic-identity rings and coordinated fraud at onboarding. Develop behavioral and device-intelligence models for capture-session anomaly detection, bot-vs-human classification, and device-fingerprint-based risk scoring at real-time latency. Drive vendor ML strategy by benchmarking external models against a Coinbase-owned evaluation set, designing dynamic routing logic across providers and geographies, and building the in-house evaluation layer that catches regressions before they reach users. Lead and mentor senior and mid-level engineers in the pod while partnering with ML Platform and Risk ML teams to align cross-company ML system design. Required Skills and Experience: 8+ years deploying production ML systems at scale, with proven technical leadership owning cross-team ML architecture from design through production. Domain experience in identity verification, biometrics, or account integrity with deep applied ML in at least two of: computer vision/biometrics, GNNs, sequence models, or NLP/LLMs. Expert-level Python with production experience in TensorFlow or PyTorch, including model training, evaluation, and serving infrastructure. Track record translating KYC/AML requirements and fraud trends into ML roadmaps and communicating trade-offs to Product, Compliance, Risk, and Security stakeholders. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Pay Transparency Notice: Base salary varies by location (see range below). Total compensation may also include equity and bonus eligibility, and benefits (medical, dental, vision, 401(k)). Annual base salary range (excluding equity and bonus): $218,025 — $256,500 USD Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
+        </is>
+      </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>workday|usaa|/job/tampa-crosstown/insurance-professional---sales-and-service_r0117484</t>
+          <t>greenhouse|coinbase|8002967</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
+          <t>coinbase</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>/job/Tampa-Crosstown/Insurance-Professional---Sales-and-Service_R0117484</t>
+          <t>8002967</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Insurance Professional - Sales and Service</t>
+          <t>Staff ML Risk Analyst</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2 Locations</t>
+          <t>Remote - USA</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/Tampa-Crosstown/Insurance-Professional---Sales-and-Service_R0117484</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>https://www.coinbase.com/careers/positions/8002967?gh_jid=8002967</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . As a Staff ML Risk Analyst on the Growth &amp; Risk team within the Consumer &amp; Business group, you'll sit at the intersection of fraud intelligence and machine learning infrastructure, defining how we identify, model, and respond to sophisticated fraud at scale. Fraud at Coinbase is fast-evolving, with professional, adaptive counterparties that outpace any human response team. You'll build and shape the ML-powered, automated solutions that detect and prevent account takeover (ATO) and scam activity before it reaches our users, setting the technical direction for the ML Analytics function within Growth &amp; Risk. What you'll do: Define the ML data and feature strategy for fraud detection, determining what data needs to enter our systems so models can take intelligent, high-accuracy action on the small fraction of traffic where intervention matters most. Own the end-to-end feature engineering pipeline, identifying, building, validating, and promoting features that drive measurable improvements in ATO and scam ML performance. Diagnose gaps between current tooling infrastructure and the solutions needed, driving the roadmap to close them by applying deep knowledge of how the ML industry has evolved architecturally. Partner with Machine Learning Engineers to translate analytical insights into production-ready ML systems, ensuring models are instrumented, monitored, and continuously improved. Mentor junior team members across the ML Analytics function, defining the technical approach and translating direction into execution. Partner cross-functionally with Product Managers and Risk Analysts to surface fraud signals and translate ML findings into business-impacting decisions. Required Skills and Experience: 8+ years of hands-on experience in machine learning analytics, data science, or a related technical field, with meaningful experience applied to risk, fraud, or payments problems. Practitioner-level proficiency in Spark, Python, and big data ML as a core working stack, with demonstrated ability to operate beyond SQL and rule-based approaches. Proven experience in feature engineering for ML models, including identifying signals, building pipelines, and validating feature quality at scale. Working knowledge of the ML infrastructure landscape evolution, from Hadoop-era big data through modern feature stores (e.g., Tecton, Feast), with the ability to apply that context to close infrastructure gaps. Demonstrated ability to optimize ML systems for sensitivity and accuracy on high-stakes, low-volume fraud traffic rather than broad-coverage, high-volume use cases. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Pay Transparency Notice: Base salary varies by location (see range below). Total compensation may also include equity and bonus eligibility, and benefits (medical, dental, vision, 401(k)). Annual base salary range (excluding equity and bonus): $193,970 — $228,200 USD Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
+        </is>
+      </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>workday|usaa|/job/plano-legacy/life-insurance-sales-agent---multi-level-opportunity_r0118601</t>
+          <t>greenhouse|coinbase|8024877</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
+          <t>coinbase</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>/job/Plano-Legacy/Life-Insurance-Sales-Agent---Multi-Level-Opportunity_R0118601</t>
+          <t>8024877</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Life Insurance Sales Agent – Multi-Level Opportunity</t>
+          <t>Technical Program Manager, GFCO Analytics</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Plano Legacy</t>
+          <t>Remote - USA</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/Plano-Legacy/Life-Insurance-Sales-Agent---Multi-Level-Opportunity_R0118601</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>https://www.coinbase.com/careers/positions/8024877?gh_jid=8024877</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . As a Technical Program Manager on the GFCO Analytics Engineering team, you'll own the roadmap and execution for the data models, metrics, and dashboards that power Customer Experience and Compliance Operations at Coinbase. This team combines deep domain expertise in regulated operations with modern data engineering (Snowflake, Airflow, Superset/Looker, and AI tooling) to deliver trusted, self-serve data products that drive faster decisions and stronger customer outcomes. You'll distill requests from 15+ cross-functional teams, prioritize work based on impact and regulatory need, and create the operational leverage that lets analytics engineers focus on building rather than managing process. What You'll Do: Own the CX Analytics Engineering roadmap, distilling requests from Operations, Compliance, Risk, WFM, BizOps, and Product teams into a prioritized backlog scoped by impact, regulatory urgency, and team capacity Drive program execution across data model builds, pipeline development, dashboard delivery, and regulatory reporting workstreams, holding the team accountable to timelines and quality standards Build and automate project management processes, reducing operational overhead so analytics engineers spend more time building data products and less time on coordination Partner with CX Operations leadership, Compliance, and Data/Platform Engineering to resolve pipeline dependencies, align on shared data models, and ensure regulatory reporting accuracy Implement testing, monitoring, and documentation standards (data contracts, alerting, quality checks) that reduce ad-hoc firefighting and build stakeholder trust in CX data products Leverage AI-assisted workflows and tooling to compress speed-to-insight, automate reporting, and scale the team's impact without growing headcount linearly with business complexity Required Skills and Experience: 7+ years of experience in technical program management, with at least 3 years supporting data engineering, analytics, or data platform teams in a regulated environment (fintech, financial services, or crypto) Proven track record owning and prioritizing a technical roadmap across multiple concurrent workstreams, balancing competing stakeholder needs with engineering capacity and regulatory requirements Fluency with modern data stack components (e.g., Snowflake, Airflow, Looker/Superset, dbt) and the ability to engage technically on data modeling, pipeline architecture, and data quality frameworks Demonstrated ability to create operational leverage through process automation, tooling improvements, and structured program management that frees engineering teams to focus on high-value delivery Experience driving alignment across 10+ cross-functional stakeholders (Operations, Compliance, Risk, Product, Engineering) where ownership is distributed and trade-offs must be actively managed Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Pay Transparency Notice: Base salary varies by location (see range below). Total compensation may also include equity and bonus eligibility, and benefits (medical, dental, vision, 401(k)). Annual base salary range (excluding equity and bonus): $148,835 — $175,100 USD Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
+        </is>
+      </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>workday|usaa|/job/tampa-crosstown/life-insurance-sales-agent---multi-level--opportunity_r0118602</t>
+          <t>greenhouse|anthropic|5198108008</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>/job/Tampa-Crosstown/Life-Insurance-Sales-Agent---Multi-Level--Opportunity_R0118602</t>
+          <t>5198108008</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Life Insurance Sales Agent – Multi-Level  Opportunity</t>
+          <t>Research Engineer, Machine Learning (RL Velocity)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2 Locations</t>
+          <t>Remote-Friendly (Travel-Required) | San Francisco, CA | New York City, NY</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/Tampa-Crosstown/Life-Insurance-Sales-Agent---Multi-Level--Opportunity_R0118602</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5198108008</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>About Anthropic Anthropic’s mission is to create reliable, interpretable, and steerable AI systems. We want AI to be safe and beneficial for our users and for society as a whole. Our team is a quickly growing group of committed researchers, engineers, policy experts, and business leaders working together to build beneficial AI systems. About the role The RL Velocity team owns the efficiency and reliability of our RL Science stack - the infrastructure, tooling, and systems that let researchers iterate quickly on training runs. As a Research Engineer on the team, you'll build and improve the core platform that underpins how we do RL at Anthropic, removing bottlenecks that slow down research and making it easier for the broader org to ship better models faster. This is high-leverage work: small improvements to velocity compound across every researcher and every run. Responsibilities Build and improve the RL training infrastructure that researchers depend on day-to-day Identify and remove bottlenecks across the RL stack: debugging, profiling, and rearchitecting where needed Partner closely with researchers and with adjacent engineering teams (inference, sandboxing, and many more) to understand pain points and ship tooling that makes them faster Own the reliability and performance of research runs end-to-end Contribute to design decisions that shape how Anthropic does RL at scale You may be a good fit if you Have strong software engineering fundamentals and a track record of building performant, reliable systems Have worked on ML infrastructure, distributed systems, or research tooling Care about enabling other people's work and find leverage through platforms rather than individual experiments Are comfortable operating across the stack, from low-level performance work to RL algorithms Have a bias toward shipping and iterating quickly, with a mix of high agency and low ego Strong candidates may also have Experience with large-scale distributed training (RL, pre-training, or post-training) Familiarity with JAX, PyTorch, or similar ML frameworks A track record of operating at the edge of research and infra in a fast-moving environment Deadline to apply: None. Applications will be reviewed on a rolling basis. The annual compensation range for this role is listed below. For sales roles, the range provided is the role’s On Target Earnings ("OTE") range, meaning that the range includes both the sales commissions/sales bonuses target and annual base salary for the role. Annual Salary: $500,000 — $850,000 USD Logistics Minimum education: Bachelor’s degree or an equivalent combination of education, training, and/or experience Required field of study: A field relevant to the role as demonstrated through coursework, training, or professional experience Minimum years of experience: Years of experience required will correlate with the internal job level requirements for the position Location-based hybrid policy: Currently, we expect all staff to be in one of our offices at least 25% of the time. However, some roles may require more time in our offices. Visa sponsorship: We do sponsor visas! However, we aren't able to successfully sponsor visas for every role and every candidate. But if we make you an offer, we will make every reasonable effort to get you a visa, and we retain an immigration lawyer to help with this. We encourage you to apply even if you do not believe you meet every single qualification. Not all strong candidates will meet every single qualification as listed. Research shows that people who identify as being from underrepresented groups are more prone to experiencing imposter syndrome and doubting the strength of their candidacy, so we urge you not to exclude yourself prematurely and to submit an application if you're interested in this work. We think AI systems like the ones we're building have enormous social and ethical implications. We think this makes representation even more important, and we strive to include a range of diverse perspectives on our team. Your safety matters to us. To protect yourself from potential scams, remember that Anthropic recruiters only contact you from @anthropic.com email addresses. In some cases, we may partner with vetted recruiting agencies who will identify themselves as working on behalf of Anthropic. Be cautious of emails from other domains. Legitimate Anthropic recruiters will never ask for money, fees, or banking information before your first day. If you're ever unsure about a communication, don't click any links—visit anthropic.com/careers directly for confirmed position openings. How we're different We believe that the highest-impact AI research will be big science. At Anthropic we work as a single cohesive team on just a few large-scale research efforts. And we value impact — advancing our long-term goals of steerable, trustworthy AI — rather than work on smaller and more specific puzzles. We view AI research as an empirical science, which has as much in common with physics and biology as with traditional efforts in computer science. We're an extremely collaborative group, and we host frequent research discussions to ensure that we are pursuing the highest-impact work at any given time. As such, we greatly value communication skills. The easiest way to understand our research directions is to read our recent research. This research continues many of the directions our team worked on prior to Anthropic, including: GPT-3, Circuit-Based Interpretability, Multimodal Neurons, Scaling Laws, AI &amp; Compute, Concrete Problems in AI Safety, and Learning from Human Preferences. Come work with us! Anthropic is a public benefit corporation headquartered in San Francisco. We offer competitive compensation and benefits, optional equity donation matching, generous vacation and parental leave, flexible working hours, and a lovely office space in which to collaborate with colleagues. Guidance on Candidates' AI Usage: Learn about our policy for using AI in our application process.</t>
+        </is>
+      </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>workday|usaa|/job/colorado-springs-campus/insurance-professional---sales-and-service_r0118400</t>
+          <t>greenhouse|intercom|8030046</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>Intercom</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
+          <t>intercom</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>/job/Colorado-Springs-Campus/Insurance-Professional---Sales-and-Service_R0118400</t>
+          <t>8030046</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Insurance Professional - Sales and Service</t>
+          <t>Director, Product Analytics</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Colorado Springs Campus</t>
+          <t>Berlin, Germany; Dublin, Ireland; EMEA, Remote; London, England</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/Colorado-Springs-Campus/Insurance-Professional---Sales-and-Service_R0118400</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>https://job-boards.greenhouse.io/intercom/jobs/8030046</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Fin is the AI Customer Agent company on a mission to help businesses provide perfect customer experiences. Our AI Agent Fin is the highest-performing AI Customer Agent on the market today, enabling businesses to deliver impeccable, always-on customer support across the customer journey – from service, to sales, to ecommerce. Powered by our own AI models, Fin resolves complex customer issues end-to-end across every channel, with minimal set-up and integration. Fin can also be combined with our natively integrated Intercom help desk for one single system that is designed to meet the needs of modern day support teams. Founded in 2011, Fin became one of the fastest growing companies and remains one of the largest private software companies in the world with nearly 30,000 global businesses using our products to transform their customer support. Driven by our core values, we push boundaries, build with speed and intensity, and relentlessly deliver incredible value to our customers. Product Data Science Leader, Fin What makes this role different This is not a classic experimentation-first product data science leadership role. Fin is a fast-moving, ambiguous, B2B AI-native product company. The role is less about owning a neat experimentation roadmap and more about helping shape direction in an environment where product bets are evolving quickly, the operating model is constantly changing, and decisions often need to be made before the data is complete. This person will not be successful if they wait to be asked for analysis. We need someone who creates momentum, brings clarity to messy problems, and helps leaders decide what matters, where to focus, and what should change. This is a highly consultative, influence-heavy leadership role. It sits at the intersection of product strategy, product analytics, customer outcomes, go-to-market signals, technical feasibility, and organizational design. Success depends on building trust and traction with product, engineering, design, research, sales, and executive stakeholders, often without relying on formal authority alone. The role is as much about shaping the system around product data science as it is about analytical depth. A major part of the job is creating the conditions for the function to be effective: improving how decisions get made, clarifying where data science should engage, helping define interfaces with adjacent functions, and ensuring insights actually influence outcomes. Vision for Product Data Science at Fin This role is not only about leading the current team well. It is also about helping define what product data science should become in an AI-native product organization. Fin is building zero-to-one products in an environment where the nature of the work is constantly shifting. As a result, the shape of product data science cannot be static or tied too closely to a traditional experimentation-and-dashboards model. We expect this leader to help define the future makeup of the function. That includes understanding where we need data scientists who are closer to engineers and builders, where we need people who operate more like researchers, and where deep statistical and analytical rigor should remain central. This person should bring a clear point of view on what an AI-native product data science function looks like, how AI should change the practice of analysis, and what capabilities, foundations, and operating model are required for the function to have the most impact over time. They should help define: the right capability mix for the team over time where foundations work belongs and how it should be prioritized how AI can increase leverage in analysis without lowering quality or rigor how product data science should evolve as Fin evolves. What this role is really about Bringing clarity to ambiguous product bets with data and insights Helping shape strategy in fast-moving B2B AI product areas Pushing for better decisions, not just better analysis Identifying product and performance gaps early; Influencing where the organization should act Creating traction for product data science where the model is still evolving Designing how product data science should work, not just delivering within the current setup Redirecting effort toward the highest-leverage problems Leading with judgment, influence, credibility, and conviction What you’ll do Help product and company leaders make better decisions on where Fin should focus Bring structure and judgment to ambiguous product, customer, and performance questions Identify what is and is not working in the product, and where intervention is most needed Shape early product direction, especially in zero-to-one and fast-evolving areas Define where product data science should engage deeply versus where lighter support is sufficient Define a vision for what product data science should look like in an AI-native product organization Shape how AI is used in analysis, insight generation, and decision support, while maintaining a high bar for rigor and judgment Improve visibility into product performance, opportunity size, and business impact Partner across product, engineering, design, research, sales, and leadership to connect product signals with customer and commercial outcomes Build trust with senior stakeholders and challenge weak logic or fuzzy thinking when needed Help design the operating model for product data science in Fin, including interfaces with analytics engineering, research, and go-to-market teams Ensure the function builds the right foundations for evaluating and improving zero-to-one AI products Coach and raise the bar for product data science work through prioritization, judgment, and leadership presence Ensure scarce data science capacity is focused on the most important problems, not just the loudest requests What we’re looking for Strong product data science leadership experience in complex product environments Track record of shaping strategy, not just supporting execution Comfort operating in ambiguity and making high-quality judgment calls with imperfect data Ability to influence senior stakeholders and challenge constructively when needed Strong analytical depth and technical skills A strong point of view on what product data science should look like in an AI-native company Experience evolving team shape and capability mix in response to changing product and organizational needs Ability to distinguish when the work calls for builder-type data scientists, research-oriented profiles, or deeper statistical specialization Strong judgment on how AI should and should not be used in analytical and data science work Excellent prioritization instincts and ability to identify high-leverage work Experience working across product, engineering, design, research, and commercial stakeholders Ability to translate across functions and connect product decisions to customer and business outcomes Strong leadership presence: credibility, judgment, communication, and follow-through Experience building or evolving operating models, team scope, or cross-functional ways of working Ideally, experience in AI-native, SaaS, or fast-moving B2B product contexts What success looks like Product and R&amp;D leaders actively rely on this person to shape priorities Data science is involved early enough to influence direction, not just validate decisions late Teams have a clearer view of product performance, opportunity size, and where intervention is needed Product data science effort is focused on the highest-leverage opportunities The interfaces between product data science and adjacent functions are clearer and more effective The function becomes embedded in how critical Fin decisions get made The overall quality of decision-making rises around the teams this person supports The team evolves toward the right mix of capabilities for an AI-native product environment AI is used to increase leverage in analysis and decision support without lowering rigor Why this role matters now Fin is operating in a space where product ships incredibly fast, decisions move quickly, ambiguity is high, and the organization needs stronger clarity on where product data science can have the most impact. We need a leader who can help shape the agenda, improve the system and operating model, and ensure product data science meaningfully changes outcomes. Benefits We are a well treated bunch, with awesome benefits! If there’s something important to you that’s not on this list, talk to us! Competitive salary and equity in a fast-growing start-up. We serve lunch every weekday, plus a variety of snack foods and a fully stocked kitchen. Regular compensation reviews - we reward great work! Pension scheme &amp; match up to 4%. Peace of mind with life assurance, as well as comprehensive health and dental insurance for you and your dependents. Flexible paid time off policy. Paid maternity leave, as well as 6 weeks paternity leave for fathers, to let you spend valuable time with your loved ones. If you’re cycling, we’ve got you covered on the Cycle-to-Work Scheme. With secure bike storage too. MacBooks are our standard, but we also offer Windows for certain roles when needed. #LI-Hybrid Policies Fin has a hybrid working policy. We believe that working in person helps us stay connected, collaborate easier and create a great culture while still providing flexibility to work from home. We expect employees to be in the office at least three days per week. We have a radically open and accepting culture at Fin. We avoid spending time on divisive subjects to foster a safe and cohesive work environment for everyone. As an organization, our policy is to not advocate on behalf of the company or our employees on any social or political topics out of our internal or external communications. We respect personal opinion and expression on these topics on personal social platforms on personal time, and do not challenge or confront anyone for their views on non-work related topics. Our goal is to focus on doing incredible work to achieve our goals and unite the company through our core values . Fin values diversity and is committed to a policy of Equal Employment Opportunity. Fin will not discriminate against an applicant or employee on the basis of race, color, religion, creed, national origin, ancestry, sex, gender, age, physical or mental disability, veteran or military status, genetic information, sexual orientation, gender identity, gender expression, marital status, or any other legally recognized protected basis under federal, state, or local law.</t>
+        </is>
+      </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>workday|usaa|/job/plano-legacy/credit-risk-analytics-manager-i_r0116413</t>
+          <t>ashby|elevenlabs|e53c5be6-5c1a-4870-ad85-8397a1f201de</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>ElevenLabs</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
+          <t>elevenlabs</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>/job/Plano-Legacy/Credit-Risk-Analytics-Manager-I_R0116413</t>
+          <t>e53c5be6-5c1a-4870-ad85-8397a1f201de</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Credit Risk Analytics Manager I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2 Locations</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/Plano-Legacy/Credit-Risk-Analytics-Manager-I_R0116413</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>workday|usaa|/job/phoenix-campus-main/insurance-professional---sales-and-service_r0118313</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>USAA</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>/job/Phoenix-Campus-Main/Insurance-Professional---Sales-and-Service_R0118313</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Insurance Professional - Sales and Service</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Phoenix Campus (Main)</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/Phoenix-Campus-Main/Insurance-Professional---Sales-and-Service_R0118313</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>workday|usaa|/job/san-antonio-home-office-i/usaa-signal-fellowship-program-data-and-analytics_r0118277</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>USAA</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>/job/San-Antonio-Home-Office-I/USAA-Signal-Fellowship-Program-Data-and-Analytics_R0118277</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>USAA Signal Fellowship Program-Data and Analytics</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>San Antonio Home Office I</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/San-Antonio-Home-Office-I/USAA-Signal-Fellowship-Program-Data-and-Analytics_R0118277</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>workday|usaa|/job/san-antonio-home-office-i/business-intelligence-analyst-senior_r0118060</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>USAA</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>/job/San-Antonio-Home-Office-I/Business-Intelligence-Analyst-Senior_R0118060</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Business Intelligence Analyst Senior</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>San Antonio Home Office I</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/San-Antonio-Home-Office-I/Business-Intelligence-Analyst-Senior_R0118060</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>workday|usaa|/job/charlotte-nc---cents/data-scientist-i_r0118100</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>USAA</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>/job/Charlotte-NC---CENTS/Data-Scientist-I_R0118100</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Data Scientist I</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Charlotte, NC - CENTS</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/Charlotte-NC---CENTS/Data-Scientist-I_R0118100</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>workday|usaa|/job/plano-legacy/data-scientist-senior_r0118066</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>USAA</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>/job/Plano-Legacy/Data-Scientist-Senior_R0118066</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Data Scientist Senior</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Plano Legacy</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/Plano-Legacy/Data-Scientist-Senior_R0118066</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>workday|usaa|/job/san-antonio-home-office-i/director-hr-data---analytics_r0118116</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>USAA</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>/job/San-Antonio-Home-Office-I/Director-HR-Data---Analytics_R0118116</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Director-HR Data &amp; Analytics</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>6 Locations</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/San-Antonio-Home-Office-I/Director-HR-Data---Analytics_R0118116</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>workday|usaa|/job/san-antonio-home-office-i/licensed-p-c-insurance-professional---sales-and-service--signing-bonus-_r0114411</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>USAA</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>usaa/wd1/USAAJOBSWD</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>/job/San-Antonio-Home-Office-I/Licensed-P-C-Insurance-Professional---Sales-and-Service--Signing-Bonus-_R0114411</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Licensed P&amp;C Insurance Professional - Sales and Service (Signing Bonus)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>San Antonio Home Office I</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>https://usaa.wd1.myworkdayjobs.com/en-US/USAAJOBSWD/job/San-Antonio-Home-Office-I/Licensed-P-C-Insurance-Professional---Sales-and-Service--Signing-Bonus-_R0114411</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>workday|allstate|/job/remote---remote/data-scientist-associate-manager---remote_r31115-1</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Allstate</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>allstate/wd5/allstate_careers</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>/job/Remote---Remote/Data-Scientist-Associate-Manager---Remote_R31115-1</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Data Scientist Associate Manager - Remote</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Remote - Remote</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>https://allstate.wd5.myworkdayjobs.com/en-US/allstate_careers/job/Remote---Remote/Data-Scientist-Associate-Manager---Remote_R31115-1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>workday|allstate|/job/remote---remote/business-intelligence-and-data-analytics-consultant-ii---remote_r32407</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Allstate</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>allstate/wd5/allstate_careers</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>/job/Remote---Remote/Business-Intelligence-and-Data-Analytics-Consultant-II---Remote_R32407</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Business Intelligence and Data Analytics Consultant II - Remote</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Remote - Remote</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>https://allstate.wd5.myworkdayjobs.com/en-US/allstate_careers/job/Remote---Remote/Business-Intelligence-and-Data-Analytics-Consultant-II---Remote_R32407</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>workday|centene|/job/remote-mo/data-analyst-iii_1642364-1</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Centene</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>centene/wd5/Centene_External</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>/job/Remote-MO/Data-Analyst-III_1642364-1</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Data Analyst III</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>8 Locations</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>https://centene.wd5.myworkdayjobs.com/en-US/Centene_External/job/Remote-MO/Data-Analyst-III_1642364-1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>workday|mmc|/job/mumbai---hiranandani/senior-manager---data-analytics---insight_r_351765-1</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>MMC</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>mmc/wd1/MMC</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>/job/Mumbai---Hiranandani/Senior-Manager---Data-Analytics---Insight_R_351765-1</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Senior Manager - Data Analytics &amp; Insight</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Mumbai - Hiranandani</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>https://mmc.wd1.myworkdayjobs.com/en-US/MMC/job/Mumbai---Hiranandani/Senior-Manager---Data-Analytics---Insight_R_351765-1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>workday|mmc|/job/bogota---calle-26/analyst--insurance-operations_r_348419</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>MMC</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>mmc/wd1/MMC</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>/job/Bogota---Calle-26/Analyst--Insurance-Operations_R_348419</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Analyst- Insurance Operations</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Bogota - Calle 26</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>https://mmc.wd1.myworkdayjobs.com/en-US/MMC/job/Bogota---Calle-26/Analyst--Insurance-Operations_R_348419</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>workday|mmc|/job/philadelphia---south-17th/vp--global-analytics_r_337035-1</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>MMC</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>mmc/wd1/MMC</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>/job/Philadelphia---South-17th/VP--Global-Analytics_R_337035-1</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>VP, Global Analytics</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>8 Locations</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>https://mmc.wd1.myworkdayjobs.com/en-US/MMC/job/Philadelphia---South-17th/VP--Global-Analytics_R_337035-1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>workday|mmc|/job/dublin---frame/senior-analyst---digital-visualization-and-data-analytics-development_r_352779</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>MMC</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>mmc/wd1/MMC</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>/job/Dublin---Frame/Senior-Analyst---Digital-Visualization-and-Data-Analytics-Development_R_352779</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Analyst - Global Data and Analytics Team (full-stack experience/Angular/React/MEAN/SQL ideal)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Dublin - Frame</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>https://mmc.wd1.myworkdayjobs.com/en-US/MMC/job/Dublin---Frame/Senior-Analyst---Digital-Visualization-and-Data-Analytics-Development_R_352779</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>workday|prog leasing|/job/utah/data-scientist--remote-_jr101816-1</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Prog Leasing</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>progleasing/wd5/ProgLeasingCareers</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>/job/Utah/Data-Scientist--Remote-_JR101816-1</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Data Scientist (Remote)</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Utah</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>https://progleasing.wd5.myworkdayjobs.com/en-US/ProgLeasingCareers/job/Utah/Data-Scientist--Remote-_JR101816-1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>workday|prog leasing|/job/senior-data-analyst--hybrid---atlanta--ha-_jr101798</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Prog Leasing</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>progleasing/wd5/ProgLeasingCareers</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>/job/Senior-Data-Analyst--Hybrid---Atlanta--HA-_JR101798</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst (Hybrid - Atlanta, GA)</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>https://progleasing.wd5.myworkdayjobs.com/en-US/ProgLeasingCareers/job/Senior-Data-Analyst--Hybrid---Atlanta--HA-_JR101798</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>workday|trinity health|/job/saint-agnes-medical-center---fresno-california/business-intelligence-analyst-lean-six-sigma-advisor_00680092</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Trinity Health</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>trinityhealth/wd1/Jobs</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>/job/Saint-Agnes-Medical-Center---Fresno-California/Business-Intelligence-Analyst-Lean-Six-Sigma-Advisor_00680092</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Business Intelligence Analyst/Lean Six Sigma Advisor</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Saint Agnes Medical Center - Fresno, California</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>https://trinityhealth.wd1.myworkdayjobs.com/en-US/Jobs/job/Saint-Agnes-Medical-Center---Fresno-California/Business-Intelligence-Analyst-Lean-Six-Sigma-Advisor_00680092</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>workday|allstate|/job/remote---remote/data-scientist-associate-manager---remote_r31115-1</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Allstate</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>allstate/wd5/allstate_careers</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>/job/Remote---Remote/Data-Scientist-Associate-Manager---Remote_R31115-1</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Data Scientist Associate Manager - Remote</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Remote - Remote</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>1</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>https://allstate.wd5.myworkdayjobs.com/en-US/allstate_careers/job/Remote---Remote/Data-Scientist-Associate-Manager---Remote_R31115-1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>workday|allstate|/job/remote---remote/business-intelligence-and-data-analytics-consultant-ii---remote_r32407</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Allstate</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>allstate/wd5/allstate_careers</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>/job/Remote---Remote/Business-Intelligence-and-Data-Analytics-Consultant-II---Remote_R32407</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Business Intelligence and Data Analytics Consultant II - Remote</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Remote - Remote</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>1</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>https://allstate.wd5.myworkdayjobs.com/en-US/allstate_careers/job/Remote---Remote/Business-Intelligence-and-Data-Analytics-Consultant-II---Remote_R32407</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>workday|allstate|/job/remote---remote/data-scientist-associate-manager---remote_r31115-1</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Allstate</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>allstate/wd5/allstate_careers</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>/job/Remote---Remote/Data-Scientist-Associate-Manager---Remote_R31115-1</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Data Scientist Associate Manager - Remote</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Remote - Remote</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>https://allstate.wd5.myworkdayjobs.com/en-US/allstate_careers/job/Remote---Remote/Data-Scientist-Associate-Manager---Remote_R31115-1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>workday|allstate|/job/remote---remote/business-intelligence-and-data-analytics-consultant-ii---remote_r32407</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Allstate</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>allstate/wd5/allstate_careers</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>/job/Remote---Remote/Business-Intelligence-and-Data-Analytics-Consultant-II---Remote_R32407</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Business Intelligence and Data Analytics Consultant II - Remote</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Remote - Remote</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>https://allstate.wd5.myworkdayjobs.com/en-US/allstate_careers/job/Remote---Remote/Business-Intelligence-and-Data-Analytics-Consultant-II---Remote_R32407</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>greenhouse|mongodb|7696633</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>MongoDB</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>mongodb</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>7696633</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7696633</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>The worldwide data management software market is massive (According to IDC, the worldwide database software market, which it refers to as the database management systems software market, was forecasted to be approximately $82 billion in 2023 growing to approximately $137 billion in 2027. This represents a 14% compound annual growth rate). At MongoDB we are transforming industries and empowering developers to build amazing apps that people use every day. We are the leading developer data platform and the first database provider to IPO in over 20 years. Join our team and be at the forefront of innovation and creativity. MongoDB is seeking a Senior Analyst to support data-driven, people-focused decision making for the company. Partnering with our People team, you will transform HR and organizational data into actionable insights to help us hire the right talent, manage our overall workforce, and improve workforce effectiveness, leading to better outcomes for our people and the company. This position requires someone with strong analytical and technical skills, the ability to tell a story with data, and who is comfortable working across multiple functional areas in a fast-paced, challenging environment. Responsibilities Partner with People teams (business partners, recruiting, culture/talent/development, etc.) to understand their questions, turn analyses into actionable data-driven insights, and make business recommendations Help develop and execute against roadmap for people data investments to both capture near-term value and set up the team for long-term success Leverage understanding of statistics to conduct analyses that help People teams make quicker, more informed decisions Write and maintain complex queries to conduct deep-dive analyses on the impact that People initiatives have on employee engagement, productivity and retention Liaise with Data Engineering and HRIS teams to create and manage a curated central repository for people data Design and build automated dashboards to empower stakeholders to self-serve their data and analytical needs Prioritize and triage analytical and reporting asks from across the People team Develop and support ongoing data governance and data quality processes Effectively communicate analytical findings to non-technical audiences Requirements 3+ years of hands-on analytics experience (focus on people/HR analytics preferred) Advanced SQL skills, comfortable manipulating very large datasets Proficient in Python or R with a strong focus on data wrangling and data analysis Extensive experience with Tableau or another leading visualization tool is required Experience analyzing complex people data (e.g. headcount, attrition, recruiting metrics, compensation data) strongly preferred but not required Experience in survey design and analysis preferred Familiarity with data architecture fundamentals and data warehousing Proficiency with data modeling and data quality best practices Demonstrated ability to effectively communicate and set priorities with key stakeholders at all levels of the organization Highly collaborative and organized, with a strong attention to detail Comfort with ambiguity and ability to work in a self-guided manner Committed to contributing to a collaborative, enjoyable, and psychologically safe work environment Exposure to Modern Cloud Data Warehouses preferred About MongoDB MongoDB is built for change, empowering our customers and our people to innovate at the speed of the market. We have redefined the database for the AI era, enabling innovators to create, transform, and disrupt industries with software. MongoDB’s unified database platform, the most widely available, globally distributed database on the market, helps organizations modernize legacy workloads, embrace innovation, and unleash AI. Our cloud-native platform, MongoDB Atlas, is the only globally distributed, multi-cloud database and is available across AWS, Google Cloud, and Microsoft Azure. With offices worldwide and over 60,000 customers, including 75% of the Fortune 100 and AI-native startups, relying on MongoDB for their most important applications, we’re powering the next era of software. Our compass at MongoDB is our Leadership Commitment, guiding how and why we make decisions, show up for each other, and win. It’s what makes us MongoDB. To drive the personal growth and business impact of our employees, we’re committed to developing a supportive and enriching culture for everyone. From employee affinity groups, to fertility assistance and a generous parental leave policy , we value our employees’ wellbeing and want to support them along every step of their professional and personal journeys. Learn more about what it’s like to work at MongoDB , and help us make an impact on the world! MongoDB is committed to providing any necessary accommodations for individuals with disabilities within our application and interview process. To request an accommodation due to a disability, please inform your recruiter. MongoDB, Inc. provides equal employment opportunities to all employees and applicants for employment and prohibits discrimination and harassment of any type and makes all hiring decisions without regard to race, color, religion, age, sex, national origin, disability status, genetics, protected veteran status, sexual orientation, gender identity or expression, or any other characteristic protected by federal, state or local laws. Req. ID: 1273383451 MongoDB’s base salary range for this role is posted below. Compensation at the time of offer is unique to each candidate and based on a variety of factors such as skill set, experience, qualifications, and work location. Salary is one part of MongoDB’s total compensation and benefits package. Other benefits for eligible employees may include: equity, participation in the employee stock purchase program, flexible paid time off, 20 weeks fully-paid gender-neutral parental leave, fertility and adoption assistance, 401(k) plan, mental health counseling, access to transgender-inclusive health insurance coverage, and health benefits offerings. Please note, the base salary range listed below and the benefits in this paragraph are only applicable to U.S.-based candidates. MongoDB’s base salary range for this role in the U.S. is: $83,000 — $162,000 USD</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>greenhouse|mongodb|7742875</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>MongoDB</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>mongodb</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>7742875</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Senior Python Engineer</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7742875</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Our Database Experience (DBX) Team A great MongoDB experience starts with great tools. The Database Experience team builds the libraries and tools that developers use day-to-day working with MongoDB. Our mission is to increase developer adoption, satisfaction and retention by providing a reliable, enjoyable interface for developers and other end-users. Our senior engineers are typically specialists in a particular programming language, but are capable of contributing to projects in other languages as well. For this role, we're looking for someone who will enjoy designing, writing, and supporting open source libraries for the Python ecosystem developers that use MongoDB. This is an opportunity to make a major impact at MongoDB as Python is one of the most popular runtimes for MongoDB users, and our driver has over 3 million daily pypi downloads. You might be right for this role if you... Have substantial experience writing high-quality software in Python Have extensive knowledge in Python tools and frameworks, scientific python and web development frameworks Have practical experience with AI/ML frameworks and technologies in Python, including large language models and agentic tools are a plus Have an interest in learning and staying up-to-date with Python ecosystem trends and best practices and incorporating them into your work Can make pragmatic design decisions, balancing tradeoffs such as usability, maintainability and delivery time Want to, or already do, participate in open source software development and communities, both online via e.g. GitHub and optionally through conferences and speaking engagements Communicate well, internally and externally, both verbally and in writing Enjoy collaborating with teammates, and mentoring junior engineers and interns Are self-motivated, organized, and have strong time management skills You'll be on the team responsible for... Developing and supporting the MongoDB Python drivers and subsidiary libraries ( PyMongo , Django MongoDB Backend , PyMongoArrow , LangChain MongoDB ) and related software, collaborating with peers in our distributed world-wide engineering team Writing and maintaining open source specifications defining common behavior and APIs shared across all of our drivers Investigating bugs and support requests from commercial customers, open source users, and internal users for the libraries our team maintains Working with our Product and Server teams on designs and specifications for new user-facing MongoDB features Success in this role means... Within one month, you will understand the high-level architecture of the drivers and how MongoDB works, and will have completed a few small bug fixes and/or feature tickets Within three months, you will be contributing effectively day-to-day, fixing bugs, implementing features, investigating and responding to open source user and customer issues, and reviewing your peers' code Within six months, you'll have implemented major, planned new features, contributed to our common driver specifications, shipped a major feature in an open source library, and will be collaborating with the Product team to help craft our roadmap Within twelve months, you'll have significantly improved the quality, performance and maintainability of our codebase, and will be taking the lead in designing and specifying major new features About MongoDB MongoDB is built for change, empowering our customers and our people to innovate at the speed of the market. We have redefined the data platform for the AI era, enabling builders to create, transform, and disrupt industries with software. MongoDB’s unified data platform, the most widely available, globally distributed data platform on the market, helps organizations modernize legacy workloads, embrace innovation, and unleash AI. Our cloud-native platform, MongoDB Atlas, is the only globally distributed, multi-cloud data platform and is available across AWS, Google Cloud, and Microsoft Azure. With offices worldwide and over 67,000 customers, including 75% of the Fortune 100 and AI-native startups, relying on MongoDB for their most important applications, we’re powering the next era of software. Our compass at MongoDB is our Leadership Commitment, guiding how and why we make decisions, show up for each other, and win. It’s what makes us MongoDB. To drive the personal growth and business impact of our employees, we’re committed to developing a supportive and enriching culture for everyone. From employee affinity groups, to fertility assistance and a generous parental leave policy , we value our employees’ wellbeing and want to support them along every step of their professional and personal journeys. Learn more about what it’s like to work at MongoDB , and help us make an impact on the world! MongoDB is committed to providing any necessary accommodations for individuals with disabilities within our application and interview process. To request an accommodation due to a disability, please inform your recruiter. MongoDB, Inc. provides equal employment opportunities to all employees and applicants for employment and prohibits discrimination and harassment of any type and makes all hiring decisions without regard to race, color, religion, age, sex, national origin, disability status, genetics, protected veteran status, sexual orientation, gender identity or expression, or any other characteristic protected by federal, state or local laws. Req ID: 1273396098 MongoDB’s base salary range for this role is posted below. Compensation at the time of offer is unique to each candidate and based on a variety of factors such as skill set, experience, qualifications, and work location. Salary is one part of MongoDB’s total compensation and benefits package. Other benefits for eligible employees may include: equity, participation in the employee stock purchase program, flexible paid time off, 20 weeks fully-paid gender-neutral parental leave, fertility and adoption assistance, 401(k) plan, mental health counseling, access to transgender-inclusive health insurance coverage, and health benefits offerings. Please note, the base salary range listed below and the benefits in this paragraph are only applicable to U.S.-based candidates. MongoDB’s base salary range for this role in the U.S. is: $126,000 — $248,000 USD</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>greenhouse|coinbase|7942306</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>coinbase</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>7942306</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>AMLCO &amp; Senior Compliance Associate</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Remote - Cyprus</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>1</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>https://www.coinbase.com/careers/positions/7942306?gh_jid=7942306</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . As the AMLCO &amp; Senior Compliance Associate for Coinbase's Cyprus MiFID entity, you'll own Financial Crime Compliance (AML/CFT) while supporting the Head of Compliance in building and running the broader compliance program. The Compliance team ensures our Cyprus operations meet CySEC and EU regulatory expectations across AML/CFT, MiFID conduct, Market Abuse, and data protection, enabling the business to scale safely. You'll combine formal AMLCO responsibilities with hands-on second-line oversight of risk assessment, monitoring, policy governance, training, and regulatory engagement. Hybrid Role: Please expect to be remote 4 days per week and in-office on Wednesdays. What you'll do: Own all AMLCO deliverables for the Cyprus MiFID entity, including the Annual AMLCO Report, AML Risk Assessment, and periodic financial crime compliance reporting to senior management and the Board. Lead second-line monitoring and testing across AML/CFT and broader conduct/compliance areas, documenting results, findings, and remediation actions for internal governance bodies. Drive regulatory engagement with CySEC, the FIU, and competent authorities, coordinating responses to information requests, inspections, and thematic reviews. Partner with first-line teams to assess the effectiveness of onboarding, KYC/EDD, sanctions screening, transaction monitoring, and STR/SAR reporting controls, escalating gaps and driving remediation. Build and maintain local compliance and AML/CFT policies, procedures, and frameworks aligned with EU/Cyprus requirements (MiFID II, AMLD, MiCA) and group-level standards. Support the Head of Compliance with day-to-day oversight, governance preparation, and key projects, serving as deputy during periods of absence. Required Skills and Experience: 4-6 years in compliance roles within Cyprus-regulated financial services, with direct AML/CFT and MiFID investment services exposure, including at least 2 years in senior-level positions. CySEC Advanced and CySEC AML certifications held. Demonstrated experience preparing AMLCO deliverables (Annual Reports, AML Risk Assessments) and executing second-line monitoring/testing programs. Proven track record engaging with CySEC, the FIU, or external auditors through inspections, thematic reviews, or regulatory reporting cycles. Hands-on experience drafting compliance policies and operating or overseeing AML/CFT frameworks within EU-regulated entities. Fluency in English required; Greek language proficiency is a strong plus. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Req ID: P76940 #LI-Remote Pay Transparency Notice: The target annual base salary for this position can range as detailed below. Total compensation may also include equity and bonus eligibility and benefits (including medical, dental, and vision). Annual base salary range (excluding equity and bonus): €64.100 — €64.100 EUR Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>greenhouse|coinbase|8020892</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>coinbase</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>8020892</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Remote - USA</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>1</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>https://www.coinbase.com/careers/positions/8020892?gh_jid=8020892</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . Analytics Engineer - Compliance Data As an Analytics Engineer on the Compliance Data team within Platform , you'll build and maintain the production-grade data foundations that every regulatory obligation at Coinbase depends on. This team owns the Compliance Data Mart (CDM), Coinbase's canonical source of truth for user, transaction, and compliance data. You'll own the full lifecycle of data models and pipelines that downstream reporting, analytics, and AI workflows all build on, while also delivering accurate, timely data when regulators come calling. What you'll do: Own end-to-end development of production-grade data models and pipelines at the core of the CDM, covering user, transaction, and compliance data across retail and institutional product lines, from architecture through deployment and maintenance. Build data quality checks, data contracts, validation logic, and monitoring that protect data integrity before issues propagate to downstream reports or workflows. Partner with upstream engineering teams to fix data gaps and absorb product changes at the source, taking accountability for data issues anywhere in the stack rather than passing them downstream. Support live regulatory exams, audits, and ad hoc regulator requests with accurate, timely data, balancing time-sensitive reactive work with long-term foundational projects. Automate recurring manual workflows into scalable pipelines and self-serve tooling, enabling downstream teams and AI agents to answer their own questions. Required Skills and Experience: 2+ years of experience building and maintaining production data pipelines and data models, with strong proficiency in SQL, Python, dbt, and a modern warehouse platform (Snowflake, Databricks, or similar). Track record implementing data quality frameworks including data contracts, validation logic, reconciliation, and monitoring to catch issues before they reach downstream reports. Experience supporting time-sensitive, high-stakes data needs (regulatory exams, audits, or financial reporting) where accuracy and timeliness are non-negotiable. Demonstrated ability to turn tribal knowledge and recurring manual workflows into durable, documented infrastructure. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Job ID: P77413 Pay Transparency Notice: Base salary varies by location (see range below). Total compensation may also include equity and bonus eligibility, and benefits (medical, dental, vision, 401(k)). Annual base salary range (excluding equity and bonus): $152,405 — $179,300 USD Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>greenhouse|coinbase|8024880</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>coinbase</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>8024880</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Analytics Engineer, GFCO Analytics</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Remote - USA</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>1</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>https://www.coinbase.com/careers/positions/8024880?gh_jid=8024880</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . We're hiring an Analytics Engineer to join the GFCO Analytics Engineering team and build the data foundations that power customer experience and compliance operations at Coinbase. You'll own end-to-end data pipelines, develop trusted metrics, and enable CX stakeholders to make faster, better decisions with clean, reliable data. This is a high-impact role where you'll directly influence how we serve and protect our customers while scaling our analytics capabilities. What you'll do: Own the design, build, and maintenance of data models and pipelines that support CX operations, compliance reporting, and customer insights, ensuring data is accurate, timely, and well-documented. Partner with CX Operations, Compliance, and Product teams to translate business needs into data requirements and deliver self-serve analytics solutions that reduce manual effort. Build and maintain dashboards, metrics, and reporting tools that give CX leaders visibility into performance, customer trends, and compliance health. Drive data quality and governance within the CX data domain by implementing testing, monitoring, and documentation standards that ensure stakeholder trust in the data. Identify opportunities to automate recurring data workflows and reporting processes, shifting the team from reactive requests toward scalable, self-serve solutions. Collaborate with broader Data Engineering and Analytics teams to align on best practices, share learnings, and contribute to Coinbase's overall data infrastructure. Required Skills and Experience: 3+ years of experience in analytics engineering, data engineering, or a related data role, with hands-on experience building and maintaining data pipelines and models. Proficiency in SQL and experience with modern data stack tools such as dbt, Airflow, and cloud data warehouses (Snowflake, Databricks, or similar). Experience with data modeling concepts (dimensional modeling, star/snowflake schemas) and building trusted, well-documented data products. Familiarity with BI/visualization tools (Looker, Tableau, or similar) and experience building dashboards and self-serve analytics solutions. Track record of partnering with non-technical stakeholders to translate business needs into data solutions, particularly in customer experience, operations, or compliance domains. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Pay Transparency Notice: Base salary varies by location (see range below). Total compensation may also include equity and bonus eligibility, and benefits (medical, dental, vision, 401(k)). Annual base salary range (excluding equity and bonus): $152,405 — $179,300 USD Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>greenhouse|coinbase|8031260</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>coinbase</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>8031260</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, CX Intelligence</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Remote - Brazil</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>1</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>https://www.coinbase.com/careers/positions/8031260?gh_jid=8031260</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . The CX Intelligence Engineering team, part of Coinbase's Enterprise Applications and Architecture org, builds the multi-agent platform powering Coinbase Chat, Help Center, and agent tooling. As a Machine Learning Engineer on this team, you'll design and scale the agentic systems that automate complex customer support workflows, connecting LLMs with internal APIs and tools to deliver fast, accurate, and compliant AI-powered experiences for millions of customers. What you'll do: Architect multi-agent systems using advanced orchestration frameworks (LangGraph, Google ADK) to automate complex customer support procedures end-to-end. Build and scale integrations using Model Context Protocol (MCP) to connect LLMs with internal Coinbase APIs, databases, and third-party tooling. Develop automated "LLM-as-a-judge" evaluation pipelines to monitor, measure, and improve the performance of non-deterministic AI agents in production. Implement RAG, fine-tuning, and prompt engineering techniques to ensure chatbot responses are grounded, accurate, and compliant with Coinbase policies. Ship production-ready Python services that are resilient, low-latency, and capable of handling Coinbase-scale traffic across asynchronous microservices. Partner with Conversation Design and Product to translate complex business logic into executable agent procedures within the decentralized architecture. Required Skills and Experience: 3+ years building and scaling ML/AI systems in production, with demonstrated experience implementing agentic "Loop" or "ReAct" based systems where AI takes actions autonomously. Deep understanding of the LLM lifecycle including context window management, token optimization, structured output parsing (Pydantic, JSON mode), and multi-agent orchestration frameworks (LangGraph, Google ADK, or similar). Strong proficiency in Python with hands-on experience in microservices architecture, asynchronous programming, high-throughput APIs, and vector databases (Pinecone, Weaviate, or equivalent). Demonstrated ability to explain model behaviors and technical trade-offs to non-technical stakeholders across CX, Legal, and Product teams. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Job ID: P77545 Pay Transparency Notice: The target annual base salary for this position can range as detailed below. Total compensation may also include equity and bonus eligibility and benefits (including medical, dental, and vision). Annual base salary range (excluding equity and bonus): R$347.900 — R$347.900 BRL Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>greenhouse|coinbase|7984814</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>coinbase</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>7984814</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Payments Risk Analyst II</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Remote - USA</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
-        <v>1</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>https://www.coinbase.com/careers/positions/7984814?gh_jid=7984814</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . Payments Risk Analyst II As a Payments Risk Analyst II on the Risk &amp; Fraud team within the Consumer &amp; Business group, you'll own the identification and mitigation of fraud risk across Coinbase's fiat payment rails, protecting the company's bottom line and millions of customers without degrading the user experience. You'll join a team that is modernizing its risk controls and building next-generation fraud prevention systems, giving you the opportunity to shape how we protect customers at scale across one of crypto's highest-volume retail platforms. What you'll do: Own end-to-end risk controls for ACH payments, scaling fraud prevention processes to keep pace with business expansion. Drive detection and mitigation of fraudulent deposit activity by implementing targeting logic against bad actors and high-risk behavior. Lead quantitative analysis of fraud performance, measuring rule precision and recall, assessing the financial impact of decisions, and surfacing tradeoffs to leadership with clear, data-backed recommendations. Partner cross-functionally with Product, Growth, Data Science, Risk ML, and Engineering to develop and iterate on risk management strategies, including the transition from heuristic rules to model-driven and synchronous friction controls. Execute investigations into anomalous customer and transaction behavior, proactively identifying monitoring gaps and closing them before they become losses. Required Skills and Experience: 4+ years of experience in risk, fraud, or payments operations, with at least 2 years focused on payments fraud prevention in a fintech, e-commerce, or financial services environment. 2+ years of hands-on experience querying and analyzing large datasets using SQL, with the ability to independently scope and execute analytics projects end-to-end. Demonstrated experience using identity-provider data and fraud-detection tooling to implement and tune risk controls. Proven ability to measure the financial impact of fraud decisions and communicate findings to senior leadership and cross-functional stakeholders. Demonstrated working knowledge of ACH payment processing and applicable NACHA rules. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Pay Transparency Notice: Base salary varies by location (see range below). Total compensation may also include equity and bonus eligibility, and benefits (medical, dental, vision, 401(k)). Annual base salary range (excluding equity and bonus): $135,320 — $159,200 USD Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>greenhouse|coinbase|7736521</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>coinbase</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>7736521</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Remote - USA</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>1</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>https://www.coinbase.com/careers/positions/7736521?gh_jid=7736521</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . Senior Analytics Engineer As a Senior Analytics Engineer on the Platform team, you'll build the scalable data models and pipelines that power analytics, experimentation, and decision-making across Coinbase. Our Analytics Engineering team transforms raw data into trusted, well-modeled sources that stakeholders across Product, Engineering, and Data Science rely on daily. You'll own end-to-end data solutions for specific business domains, turning complex data flows into clean, reusable frameworks that unlock commercial value at scale. What you'll do: Own end-to-end data modeling for assigned business domains, from understanding source system data flows through designing modular, reusable models (star/snowflake schemas) that serve as the single source of truth for downstream teams. Build and optimize ETL/ELT pipelines using modern tools like dbt and Airflow, ensuring data quality, reliability, and performance at scale across Snowflake or similar warehouse architectures. Partner with Engineering, Product, and Data Science teams to identify data gaps, define requirements, and deliver data products that directly enable experimentation, ad hoc analysis, and business metric optimization. Develop scalable abstractions and frameworks (UDFs, Python packages, internal data apps) that multiply the efficiency of other data teams and reduce time-to-insight across the organization. Design and deliver dashboards and visualization layers using tools like Looker or Tableau, translating complex data into clear, actionable views for cross-functional stakeholders. Required Skills and Experience: 5+ years in analytics engineering or data engineering with demonstrated expertise in designing modular data models and building production ETL/ELT pipelines using dbt, Airflow, or similar. Advanced SQL proficiency for complex transformations and query optimization, plus intermediate-to-advanced Python for scripting, automation, and building scalable frameworks (OOP experience preferred). Production experience with modern data warehouse architectures (Snowflake, Databricks) including performance tuning, data quality monitoring, and version-controlled development workflows (GitHub, CI/CD). Proven track record delivering data solutions that generated measurable business impact, with the ability to independently build domain expertise and communicate technical trade-offs to Product, Engineering, and business stakeholders. Experience with prompt engineering for LLMs (e.g., GPT), including designing and optimizing prompts for internal tooling and automation use cases. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Pay Transparency Notice: Base salary varies by location (see range below). Total compensation may also include equity and bonus eligibility, and benefits (medical, dental, vision, 401(k)). Annual base salary range (excluding equity and bonus): $180,370 — $212,200 USD Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>greenhouse|coinbase|8009392</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>coinbase</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>8009392</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist, CX Analytics</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Remote - USA</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>1</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>https://www.coinbase.com/careers/positions/8009392?gh_jid=8009392</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . As a Senior Data Scientist on the CX Consumer Analytics team, you will serve as the foundational link between CX operations and top-line financial impact, owning the revenue calibration models, experimentation frameworks, and behavioral intelligence that connect every customer support interaction to Coinbase's asset accumulation flywheel. You will partner closely with CX Analytics Engineers, Program Managers, and Product teams to translate complex operational and behavioral data into defensible, executive-ready insights that drive measurable improvements in retention, product adoption, and automation quality. What you'll do: Own and evolve CX's Downstream Impact of Support (DSI) revenue calibration models, translating support interaction data into quantified revenue signals. Design and execute causal inference frameworks and experiments to measure the incremental impact of CX programs (Concierge, Proactive Outreach, automation interventions) on customer retention and product engagement. Build and maintain LLM-powered classification pipelines for CX contact taxonomy, customer friction detection, and issue attribution, partnering with Analytics Engineers to productionize models into CX's governed Source of Truth infrastructure. Partner with CX Program Managers and Product teams to define segmentation models and behavioral signals that enable personalized experiences and improve business outcomes. Maintain a high bar for statistical rigor across CX's analytics function, ensuring experimentation, causal analyses, and model outputs meet the standards required for executive reporting and regulatory defensibility. Required Skills and Experience: A BA/BS in a quantitative field (e.g., Statistics, Mathematics, Computer Science, Economics) with 5+ years of relevant experience, or a PhD in a quantitative field with 3+ years of relevant experience. Demonstrated experience building revenue attribution or causal impact models and driving data science projects through ambiguous problem spaces in a consumer-facing or operational analytics context. Practical expertise applying statistical concepts including A/B testing, causal inference, and ML to real-world business problems, with a high bar for production-grade accuracy and evaluation rigor. Experience designing and deploying LLM-based classification or NLP pipelines for operational or customer-facing use cases. Ability to influence cross-functional stakeholders by synthesizing complex model outputs into clear, actionable narratives for executive and product audiences. Demonstrates the ability to responsibly use generative AI tools and copilots (e.g., LibreChat, Gemini, Glean) in daily workflows, continuously learn as tools evolve, and apply human‑in‑the‑loop practices to deliver business‑ready outputs and drive measurable improvements in efficiency, cost, and quality. Pay Transparency Notice: Base salary varies by location (see range below). Total compensation may also include equity and bonus eligibility, and benefits (medical, dental, vision, 401(k)). Annual base salary range (excluding equity and bonus): $180,370 — $212,000 USD Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>greenhouse|coinbase|7739592</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>coinbase</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>7739592</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Remote - India</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
-        <v>1</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>https://www.coinbase.com/careers/positions/7739592?gh_jid=7739592</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . The CX Intelligence team is part of Coinbase’s Enterprise Applications and Architecture org and builds the customer-facing and internal CX experiences that connect the Help Center, chatbots (CBCB), and agent workflows. The team owns the multi-agent platform which powers coinbase chat, Help Center and agent tooling surfaces, partnering closely with Conversation Design, CX, and other Engg teams to deliver secure, compliant, and scalable AI-powered support. Our work provides the trusted and accurate automated and agent-assisted experiences—helping customers get answers faster while enabling human agents to resolve cases more effectively. We are hiring an IC5 Machine Learning Engineer to drive the evolution of our conversational ecosystem by building a seamless hybrid vendor-internal chatbot experience. You will lead the design and implementation of a sophisticated unified orchestration layer that coordinates interactions between vendor AI, internal multi-agent systems, and human participants. This role is pivotal in managing complex state transitions, context sharing, and intent routing across a distributed environment. You’ll thrive here if you enjoy high ownership, architecting complex hand-off logic between disparate LLM frameworks, and building reliable AI-enabled products that are fast, measurable, and scalable. What you'll do: Architect and deploy the orchestration layer that manages state transitions, context sharing, and intent routing across vendor and internal LLM frameworks in a distributed conversational environment. Build production-grade Python services that bridge advanced ML/AI research with reliable, measurable customer-facing products. Lead end-to-end project execution for complex ML initiatives, managing priorities, technical trade-offs, and cross-functional dependencies from design through delivery. Establish best practices for system design, coding standards, and AI/ML development workflows across the team. Mentor engineers on architectural integrity and modern AI/ML patterns, raising the technical bar for the broader team. Conduct design reviews to ensure every feature meets Coinbase's standards for security, scalability, and performance. Required Skills and Experience: 5+ years of professional experience in machine learning and software engineering, with a track record of shipping production-grade ML services at scale. Hands-on expertise building with modern AI architectures (LLMs, deep learning) and the generative AI ecosystem, including frameworks such as LangGraph, LangSmith, Google ADK, Vertex AI, or AWS Bedrock. Deep proficiency in Python with demonstrated ability to write clean, maintainable, highly-tested production code. Specialized knowledge in at least one domain: NLP, information retrieval, computer vision, or advanced statistical modeling. Proven ability to write technical design documents and present ML system architectures to cross-functional stakeholders, translating complex technical concepts for non-technical audiences. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Demonstrates the ability to responsibly use generative AI tools and copilots (e.g., LibreChat, Gemini, Glean) in daily workflows, continuously learn as tools evolve, and apply human‑in‑the‑loop practices to deliver business‑ready outputs and drive measurable improvements in efficiency, cost, and quality. Pay Transparency Notice: The target annual base salary for this position can range as detailed below. Total compensation may also include equity and bonus eligibility and benefits (including medical, dental, and vision). Annual base salary range (excluding equity and bonus): ₹6,612,600 — ₹6,612,600 INR Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
-        </is>
-      </c>
-      <c r="L66" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>greenhouse|coinbase|8008569</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>coinbase</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>8008569</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer, CX Intelligence</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Remote - Brazil</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
-        <v>1</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>https://www.coinbase.com/careers/positions/8008569?gh_jid=8008569</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . As a Machine Learning Engineer on the CX Intelligence team within Enterprise Applications and Architecture, you'll build the AI-powered conversational systems that connect Coinbase's Help Center, chatbots, and agent workflows. The team owns the multi-agent platform powering Coinbase Chat and agent tooling, partnering with Conversation Design, CX, and Engineering to deliver secure, scalable automated support. You'll lead the design and implementation of a unified orchestration layer that coordinates interactions between vendor AI, internal multi-agent systems, and human participants, directly improving how millions of customers get help. What you'll do: Architect and deploy the orchestration layer that manages state transitions, context sharing, and intent routing across vendor and internal LLM frameworks in a distributed conversational environment. Build production-grade Python services that bridge advanced ML/AI research with reliable, measurable customer-facing products. Lead end-to-end project execution for complex ML initiatives, managing priorities, technical trade-offs, and cross-functional dependencies from design through delivery. Establish best practices for system design, coding standards, and AI/ML development workflows across the team. Mentor engineers on architectural integrity and modern AI/ML patterns, raising the technical bar for the broader team. Conduct design reviews to ensure every feature meets Coinbase's standards for security, scalability, and performance. Required Skills and Experience: 5+ years of professional experience in machine learning and software engineering, with a track record of shipping production-grade ML services at scale. Hands-on expertise building with modern AI architectures (LLMs, deep learning) and the generative AI ecosystem, including frameworks such as LangGraph, LangSmith, Google ADK, Vertex AI, or AWS Bedrock. Deep proficiency in Python with demonstrated ability to write clean, maintainable, highly-tested production code. Specialized knowledge in at least one domain: NLP, information retrieval, computer vision, or advanced statistical modeling. Proven ability to write technical design documents and present ML system architectures to cross-functional stakeholders, translating complex technical concepts for non-technical audiences. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Pay Transparency Notice: The target annual base salary for this position can range as detailed below. Total compensation may also include equity and bonus eligibility and benefits (including medical, dental, and vision). Annual base salary range (excluding equity and bonus): R$455.500 — R$455.500 BRL Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>greenhouse|coinbase|8008047</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>coinbase</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>8008047</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Senior Program Manager, Contracts &amp; Analytics</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Remote - USA</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
-        <v>1</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>https://www.coinbase.com/careers/positions/8008047?gh_jid=8008047</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . As a Senior Program Manager, Contracts &amp; Analytics, you'll join Coinbase's Legal Operations team to own the strategic direction, in-house build roadmap, and ongoing optimization of our Contract Lifecycle Management (CLM) ecosystem. This role goes beyond configuration - you'll define what gets built, set the technical vision for contracting workflows, and drive AI enablement across the team. You'll serve as a strategic partner to Institutional Sales, Enterprise Architecture, and Engineering, ensuring Coinbase's contracting infrastructure scales with the business and delivers measurable speed, compliance, and insight improvements. What you'll do: Own the CLM technology roadmap and backlog, setting strategic direction for what to build, integrate, or optimize across Ironclad, Evisort, Salesforce, and emerging tools, and translating that vision into a prioritized delivery plan. Lead in-house builds and workflow development that extend beyond standard SaaS configuration, partnering with Enterprise Architecture and Engineering to design scalable, integrated contracting solutions. Drive AI enablement for the Legal Operations team by identifying high-impact automation opportunities, standing up proof of concepts (e.g., N8N, Workato, Claude, Glean), and facilitating trainings, office hours, and adoption programs that raise the team's AI fluency. Develop and manage the comprehensive contracts reporting framework and system of record for all agreements, including data extraction, metadata integrity, and data models that surface actionable insights to Institutional Sales and Legal leadership. Communicate roadmap enhancements, program outcomes, and strategic recommendations to senior stakeholders, ensuring cross-functional alignment on contracting priorities and technology investments. Lead large, cross-functional contracts initiatives end-to-end, managing dependencies across Legal, Sales, Engineering, and Compliance, and delivering on time and within scope. Required Skills and Experience: 8+ years of program or project management experience within Legal Operations, contract management, or a technology-driven operations function, with a track record of setting strategic direction for tooling and workflows, not just executing on them. Demonstrated experience owning a technology roadmap and backlog, including prioritizing build-vs-buy decisions, scoping in-house development work, and partnering with engineering and architecture teams to deliver integrated solutions. Expert-level, hands-on experience with Contract Lifecycle Management (CLM) systems (Ironclad required), including workflow design, template management, reporting, and integration planning with platforms like Salesforce. Proven ability to drive AI and automation adoption within a team, including evaluating tools, building proof of concepts, and leading enablement programs that result in measurable workflow improvements. Working knowledge of legal technology and AI-driven contract review tools (e.g., Evisort), with experience in data extraction, metadata management, and building reporting frameworks that serve as the system of record for agreements. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Postion ID: P77368 #LI-Remote Pay Transparency Notice: Base salary varies by location (see range below). Total compensation may also include equity and bonus eligibility, and benefits (medical, dental, vision, 401(k)). Annual base salary range (excluding equity and bonus): $148,835 — $175,100 USD Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
-        </is>
-      </c>
-      <c r="L68" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>greenhouse|coinbase|7891045</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>coinbase</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>7891045</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Staff Machine Learning Engineer(Platform - Identity)</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Remote - USA</t>
-        </is>
-      </c>
-      <c r="H69" t="n">
-        <v>1</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>https://www.coinbase.com/careers/positions/7891045?gh_jid=7891045</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . Staff Machine Learning Engineer, Identity Verification As a Staff Machine Learning Engineer on the Identity Verification team within the Platform group, you'll own the ML systems that determine whether a person, document, and capture session are legitimate. Every signup, account recovery, and high-risk action at Coinbase depends on these models. You'll lead the technical strategy for IDV ML end-to-end, from architecture through production enforcement, protecting the integrity of millions of accounts. What you'll do: Own the full IDV ML stack, including document authenticity models, 1:1 and 1:N face-match, liveness detection, presentation-attack detection, and deepfake/injection detection from feature pipeline through threshold tuning and production enforcement. Build identity-graph systems using GNNs that cluster accounts sharing biometric, device, and document signals to detect synthetic-identity rings and coordinated fraud at onboarding. Develop behavioral and device-intelligence models for capture-session anomaly detection, bot-vs-human classification, and device-fingerprint-based risk scoring at real-time latency. Drive vendor ML strategy by benchmarking external models against a Coinbase-owned evaluation set, designing dynamic routing logic across providers and geographies, and building the in-house evaluation layer that catches regressions before they reach users. Lead and mentor senior and mid-level engineers in the pod while partnering with ML Platform and Risk ML teams to align cross-company ML system design. Required Skills and Experience: 8+ years deploying production ML systems at scale, with proven technical leadership owning cross-team ML architecture from design through production. Domain experience in identity verification, biometrics, or account integrity with deep applied ML in at least two of: computer vision/biometrics, GNNs, sequence models, or NLP/LLMs. Expert-level Python with production experience in TensorFlow or PyTorch, including model training, evaluation, and serving infrastructure. Track record translating KYC/AML requirements and fraud trends into ML roadmaps and communicating trade-offs to Product, Compliance, Risk, and Security stakeholders. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Pay Transparency Notice: Base salary varies by location (see range below). Total compensation may also include equity and bonus eligibility, and benefits (medical, dental, vision, 401(k)). Annual base salary range (excluding equity and bonus): $218,025 — $256,500 USD Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
-        </is>
-      </c>
-      <c r="L69" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>greenhouse|coinbase|8002967</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>coinbase</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>8002967</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Staff ML Risk Analyst</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Remote - USA</t>
-        </is>
-      </c>
-      <c r="H70" t="n">
-        <v>1</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>https://www.coinbase.com/careers/positions/8002967?gh_jid=8002967</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . As a Staff ML Risk Analyst on the Growth &amp; Risk team within the Consumer &amp; Business group, you'll sit at the intersection of fraud intelligence and machine learning infrastructure, defining how we identify, model, and respond to sophisticated fraud at scale. Fraud at Coinbase is fast-evolving, with professional, adaptive counterparties that outpace any human response team. You'll build and shape the ML-powered, automated solutions that detect and prevent account takeover (ATO) and scam activity before it reaches our users, setting the technical direction for the ML Analytics function within Growth &amp; Risk. What you'll do: Define the ML data and feature strategy for fraud detection, determining what data needs to enter our systems so models can take intelligent, high-accuracy action on the small fraction of traffic where intervention matters most. Own the end-to-end feature engineering pipeline, identifying, building, validating, and promoting features that drive measurable improvements in ATO and scam ML performance. Diagnose gaps between current tooling infrastructure and the solutions needed, driving the roadmap to close them by applying deep knowledge of how the ML industry has evolved architecturally. Partner with Machine Learning Engineers to translate analytical insights into production-ready ML systems, ensuring models are instrumented, monitored, and continuously improved. Mentor junior team members across the ML Analytics function, defining the technical approach and translating direction into execution. Partner cross-functionally with Product Managers and Risk Analysts to surface fraud signals and translate ML findings into business-impacting decisions. Required Skills and Experience: 8+ years of hands-on experience in machine learning analytics, data science, or a related technical field, with meaningful experience applied to risk, fraud, or payments problems. Practitioner-level proficiency in Spark, Python, and big data ML as a core working stack, with demonstrated ability to operate beyond SQL and rule-based approaches. Proven experience in feature engineering for ML models, including identifying signals, building pipelines, and validating feature quality at scale. Working knowledge of the ML infrastructure landscape evolution, from Hadoop-era big data through modern feature stores (e.g., Tecton, Feast), with the ability to apply that context to close infrastructure gaps. Demonstrated ability to optimize ML systems for sensitivity and accuracy on high-stakes, low-volume fraud traffic rather than broad-coverage, high-volume use cases. Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Pay Transparency Notice: Base salary varies by location (see range below). Total compensation may also include equity and bonus eligibility, and benefits (medical, dental, vision, 401(k)). Annual base salary range (excluding equity and bonus): $193,970 — $228,200 USD Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
-        </is>
-      </c>
-      <c r="L70" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>greenhouse|coinbase|8024877</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>coinbase</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>8024877</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Technical Program Manager, GFCO Analytics</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Remote - USA</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>1</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>https://www.coinbase.com/careers/positions/8024877?gh_jid=8024877</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Ready to do the most impactful work of your career? At Coinbase , we are uncompromising on our mission to increase economic freedom. The bar is high, the environment is intense, and we like it that way. This isn't a place for complacency, it’s a place to be pushed past your perceived limits. If you're ready to build the future of finance alongside people who refuse to settle for "good enough," you belong here. Coinbase is a remote-first, but not remote-only company. Expect to get together quarterly for intense in-person working sessions called “surges.” learn more about working at Coinbase . As a Technical Program Manager on the GFCO Analytics Engineering team, you'll own the roadmap and execution for the data models, metrics, and dashboards that power Customer Experience and Compliance Operations at Coinbase. This team combines deep domain expertise in regulated operations with modern data engineering (Snowflake, Airflow, Superset/Looker, and AI tooling) to deliver trusted, self-serve data products that drive faster decisions and stronger customer outcomes. You'll distill requests from 15+ cross-functional teams, prioritize work based on impact and regulatory need, and create the operational leverage that lets analytics engineers focus on building rather than managing process. What You'll Do: Own the CX Analytics Engineering roadmap, distilling requests from Operations, Compliance, Risk, WFM, BizOps, and Product teams into a prioritized backlog scoped by impact, regulatory urgency, and team capacity Drive program execution across data model builds, pipeline development, dashboard delivery, and regulatory reporting workstreams, holding the team accountable to timelines and quality standards Build and automate project management processes, reducing operational overhead so analytics engineers spend more time building data products and less time on coordination Partner with CX Operations leadership, Compliance, and Data/Platform Engineering to resolve pipeline dependencies, align on shared data models, and ensure regulatory reporting accuracy Implement testing, monitoring, and documentation standards (data contracts, alerting, quality checks) that reduce ad-hoc firefighting and build stakeholder trust in CX data products Leverage AI-assisted workflows and tooling to compress speed-to-insight, automate reporting, and scale the team's impact without growing headcount linearly with business complexity Required Skills and Experience: 7+ years of experience in technical program management, with at least 3 years supporting data engineering, analytics, or data platform teams in a regulated environment (fintech, financial services, or crypto) Proven track record owning and prioritizing a technical roadmap across multiple concurrent workstreams, balancing competing stakeholder needs with engineering capacity and regulatory requirements Fluency with modern data stack components (e.g., Snowflake, Airflow, Looker/Superset, dbt) and the ability to engage technically on data modeling, pipeline architecture, and data quality frameworks Demonstrated ability to create operational leverage through process automation, tooling improvements, and structured program management that frees engineering teams to focus on high-value delivery Experience driving alignment across 10+ cross-functional stakeholders (Operations, Compliance, Risk, Product, Engineering) where ownership is distributed and trade-offs must be actively managed Utilizes generative AI responsibly, maintaining human oversight to deliver business-ready outputs and drive measurable improvements in workflow efficiency, cost, and quality. Pay Transparency Notice: Base salary varies by location (see range below). Total compensation may also include equity and bonus eligibility, and benefits (medical, dental, vision, 401(k)). Annual base salary range (excluding equity and bonus): $148,835 — $175,100 USD Application Limit: Candidates may submit a maximum of 3 applications within a 6-month period. Equal Opportunity Employer: Coinbase is an Equal Opportunity Employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, protected veteran status, or genetic information. Applicants with criminal histories will be considered consistent with applicable federal, state, and local laws. US Applicants: View Employee Rights , Know Your Rights , and E-Verify Notice of Participation. Accommodations: If you are an individual with a disability who needs a reasonable accommodation, email us your request and contact info at accommodations[at]coinbase.com. Need screen reading technology? Click here to download a free compatible screen reader and view the tutorial . Data Privacy &amp; Arbitration: By submitting your application, you agree to our Candidate Privacy Notice . US applicants: By submitting your application, you agree to Arbitration of Disputes . AI Disclosure: Coinbase is piloting an AI tool based on machine learning technologies to conduct initial screening interviews to qualified applicants. The tool simulates realistic interview scenarios and engages in dynamic conversation. Coinbase is also piloting an AI interview intelligence platform to transcribe and summarize interview notes, allowing our interviewers to fully focus on you as the candidate. Coinbase will not use AI to make decisions impacting employment.</t>
-        </is>
-      </c>
-      <c r="L71" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>greenhouse|anthropic|5198108008</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>anthropic</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>5198108008</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Research Engineer, Machine Learning (RL Velocity)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Remote-Friendly (Travel-Required) | San Francisco, CA | New York City, NY</t>
-        </is>
-      </c>
-      <c r="H72" t="n">
-        <v>1</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5198108008</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>About Anthropic Anthropic’s mission is to create reliable, interpretable, and steerable AI systems. We want AI to be safe and beneficial for our users and for society as a whole. Our team is a quickly growing group of committed researchers, engineers, policy experts, and business leaders working together to build beneficial AI systems. About the role The RL Velocity team owns the efficiency and reliability of our RL Science stack - the infrastructure, tooling, and systems that let researchers iterate quickly on training runs. As a Research Engineer on the team, you'll build and improve the core platform that underpins how we do RL at Anthropic, removing bottlenecks that slow down research and making it easier for the broader org to ship better models faster. This is high-leverage work: small improvements to velocity compound across every researcher and every run. Responsibilities Build and improve the RL training infrastructure that researchers depend on day-to-day Identify and remove bottlenecks across the RL stack: debugging, profiling, and rearchitecting where needed Partner closely with researchers and with adjacent engineering teams (inference, sandboxing, and many more) to understand pain points and ship tooling that makes them faster Own the reliability and performance of research runs end-to-end Contribute to design decisions that shape how Anthropic does RL at scale You may be a good fit if you Have strong software engineering fundamentals and a track record of building performant, reliable systems Have worked on ML infrastructure, distributed systems, or research tooling Care about enabling other people's work and find leverage through platforms rather than individual experiments Are comfortable operating across the stack, from low-level performance work to RL algorithms Have a bias toward shipping and iterating quickly, with a mix of high agency and low ego Strong candidates may also have Experience with large-scale distributed training (RL, pre-training, or post-training) Familiarity with JAX, PyTorch, or similar ML frameworks A track record of operating at the edge of research and infra in a fast-moving environment Deadline to apply: None. Applications will be reviewed on a rolling basis. The annual compensation range for this role is listed below. For sales roles, the range provided is the role’s On Target Earnings ("OTE") range, meaning that the range includes both the sales commissions/sales bonuses target and annual base salary for the role. Annual Salary: $500,000 — $850,000 USD Logistics Minimum education: Bachelor’s degree or an equivalent combination of education, training, and/or experience Required field of study: A field relevant to the role as demonstrated through coursework, training, or professional experience Minimum years of experience: Years of experience required will correlate with the internal job level requirements for the position Location-based hybrid policy: Currently, we expect all staff to be in one of our offices at least 25% of the time. However, some roles may require more time in our offices. Visa sponsorship: We do sponsor visas! However, we aren't able to successfully sponsor visas for every role and every candidate. But if we make you an offer, we will make every reasonable effort to get you a visa, and we retain an immigration lawyer to help with this. We encourage you to apply even if you do not believe you meet every single qualification. Not all strong candidates will meet every single qualification as listed. Research shows that people who identify as being from underrepresented groups are more prone to experiencing imposter syndrome and doubting the strength of their candidacy, so we urge you not to exclude yourself prematurely and to submit an application if you're interested in this work. We think AI systems like the ones we're building have enormous social and ethical implications. We think this makes representation even more important, and we strive to include a range of diverse perspectives on our team. Your safety matters to us. To protect yourself from potential scams, remember that Anthropic recruiters only contact you from @anthropic.com email addresses. In some cases, we may partner with vetted recruiting agencies who will identify themselves as working on behalf of Anthropic. Be cautious of emails from other domains. Legitimate Anthropic recruiters will never ask for money, fees, or banking information before your first day. If you're ever unsure about a communication, don't click any links—visit anthropic.com/careers directly for confirmed position openings. How we're different We believe that the highest-impact AI research will be big science. At Anthropic we work as a single cohesive team on just a few large-scale research efforts. And we value impact — advancing our long-term goals of steerable, trustworthy AI — rather than work on smaller and more specific puzzles. We view AI research as an empirical science, which has as much in common with physics and biology as with traditional efforts in computer science. We're an extremely collaborative group, and we host frequent research discussions to ensure that we are pursuing the highest-impact work at any given time. As such, we greatly value communication skills. The easiest way to understand our research directions is to read our recent research. This research continues many of the directions our team worked on prior to Anthropic, including: GPT-3, Circuit-Based Interpretability, Multimodal Neurons, Scaling Laws, AI &amp; Compute, Concrete Problems in AI Safety, and Learning from Human Preferences. Come work with us! Anthropic is a public benefit corporation headquartered in San Francisco. We offer competitive compensation and benefits, optional equity donation matching, generous vacation and parental leave, flexible working hours, and a lovely office space in which to collaborate with colleagues. Guidance on Candidates' AI Usage: Learn about our policy for using AI in our application process.</t>
-        </is>
-      </c>
-      <c r="L72" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>greenhouse|intercom|8030046</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Intercom</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>intercom</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>8030046</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Director, Product Analytics</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Berlin, Germany; Dublin, Ireland; EMEA, Remote; London, England</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>1</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/intercom/jobs/8030046</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Fin is the AI Customer Agent company on a mission to help businesses provide perfect customer experiences. Our AI Agent Fin is the highest-performing AI Customer Agent on the market today, enabling businesses to deliver impeccable, always-on customer support across the customer journey – from service, to sales, to ecommerce. Powered by our own AI models, Fin resolves complex customer issues end-to-end across every channel, with minimal set-up and integration. Fin can also be combined with our natively integrated Intercom help desk for one single system that is designed to meet the needs of modern day support teams. Founded in 2011, Fin became one of the fastest growing companies and remains one of the largest private software companies in the world with nearly 30,000 global businesses using our products to transform their customer support. Driven by our core values, we push boundaries, build with speed and intensity, and relentlessly deliver incredible value to our customers. Product Data Science Leader, Fin What makes this role different This is not a classic experimentation-first product data science leadership role. Fin is a fast-moving, ambiguous, B2B AI-native product company. The role is less about owning a neat experimentation roadmap and more about helping shape direction in an environment where product bets are evolving quickly, the operating model is constantly changing, and decisions often need to be made before the data is complete. This person will not be successful if they wait to be asked for analysis. We need someone who creates momentum, brings clarity to messy problems, and helps leaders decide what matters, where to focus, and what should change. This is a highly consultative, influence-heavy leadership role. It sits at the intersection of product strategy, product analytics, customer outcomes, go-to-market signals, technical feasibility, and organizational design. Success depends on building trust and traction with product, engineering, design, research, sales, and executive stakeholders, often without relying on formal authority alone. The role is as much about shaping the system around product data science as it is about analytical depth. A major part of the job is creating the conditions for the function to be effective: improving how decisions get made, clarifying where data science should engage, helping define interfaces with adjacent functions, and ensuring insights actually influence outcomes. Vision for Product Data Science at Fin This role is not only about leading the current team well. It is also about helping define what product data science should become in an AI-native product organization. Fin is building zero-to-one products in an environment where the nature of the work is constantly shifting. As a result, the shape of product data science cannot be static or tied too closely to a traditional experimentation-and-dashboards model. We expect this leader to help define the future makeup of the function. That includes understanding where we need data scientists who are closer to engineers and builders, where we need people who operate more like researchers, and where deep statistical and analytical rigor should remain central. This person should bring a clear point of view on what an AI-native product data science function looks like, how AI should change the practice of analysis, and what capabilities, foundations, and operating model are required for the function to have the most impact over time. They should help define: the right capability mix for the team over time where foundations work belongs and how it should be prioritized how AI can increase leverage in analysis without lowering quality or rigor how product data science should evolve as Fin evolves. What this role is really about Bringing clarity to ambiguous product bets with data and insights Helping shape strategy in fast-moving B2B AI product areas Pushing for better decisions, not just better analysis Identifying product and performance gaps early; Influencing where the organization should act Creating traction for product data science where the model is still evolving Designing how product data science should work, not just delivering within the current setup Redirecting effort toward the highest-leverage problems Leading with judgment, influence, credibility, and conviction What you’ll do Help product and company leaders make better decisions on where Fin should focus Bring structure and judgment to ambiguous product, customer, and performance questions Identify what is and is not working in the product, and where intervention is most needed Shape early product direction, especially in zero-to-one and fast-evolving areas Define where product data science should engage deeply versus where lighter support is sufficient Define a vision for what product data science should look like in an AI-native product organization Shape how AI is used in analysis, insight generation, and decision support, while maintaining a high bar for rigor and judgment Improve visibility into product performance, opportunity size, and business impact Partner across product, engineering, design, research, sales, and leadership to connect product signals with customer and commercial outcomes Build trust with senior stakeholders and challenge weak logic or fuzzy thinking when needed Help design the operating model for product data science in Fin, including interfaces with analytics engineering, research, and go-to-market teams Ensure the function builds the right foundations for evaluating and improving zero-to-one AI products Coach and raise the bar for product data science work through prioritization, judgment, and leadership presence Ensure scarce data science capacity is focused on the most important problems, not just the loudest requests What we’re looking for Strong product data science leadership experience in complex product environments Track record of shaping strategy, not just supporting execution Comfort operating in ambiguity and making high-quality judgment calls with imperfect data Ability to influence senior stakeholders and challenge constructively when needed Strong analytical depth and technical skills A strong point of view on what product data science should look like in an AI-native company Experience evolving team shape and capability mix in response to changing product and organizational needs Ability to distinguish when the work calls for builder-type data scientists, research-oriented profiles, or deeper statistical specialization Strong judgment on how AI should and should not be used in analytical and data science work Excellent prioritization instincts and ability to identify high-leverage work Experience working across product, engineering, design, research, and commercial stakeholders Ability to translate across functions and connect product decisions to customer and business outcomes Strong leadership presence: credibility, judgment, communication, and follow-through Experience building or evolving operating models, team scope, or cross-functional ways of working Ideally, experience in AI-native, SaaS, or fast-moving B2B product contexts What success looks like Product and R&amp;D leaders actively rely on this person to shape priorities Data science is involved early enough to influence direction, not just validate decisions late Teams have a clearer view of product performance, opportunity size, and where intervention is needed Product data science effort is focused on the highest-leverage opportunities The interfaces between product data science and adjacent functions are clearer and more effective The function becomes embedded in how critical Fin decisions get made The overall quality of decision-making rises around the teams this person supports The team evolves toward the right mix of capabilities for an AI-native product environment AI is used to increase leverage in analysis and decision support without lowering rigor Why this role matters now Fin is operating in a space where product ships incredibly fast, decisions move quickly, ambiguity is high, and the organization needs stronger clarity on where product data science can have the most impact. We need a leader who can help shape the agenda, improve the system and operating model, and ensure product data science meaningfully changes outcomes. Benefits We are a well treated bunch, with awesome benefits! If there’s something important to you that’s not on this list, talk to us! Competitive salary and equity in a fast-growing start-up. We serve lunch every weekday, plus a variety of snack foods and a fully stocked kitchen. Regular compensation reviews - we reward great work! Pension scheme &amp; match up to 4%. Peace of mind with life assurance, as well as comprehensive health and dental insurance for you and your dependents. Flexible paid time off policy. Paid maternity leave, as well as 6 weeks paternity leave for fathers, to let you spend valuable time with your loved ones. If you’re cycling, we’ve got you covered on the Cycle-to-Work Scheme. With secure bike storage too. MacBooks are our standard, but we also offer Windows for certain roles when needed. #LI-Hybrid Policies Fin has a hybrid working policy. We believe that working in person helps us stay connected, collaborate easier and create a great culture while still providing flexibility to work from home. We expect employees to be in the office at least three days per week. We have a radically open and accepting culture at Fin. We avoid spending time on divisive subjects to foster a safe and cohesive work environment for everyone. As an organization, our policy is to not advocate on behalf of the company or our employees on any social or political topics out of our internal or external communications. We respect personal opinion and expression on these topics on personal social platforms on personal time, and do not challenge or confront anyone for their views on non-work related topics. Our goal is to focus on doing incredible work to achieve our goals and unite the company through our core values . Fin values diversity and is committed to a policy of Equal Employment Opportunity. Fin will not discriminate against an applicant or employee on the basis of race, color, religion, creed, national origin, ancestry, sex, gender, age, physical or mental disability, veteran or military status, genetic information, sexual orientation, gender identity, gender expression, marital status, or any other legally recognized protected basis under federal, state, or local law.</t>
-        </is>
-      </c>
-      <c r="L73" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>greenhouse|hume ai|4816209008</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Hume AI</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>humeai</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>4816209008</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Backend &amp; Machine Learning</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>New York, New York, United States</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/humeai/jobs/4816209008</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Hume AI is seeking a talented senior software engineer with experience in backend services and ML infrastructure who is interested in working with our team to build state-of-the-art audio models and evaluation tools. Join us in the heart of New York City and contribute to our endeavor to ensure that AI is guided by human values, the most pivotal challenge (and opportunity) of the 21st century. About Us Hume AI is a Series B startup dedicated to building artificial intelligence that is directly optimized for human well-being. As the first company to release speech language models, we’re focused on expanding our research to encompass audio understanding models and evaluation platforms for enterprises. Our goal is to enable a future in which technology draws on an understanding of human emotional expression to better serve human goals. As part of our mission, we also conduct groundbreaking scientific research, publish in leading scientific journals like Nature , and support a non-profit, The Hume Initiative, that has released the first concrete ethical guidelines for empathic AI ( www.thehumeinitiative.org ). You can learn more about us on our website ( https://hume.ai/ ) and read about us in WIRED , Forbes , and Venturebeat . About the Role We are looking for an experienced and motivated senior engineer with experience in backend services and ML infrastructure. In this role you will help us integrate cutting edge AI models into services and toolkits for researchers and developers. You will work closely with research scientists and other engineers to build new capabilities into the Hume platform, and you will have the opportunity to take part in a wide range of engineering initiatives across backend applications, cloud infrastructure, and the ML lifecycle, including evaluation and deployment at scale. Requirements Expertise in the Python ecosystem and popular ML libraries and tools (e.g. PyTorch, JAX, TensorFlow, XGBoost, sklearn, pandas, numpy). Experience building and deploying models for inference services. Experience writing backend services in multiple languages (e.g. Kotlin, Go, Rust, Java, C++). Understanding of core ML concepts including model architecture, training, and evaluation. Expertise working with storage and compute on a cloud platform (e.g.Google Cloud, AWS). Excellent communication and collaboration skills. Bonus Familiarity with data engineering principles and/or building large-scale data pipelines. Familiarity with building and deploying LLM-integrated products. Experience working at the intersection of machine learning research and engineering. Understanding of modern deployment strategies utilizing cloud technologies. (e.g. blue/green, canary deployments, etc). Experience using service deployment tooling (e.g. Kubernetes, Helm, Docker, Argo). Application Note Please apply only to the position that best aligns with your qualifications. If you submit multiple applications or have applied within the past 6 months, only your initial submission will be considered. Annual Salary $180,000 — $250,000 USD</t>
-        </is>
-      </c>
-      <c r="L74" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>ashby|elevenlabs|e53c5be6-5c1a-4870-ad85-8397a1f201de</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>ashby</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>ElevenLabs</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>elevenlabs</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>e53c5be6-5c1a-4870-ad85-8397a1f201de</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="H75" t="n">
-        <v>1</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
           <t>https://jobs.ashbyhq.com/elevenlabs/e53c5be6-5c1a-4870-ad85-8397a1f201de</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>ABOUT ELEVENLABS
 ElevenLabs is an AI research and product company transforming how we interact with technology.
@@ -4614,58 +2494,58 @@
 #LI-Remote</t>
         </is>
       </c>
-      <c r="L75" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>ashby|deepgram|378e83b4-28c0-4b4e-8cf0-9355712bd06d</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Deepgram</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>deepgram</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>378e83b4-28c0-4b4e-8cf0-9355712bd06d</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Billing &amp; Analytics Software Engineer</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>USA | Remote</t>
         </is>
       </c>
-      <c r="H76" t="n">
-        <v>1</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/deepgram/378e83b4-28c0-4b4e-8cf0-9355712bd06d</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>COMPANY OVERVIEW
 Deepgram is the leading platform underpinning the emerging trillion-dollar Voice AI economy, providing real-time APIs for speech-to-text (STT), text-to-speech (TTS), and building production-grade voice agents at scale. More than 200,000 developers and 1,300+ organizations build voice offerings that are ‘Powered by Deepgram’, including Twilio, Cloudflare, Sierra, Decagon, Vapi, Daily, Cresta, Granola, and Jack in the Box. Deepgram’s voice-native foundation models are accessed through cloud APIs or as self-hosted and on-premises software, with unmatched accuracy, low latency, and cost efficiency. Backed by a recent Series C led by leading global investors and strategic partners, Deepgram has processed over 50,000 years of audio and transcribed more than 1 trillion words. There is no organization in the world that understands voice better than Deepgram.
@@ -4705,58 +2585,58 @@
 Deepgram’s growth is powered by a usage-based model where customers pay for what they consume. Every usage event, every invoice, every plan upgrade flows through the systems this role owns. As Billing &amp; Analytics Engineer, you’ll ensure that Deepgram gets paid accurately and on time, that customers have full visibility into their consumption, and that internal teams have the financial data they need to scale the business. By creating a dedicated billing engineering function, this role directly enables the Console and PLG teams to move faster on product innovation without billing complexity as a bottleneck.</t>
         </is>
       </c>
-      <c r="L76" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>ashby|deepgram|9a030b32-d671-43e0-a221-4653bb73ba29</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Deepgram</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>deepgram</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>9a030b32-d671-43e0-a221-4653bb73ba29</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Research Engineer, Machine Learning Systems</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>USA | Remote</t>
         </is>
       </c>
-      <c r="H77" t="n">
-        <v>1</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/deepgram/9a030b32-d671-43e0-a221-4653bb73ba29</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>COMPANY OVERVIEW
 Deepgram is the leading platform underpinning the emerging trillion-dollar Voice AI economy, providing real-time APIs for speech-to-text (STT), text-to-speech (TTS), and building production-grade voice agents at scale. More than 200,000 developers and 1,300+ organizations build voice offerings that are ‘Powered by Deepgram’, including Twilio, Cloudflare, Sierra, Decagon, Vapi, Daily, Cresta, Granola, and Jack in the Box. Deepgram’s voice-native foundation models are accessed through cloud APIs or as self-hosted and on-premises software, with unmatched accuracy, low latency, and cost efficiency. Backed by a recent Series C led by leading global investors and strategic partners, Deepgram has processed over 50,000 years of audio and transcribed more than 1 trillion words. There is no organization in the world that understands voice better than Deepgram.
@@ -4790,58 +2670,58 @@
 At Deepgram, you’ll help shape the future of human–machine communication. Our research culture prioritizes ownership, experimentation, and real-world impact. As a Member of the Research Staff, you'll be empowered to build tools and systems that accelerate ML research and product deployment at scale.</t>
         </is>
       </c>
-      <c r="L77" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>ashby|n8n|edd9e287-262e-4fcb-8aa5-2067e6526efa</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>n8n</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>n8n</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>edd9e287-262e-4fcb-8aa5-2067e6526efa</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Product Data Analyst</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H78" t="n">
-        <v>1</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/n8n/edd9e287-262e-4fcb-8aa5-2067e6526efa</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>The AI orchestration of your wildest imagination.
 n8n is the open workflow orchestration platform built for the new era of AI. We give technical teams the freedom of code with the speed of no-code, so they can automate faster, smarter, and without limits. Backed by a fiercely inventive community and 500+ builder-approved integrations, we’re changing the way people bring systems together and scale ideas for impact.
@@ -4924,114 +2804,114 @@
 * Country-specific details are provided in your contract.</t>
         </is>
       </c>
-      <c r="L78" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>greenhouse|boomi|5779584004</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Boomi</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>boomilp</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>5779584004</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Senior Data Engineer - Agentic AI Engineering</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>United States of America</t>
         </is>
       </c>
-      <c r="H79" t="n">
-        <v>1</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>https://boomi.com/boomi-jobs/?gh_jid=5779584004</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>About Boomi and What Makes Us Special Are you ready to work at a fast-growing company where you can make a difference? Boomi, the data activation company for AI, powers the agentic enterprise by bringing data to life across the business. The award-winning Boomi Enterprise Platform is the active data foundation that delivers essential agentic infrastructure enabling organizations to drive agentic transformation and harness the power of AI with secure, scalable connectivity. Trusted by over 30,000 customers and supported by a network of 800+ partners, Boomi helps organisations of all sizes achieve agility, efficiency, and innovation at scale. At Boomi, you’ll work with world-class people and industry-leading technology. We hire trailblazers with an entrepreneurial spirit who can solve challenging problems, make a real impact, and want to be part of building something big. If this sounds like a good fit for you, check out boomi.com or visit our Boomi Careers page to learn more. How You’ll Make An Impact As a Data Engineer at Boomi, you will architect the "paved road" for our AI initiatives. You will transition our "Customer Zero" prototypes from experimental code into robust, secure, and observable. You will be the bridge between cutting-edge AI research and enterprise-grade reliability, enabling the entire engineering organization to ship intelligent features faster and safer. We are seeking a highly skilled Data Engineer to join our Agentic AI Engineering Team. This role focuses on building and operating scalable, high-quality data infrastructure that powers agentic AI systems, including LLM-based agents, multi-agent workflows, and tool-using AI systems. You will play a critical role in enabling data-driven training, evaluation, memory, observability, and continuous improvement of intelligent agents. What You Will Do Architect and build scalable, secure, and observable data infrastructure to power LLM-based agents, multi-agent systems, and tool-using AI workflows. Design and operate robust batch and real-time data pipelines supporting embeddings, RAG systems, and agent memory frameworks. Develop and manage vector database solutions to enable low-latency retrieval and contextual intelligence for AI applications. Build data frameworks for training, evaluation, benchmarking, and continuous improvement of agentic AI systems. Implement strong data governance, quality controls, lineage tracking, and PII/security compliance across AI data platforms. Collaborate with AI/ML, platform, and DevOps teams to productionize experimental AI prototypes into enterprise-grade solutions. Optimize data systems for performance, scalability, reliability, and cost efficiency across cloud environments (AWS, Azure, or GCP). The Experience You Bring 5+ years of experience building and operating large-scale data platforms as a Data Engineer. Strong programming expertise in Python and SQL for developing scalable and efficient data solutions. Hands-on experience designing batch and real-time data pipelines, including streaming systems like Kafka or Kinesis. Experience with modern data platforms and cloud environments (AWS, Azure, or GCP), including tools like Snowflake. Strong understanding of LLM/AI data workflows, including embeddings, RAG pipelines, evaluation datasets, and vector databases (Pinecone, Milvus ). Experience with DataOps/MLOps tools such as Airflow, dbt, Lavender, and MLflow for orchestration and lifecycle management. Strong knowledge of data quality, governance, and security, including PII handling, access controls, lineage, and ensuring data reliability. Bonus Points If You Have Experience supporting agentic AI systems, multi-agent architectures, or tool-using AI agents. Familiarity with agent memory models, conversation histories, and reasoning trace storage. Experience with synthetic data generation and simulation frameworks. Exposure to prompt engineering workflows and prompt/version management. Experience optimizing data systems for low-latency AI workloads. Aren’t sure if you’re a match? We know that impostor syndrome and the confidence gap can prevent us from meeting spectacular candidates — so don’t hesitate to apply; you could be the perfect fit! Location Conshohocken, PA or Denver, CO (Preferred) Or US Remote Compensation and Benefits Boomi is committed to fair and equitable compensation practices. Base compensation for this position in our corporate headquarters in Conshohocken, PA ranges from $138,862 - $173,578. This position is remote-friendly and, as such, final compensation will be determined by various factors including the candidate’s knowledge, skills, experience, and geographic location. An overview of our benefits can be found here . #LI-ES1 Be Bold. Be You. Be Boomi. We take pride in our culture and core values and are committed to being a place where everyone can be their true, authentic self. Our team members are our most valuable resources, and we look for and encourage diversity in backgrounds, thoughts, life experiences, knowledge, and capabilities. All employment decisions are based on business needs, job requirements, and individual qualifications. Boomi strives to create an inclusive and accessible environment for candidates and employees. If you need accommodation during the application or interview process, please submit a request to talent@boomi.com . This inbox is strictly for accommodations, please do not send resumes or general inquiries.</t>
         </is>
       </c>
-      <c r="L79" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>ashby|cohere|3136a5a5-06fd-4c82-8b72-a43467e6b128</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Cohere</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>cohere</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>3136a5a5-06fd-4c82-8b72-a43467e6b128</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Member of Technical Staff, Modeling</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>London</t>
         </is>
       </c>
-      <c r="H80" t="n">
-        <v>1</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/cohere/3136a5a5-06fd-4c82-8b72-a43467e6b128</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>Who are we?
 Cohere is the leading security-first enterprise AI company. We build cutting-edge foundation AI models and end-to-end products that are designed to solve real-world business problems.
@@ -5074,58 +2954,58 @@
 We may use AI-enabled tools to screen and assess applicants against the criteria for this position. This helps our recruiters identify potentially qualified candidates, but it doesn't limit the applications our recruiters may review or consider.</t>
         </is>
       </c>
-      <c r="L80" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>ashby|cohere|39cab400-c976-41d9-9002-880ac6985b64</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Cohere</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>cohere</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>39cab400-c976-41d9-9002-880ac6985b64</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Lead Data Scientist</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H81" t="n">
-        <v>1</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/cohere/39cab400-c976-41d9-9002-880ac6985b64</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>Who are we?
 Cohere is the leading security-first enterprise AI company. We build cutting-edge foundation AI models and end-to-end products that are designed to solve real-world business problems.
@@ -5169,58 +3049,58 @@
 We may use AI-enabled tools to screen and assess applicants against the criteria for this position. This helps our recruiters identify potentially qualified candidates, but it doesn't limit the applications our recruiters may review or consider.</t>
         </is>
       </c>
-      <c r="L81" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>ashby|cohere|36d1f52f-8270-4652-adf5-5303a0ff341b</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Cohere</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>cohere</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>36d1f52f-8270-4652-adf5-5303a0ff341b</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Machine Learning Intern/Co-op  (Fall, 2026)</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="H82" t="n">
-        <v>1</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/cohere/36d1f52f-8270-4652-adf5-5303a0ff341b</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Who are we?
 Cohere is the leading security-first enterprise AI company. We build cutting-edge foundation AI models and end-to-end products that are designed to solve real-world business problems.
@@ -5270,58 +3150,58 @@
 We may use AI-enabled tools to screen and assess applicants against the criteria for this position. This helps our recruiters identify potentially qualified candidates, but it doesn't limit the applications our recruiters may review or consider.</t>
         </is>
       </c>
-      <c r="L82" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>ashby|cohere|582c4a60-14a2-49d5-b4d3-24c4ec50508d</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Cohere</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>cohere</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>582c4a60-14a2-49d5-b4d3-24c4ec50508d</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Senior Technical Program Manager, Machine Learning Infrastructure</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="H83" t="n">
-        <v>1</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" t="inlineStr">
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/cohere/582c4a60-14a2-49d5-b4d3-24c4ec50508d</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>Who are we?
 Cohere is the leading security-first enterprise AI company. We build cutting-edge foundation AI models and end-to-end products that are designed to solve real-world business problems.
@@ -5370,394 +3250,226 @@
 We may use AI-enabled tools to screen and assess applicants against the criteria for this position. This helps our recruiters identify potentially qualified candidates, but it doesn't limit the applications our recruiters may review or consider.</t>
         </is>
       </c>
-      <c r="L83" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>greenhouse|celonis|7725788003</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>celonis</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>7725788003</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Associate Value Engineer (AI-Driven Data Science &amp; Analytics) - Orbit Program</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>New York, US, New York</t>
         </is>
       </c>
-      <c r="H84" t="n">
-        <v>1</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" t="inlineStr">
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7725788003?gh_jid=7725788003</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Celonis is the global leader in Process Intelligence and the pioneer of Process Mining technology. As one of the world’s fastest-growing enterprise SaaS companies, we are changemakers pushing the boundaries of what’s possible. We invest heavily in advanced AI capabilities—specifically our Process Intelligence Graph—to turn data insights into immediate business action. We believe there is a massive opportunity to unlock global productivity and sustainability by placing intelligence at the core of every business process. Join our mission to make processes work for people, companies, and the planet. The Team: Global Value Engineering Center of Excellence Become an integral part of our international, diverse, and dynamic Global Value Engineering Center of Excellence. Our Value Engineers are trusted advisors who operate at the intersection of technology and business , partnering with sales and customers to develop compelling Celonis-powered solutions and prototypes that address critical business challenges. We foster a fast-paced, collaborative environment built on trust, continuous learning, and mutual growth through coaching and mentorship. The Role: Launch Your Enterprise Software Career Kickstart your career in enterprise software through our immersive 12-month Orbit Program . This program offers a unique blend of client engagements, dedicated mentorship, and a strong team culture where collaboration and shared success are paramount. You'll leverage your technical background to develop essential Value Engineering skills, build lasting client relationships, and establish yourself as a trusted advisor, paving the way for significant career growth within Celonis. The Orbit Program is structured into classes and cohorts , with start dates organized twice a year. You'll likely join a cohort with a summer start date (June/July) or a winter start date (January/February) , allowing you to grow and develop alongside your cohort peers. Your journey begins with comprehensive onboarding and enablement, followed by hands-on experience in customer engagements and targeted training. You will gain expertise in: Building and coding within the Celonis platform (SQL and PQL) Scoping business and technical requirements Effectively handling objections Developing industry domain knowledge Delivering impactful presentations and demos Understanding value selling and realization Managing customer accounts What You'll Do: Consult with customers using systems analysis to identify core business challenges and determine how Celonis can drive impactful solutions. Present the Celonis AI value proposition and vision to customers and align our solutions with their AI strategy. Prototype and develop AI solutions tailored to customer needs, including both traditional machine learning and LLM-based solutions . Execute proof projects showcasing the value of Celonis Process Intelligence in the context of our customers’ strategy, business initiatives, and challenges Develop and modify Celonis data models using SQL and analyses using PQL (Celonis proprietary language) to create compelling prototypes that address customer pain points. Lead proof-of-concept projects within the Celonis platform to demonstrate tangible value aligned with customer strategies and needs. Collaborate with customers and partners to design and build Celonis solutions that ensure a positive return on investment. Establish strong, trusted advisor relationships with customers through your technical expertise, product knowledge, and business acumen. Articulate and quantify strategic business value for customers, delivering impactful presentations to senior executives. Partner with the implementation services team to ensure successful value realization for customers. Identify opportunities for innovation and collaborate with Product &amp; Engineering teams to influence future product development. Contribute to the Global Value Engineering Center of Excellence by creating reusable collateral, best practices, and tools. What You Need: Bachelor’s degree in Business, Engineering, Data Analytics, Economics, Computer Science, Mathematics , or a related STEM field. Extensive internship experience or 1-3 years of full-time work experience. Hands-on experience with at least one of the following: SQL, Microsoft Power BI, Tableau, or another data analytics solution. A strong passion for technology, big data, and its transformative potential. Excellent analytical and creative problem-solving skills , with the ability to apply technology to business challenges. A customer-centric mindset with a focus on delivering value. The ability to build relationships with senior management and influence decision-making. Confidence in presenting to diverse audiences. A proactive approach to problem-solving, with a willingness to learn from mistakes. Curiosity, self-motivation, a commitment to continuous learning, and the desire to thrive in a fast-paced, high-growth environment. Strong organizational skills with the ability to prioritize and execute on deadlines. Excellent communication skills and fluency in English. Bonus Points: GPA of 3.6 or higher. Degree in Industrial Engineering or a similar field. Degrees combining technical (e.g., Computer Science, Data Science) and business (e.g., Economics, Marketing) skills. Experience with Python and Machine Learning. Customer-facing , customer success/service, or sales experience. Experience with Proof of Concept projects. Supply Chain process experience (Procurement, Order Management, Inventory Management, Production). Finance process experience (Accounts Payable, Accounts Receivable). Experience modeling ROI and TCO for business case justification. Experience with SAP and/or Oracle. Fluency in French and/or Spanish. Visa sponsorship is not offered for this role. The base salary range below is for the role in the specified location, based on a Full Time Schedule. Total compensation package will include base salary + bonus/commission + equity + benefits (health, dental, life, 401k, and paid time off). Please note that the base salary range is a guideline, and that the actual total compensation offer will be determined based on various factors, including, but not limited to, applicant's qualifications, skills, experiences, and location. The base salary range below is for the role in New York, based on a Full Time Schedule. $90,000 — $95,000 USD What Celonis can offer you: Pioneer Innovation: Work with the global leader in Process Mining and the Process Intelligence Graph to shape the future of AI-driven business operations. Ownership from Day 1: Every full-time "Celonaut" is an owner, receiving Restricted Stock Units (RSUs) and merit-based refresh grants. Unrivaled Family Support: Benefit from our inclusive parental leave policy—24 weeks of fully paid leave for primary carers and 12 weeks for supporting carers, available from your first day of employment. Work-Life Integration: Enjoy Unlimited PTO (in applicable regions) and generous PTO globally, as well as a flexible hybrid work model that balances remote focus with vibrant office collaboration. Continuous Growth: Elevate your skills through our 70-20-10 learning framework, mentorship programs, and access to a dedicated learning platform. Holistic Well-being: Prioritize your health with subsidized Wellhub memberships, mental health counseling, and dedicated "Wellness Weeks" that prioritize work/life balance. Drive Sustainability: Participate in annual Impact Days, where you receive paid time off to volunteer for community and environmental causes with your local office, or virtually. Global Inclusion &amp; Belonging: Find community through our Inclusion Think Tank and participate in our annual Inclusion Days, ensuring every voice is heard and valued. Value-Driven Impact: Join a mission-led organization where our core values—Live for Customer Value, The Best Team Wins, We Own It, and Earth Is Our Future—drive every decision. About Us: Celonis makes processes work — for people, companies, and the planet. Powered by process mining and AI, the Celonis Process Intelligence Platform integrates process data and business context to create a living digital twin of business operations. We enable thousands of companies worldwide to understand how their business actually runs and, together with their partners, build intelligent solutions that transform and continuously improve the way they operate — unlocking billions in value. Celonis is headquartered in Munich, Germany, and New York City, USA, with more than 20 offices worldwide. Get familiar with the Celonis Process Intelligence Platform by watching this video . Celonis Inclusion Statement: At Celonis, we believe our people make us who we are and that “The Best Team Wins”. We know that the best teams are made up of people who bring different perspectives to the table. And when everyone feels included, able to speak up and knows their voice is heard - that's when creativity and innovation happen. Your Privacy: Any information you submit to Celonis as part of your application will be processed in accordance with Celonis’ Accessibility and Candidate Notices By submitting this application, you confirm that you agree to the storing and processing of your personal data by Celonis as described in our Privacy Notice for the Application and Hiring Process . Please be aware of common job offer scams, impersonators and frauds. Learn more here .</t>
         </is>
       </c>
-      <c r="L84" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>greenhouse|celonis|7781716003</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>celonis</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>7781716003</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Associate Value Engineer (AI-Driven Data Science &amp; Analytics) - Orbit Program</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Raleigh, US, North Carolina</t>
         </is>
       </c>
-      <c r="H85" t="n">
-        <v>1</v>
-      </c>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7781716003?gh_jid=7781716003</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>Celonis is the global leader in Process Intelligence and the pioneer of Process Mining technology. As one of the world’s fastest-growing enterprise SaaS companies, we are changemakers pushing the boundaries of what’s possible. We invest heavily in advanced AI capabilities—specifically our Process Intelligence Graph—to turn data insights into immediate business action. We believe there is a massive opportunity to unlock global productivity and sustainability by placing intelligence at the core of every business process. Join our mission to make processes work for people, companies, and the planet. The Team: Global Value Engineering Center of Excellence Become an integral part of our international, diverse, and dynamic Global Value Engineering Center of Excellence. Our Value Engineers are trusted advisors who operate at the intersection of technology and business , partnering with sales and customers to develop compelling Celonis-powered solutions and prototypes that address critical business challenges. We foster a fast-paced, collaborative environment built on trust, continuous learning, and mutual growth through coaching and mentorship. The Role: Launch Your Enterprise Software Career Kickstart your career in enterprise software through our immersive 12-month Orbit Program . This program offers a unique blend of client engagements, dedicated mentorship, and a strong team culture where collaboration and shared success are paramount. You'll leverage your technical background to develop essential Value Engineering skills, build lasting client relationships, and establish yourself as a trusted advisor, paving the way for significant career growth within Celonis. Your journey begins with comprehensive onboarding and enablement, followed by hands-on experience in customer engagements and targeted training. You will gain expertise in: Building and coding within the Celonis platform (SQL and PQL) Scoping business and technical requirements Effectively handling objections Developing industry domain knowledge Delivering impactful presentations and demos Understanding value selling and realization Managing customer accounts What You'll Do: Consult with customers using systems analysis to identify core business challenges and determine how Celonis can drive impactful solutions. Present the Celonis AI value proposition and vision to customers and align our solutions with their AI strategy. Prototype and develop AI solutions tailored to customer needs, including both traditional machine learning and LLM-based solutions . Execute proof projects showcasing the value of Celonis Process Intelligence in the context of our customers’ strategy, business initiatives, and challenges Develop and modify Celonis data models using SQL and analyses using PQL (Celonis proprietary language) to create compelling prototypes that address customer pain points. Lead proof-of-concept projects within the Celonis platform to demonstrate tangible value aligned with customer strategies and needs. Collaborate with customers and partners to design and build Celonis solutions that ensure a positive return on investment. Establish strong, trusted advisor relationships with customers through your technical expertise, product knowledge, and business acumen. Articulate and quantify strategic business value for customers, delivering impactful presentations to senior executives. Partner with the implementation services team to ensure successful value realization for customers. Identify opportunities for innovation and collaborate with Product &amp; Engineering teams to influence future product development. Contribute to the Global Value Engineering Center of Excellence by creating reusable collateral, best practices, and tools. What You Need: Bachelor’s degree in Engineering, Data Analytics, Industrial Engineering, Computer Science, Mathematics , or a related STEM field. Extensive internship experience or 1-3 years of full-time work experience. Hands-on experience with at least one of the following: SQL, Microsoft Power BI, Tableau, or another data analytics solution. A strong passion for technology, big data, and its transformative potential. Excellent analytical and creative problem-solving skills , with the ability to apply technology to business challenges. A customer-centric mindset with a focus on delivering value. The ability to build relationships with senior management and influence decision-making. Confidence in presenting to diverse audiences. A proactive approach to problem-solving, with a willingness to learn from mistakes. Curiosity, self-motivation, a commitment to continuous learning, and the desire to thrive in a fast-paced, high-growth environment. Strong organizational skills with the ability to prioritize and execute on deadlines. Excellent communication skills and fluency in English. Bonus Points: GPA of 3.6 or higher. Degree in Computer Science or Data Science or a similar field. Degrees combining technical (e.g., Computer Science, Data Science) and business (e.g., Economics, Marketing) skills. Experience with Python and Machine Learning. Customer-facing , customer success/service, or sales experience. Experience with Proof of Concept projects. Supply Chain process experience (Procurement, Order Management, Inventory Management, Production). Finance process experience (Accounts Payable, Accounts Receivable). Experience modeling ROI and TCO for business case justification. Experience with SAP and/or Oracle. Fluency in French and/or Spanish. Visa sponsorship is not offered for this role. What Celonis can offer you: Pioneer Innovation: Work with the global leader in Process Mining and the Process Intelligence Graph to shape the future of AI-driven business operations. Ownership from Day 1: Every full-time "Celonaut" is an owner, receiving Restricted Stock Units (RSUs) and merit-based refresh grants. Unrivaled Family Support: Benefit from our inclusive parental leave policy—24 weeks of fully paid leave for primary carers and 12 weeks for supporting carers, available from your first day of employment. Work-Life Integration: Enjoy Unlimited PTO (in applicable regions) and generous PTO globally, as well as a flexible hybrid work model that balances remote focus with vibrant office collaboration. Continuous Growth: Elevate your skills through our 70-20-10 learning framework, mentorship programs, and access to a dedicated learning platform. Holistic Well-being: Prioritize your health with subsidized Wellhub memberships, mental health counseling, and dedicated "Wellness Weeks" that prioritize work/life balance. Drive Sustainability: Participate in annual Impact Days, where you receive paid time off to volunteer for community and environmental causes with your local office, or virtually. Global Inclusion &amp; Belonging: Find community through our Inclusion Think Tank and participate in our annual Inclusion Days, ensuring every voice is heard and valued. Value-Driven Impact: Join a mission-led organization where our core values—Live for Customer Value, The Best Team Wins, We Own It, and Earth Is Our Future—drive every decision. About Us: Celonis makes processes work — for people, companies, and the planet. Powered by process mining and AI, the Celonis Process Intelligence Platform integrates process data and business context to create a living digital twin of business operations. We enable thousands of companies worldwide to understand how their business actually runs and, together with their partners, build intelligent solutions that transform and continuously improve the way they operate — unlocking billions in value. Celonis is headquartered in Munich, Germany, and New York City, USA, with more than 20 offices worldwide. Get familiar with the Celonis Process Intelligence Platform by watching this video . Celonis Inclusion Statement: At Celonis, we believe our people make us who we are and that “The Best Team Wins”. We know that the best teams are made up of people who bring different perspectives to the table. And when everyone feels included, able to speak up and knows their voice is heard - that's when creativity and innovation happen. Your Privacy: Any information you submit to Celonis as part of your application will be processed in accordance with Celonis’ Accessibility and Candidate Notices By submitting this application, you confirm that you agree to the storing and processing of your personal data by Celonis as described in our Privacy Notice for the Application and Hiring Process . Please be aware of common job offer scams, impersonators and frauds. Learn more here .</t>
         </is>
       </c>
-      <c r="L85" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>greenhouse|contentful|7560356</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Contentful</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>contentful</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>7560356</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Senior Business Intelligence Analyst</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Denver, Colorado, United States</t>
         </is>
       </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" t="inlineStr">
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/contentful/jobs/7560356</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>About the opportunity Contentful is seeking a Senior Business intelligence Analyst to join our growing Field organization. In this highly visible and impactful role, you will serve as the analytics thought leader for our Field Organization , transforming data into actionable insight that drives growth, improves efficiency, and enables strategic decision-making. You’ll work closely with field leadership, revenue operations, marketing, product and finance to uncover opportunities that accelerate pipeline generation, improve conversion rates, and optimize field performance. As a key business partner, you’ll help shape go-to-market strategy through data-informed recommendations and forward-looking analysis. This role sits within the Field organization but partners closely with our central Data team - leveraging Contentful’s Insight360 platform to ensure the field organization has trusted, timely, and actionable data. You’ll interrogate data, experiment, build dashboards and models, and guide leadership with fact-based storytelling that drives meaningful business outcomes. If you’re a hands-on analytics expert with a passion for solving commercial challenges through data, this is an opportunity to make a tangible impact on the growth and success of Contentful. What to expect? Partner with Field leadership to define, measure, and monitor key performance metrics across pipeline health, bookings, productivity, and retention. Deliver high-quality insights and analysis that guide tactical and strategic decisions, supporting both day-to-day operations and long-term growth initiatives. Build and maintain dashboards, reports, and models that provide real-time visibility into field performance using Contentful’s Insight360 platform and modern BI tools. Collaborate with the central Data team to ensure data integrity, develop new data capabilities, and define requirements for future enhancements to the data platform. Act as Data Steward for the Field organisation to help drive data capture improvements, define key metrics and attributes as well as ensure strong data hygiene for field owned data. Conduct deep-dive analyses on key topics such as funnel conversion, territory design, forecasting accuracy, and field capacity planning. Partner with Marketing, Customer Success, Product and Finance to create a holistic view of the customer lifecycle , connecting data across the revenue funnel. Translate complex data into clear, compelling narratives and visualizations for field leaders and executives. Act as a trusted advisor to field leadership , driving data-informed strategy, identifying improvement opportunities, and recommending operational efficiencies. Foster a culture of data-driven decision-making within the Field organization by promoting data fluency and self-service analytics. What do you need to be successful? Field leadership makes faster, more confident decisions using trusted, actionable insights. Insight360 and supporting dashboards become the single source of truth for Field performance and forecasting. The Field organization proactively uses data to identify growth opportunities, optimize resources, and exceed revenue targets . Cross-functional collaboration with the Data team ensures alignment between sales and CS needs and enterprise data strategy . You are recognized as a go-to strategic partner who blends analytical rigor with commercial acumen. What's in it for you? Join an ambitious tech company reshaping the way people build digital experiences Full-time employees receive Stock Options for the opportunity to share in the success of our company Comprehensive healthcare package covering 100% of monthly health premiums for employees and 85% of costs for your dependents. Fertility and family building benefits, including a lifetime reimbursable wallet to support your growing family. We value Work-Life balance and You Time ! A generous amount of paid time off, including vacation days, sick days, compassion days for loss, education days, and volunteer days Company paid parental leave to care for and focus on your growing family Use your personal annual education budget to improve your skills and grow in your career Enjoy a full range of virtual and in-person events, including workshops, guest speakers, and fun team activities, supporting learning and networking exchange beyond the usual work duties An annual wellbeing stipend to care for your physical, financial, or emotional health A monthly communication stipend and phone hardware upgrade reimbursement. New hire office equipment stipend for hybrid or distributed employees. Get the gear you need to work at your best. This role will need to be conducted in a state in which we are currently registered to do business. In addition, this position is not eligible for visa sponsorship. Applicants must be authorized to work without the need for visa sponsorship by the start date of employment. This position is eligible for equity awards in accordance with the terms of Contentful’s equity plans. The application deadline is 05/21/2026 Colorado Salary Statement: The salary range displayed is specifically for those potential hires who will work or reside in the state of Colorado if selected for the role. Any offered salary is determined based on internal equity, internal salary ranges, market data/ranges, applicant's skills and prior relevant experience, certain degrees and certifications (e.g. JD/technology), for example. Colorado Salary: $126,000- $170,000 Who are we? Contentful is a leading digital experience platform that helps modern businesses meet the growing demand for engaging, personalized content at scale. By blending composability with native AI capabilities, Contentful enables dynamic personalization, automated content delivery, and real-time experimentation, powering next-generation digital experiences across brands, regions, and channels for more than 4,200 organizations worldwide. More than 700 people from more than 70 nations contribute their energy and creativity to Contentful, working from hubs in Berlin, Denver, San Francisco, London, New York, and distributed worldwide. Everyone is welcome here! “Everyone is welcome here” is a celebrated component of our culture. At Contentful, we strive to create an inclusive environment that empowers our employees. We believe that our products and services benefit from our diverse backgrounds and experiences, and we are proud to be an equal opportunity employer. All qualified applications will receive consideration for employment without regard to race, color, national origin, religion, sexual orientation, gender, gender identity, age, physical [dis]ability, or length of time spent unemployed. We invite you to apply and join us! If you need reasonable accommodations at any point during the application or interview process, please let your recruiting coordinator know. Please be aware of scammers who may fraudulently allege to be from Contentful. These types of fraud can be carried out through copycat websites, fake email addresses claiming to be from our company, or social media. We do not ask for your personal information, such as bank account numbers, identification numbers, etc, through social media or chat-based apps, nor do we request or send money for the purchase of business equipment. If you suspect fraud, please report it to your local authorities, as well as reach out to us at security-esk@contentful.com with any information you may have. By clicking “Apply for this job,” I acknowledge that I have read the “ Contentful’s Candidate Privacy Notice ” and hereby consent to the collection, processing, use, and storage of my personal information as described therein.</t>
         </is>
       </c>
-      <c r="L86" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>greenhouse|hellofresh|7977373</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>HelloFresh</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>hellofresh</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>7977373</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Claims &amp; Risk Analyst</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Boulder, Colorado, United States; Irving, TX, United States; New York, NY, United States</t>
-        </is>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>https://careers.hellofresh.com/global/en/job/7977373?gh_jid=7977373</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>HelloFresh is seeking a Claims &amp; Risk Analyst to join our team! As a Claims &amp; Risk Analyst, you will support day-to-day operations across claims management, reporting, and insurance program administration. This role is primarily focused on supporting our Workers' Compensation program, while also assisting with a smaller portfolio of general liability, property, subrogation (recovery), and commercial auto claims as needed. You will play a key role in ensuring claims are managed efficiently from intake through resolution by supporting claim intake, tracking, reporting, and timely claim processing. You'll maintain accurate claims data and dashboards while coordinating with internal stakeholders, third-party administrators (TPAs), carriers, and brokers to help drive claims toward successful resolution. This position offers the opportunity to gain broad exposure across corporate risk management, including claims oversight, data analytics, return-to-work programs, insurance renewals, and continuous process improvement. You will... Manage claim intake end-to-end, including FNOL processing, initial review, severity assignment, and escalation identification Monitor and support claims throughout the lifecycle by handling routine follow-ups, identifying aging or high-risk claims, and coordinating with adjusters to ensure timely progression Prepare and support bi-weekly claim reviews, including compiling data, tracking action items, and maintaining TPA performance metrics Build, maintain, and validate dashboards and reports across claims, trends, KPIs, and loss data to ensure accuracy and consistency Analyze claims data to identify trends, emerging risks, and recurring root causes, and partner with internal stakeholders to support action planning Track Return-to-Work progression for injured workers, and compliance-related data, including audit support and timely updates across systems Track and support subrogation and recovery efforts, including follow-ups on outstanding items and documentation Assist with insurance program administration, including exposure data collection, renewal support, and submission preparation Review claim files and collaborate with TPAs on reserve adequacy and claim strategy Partner cross-functionally to gather required documentation and support efficient claim processing Participate in regular calls with carriers, brokers, and TPAs to support claim oversight and program execution Support additional risk management and claims-related tasks as needed At a minimum, you have... 2–3 years experience with workers' compensation claims, either as a claims adjuster or through direct involvement of an employer's Workers' Compensation program within a risk management function. Bachelor’s degree preferred; will consider high school diploma with 2+ years of experience listed above ARM, CPCU, CRM, AIC or other risk/insurance designations preferred but not required Strong Excel and data analysis capabilities; Power BI and/or RMIS experience is a plus A proactive and self-motivated mindset and are highly responsive to meeting the needs of our internal and external customer Ability to work both independently and collaboratively in a team environment, while effectively prioritizing tasks and managing time Ability to adapt to changing business needs, with a flexible approach to shifting priorities, processes, and responsibilities You’ll get… Competitive Salary &amp; 401k company match that vests immediately upon participation Generous parental leave of 16 weeks &amp; PTO policy $0 monthly premium and other flexible health plans 85% discount on your subscription to HelloFresh (as well as other product initiatives) Employee Resource Groups Collaborative, dynamic work environment within a fast-paced, mission-driven company This job description is intended to provide a general overview of the responsibilities. However, the Company reserves the right to adjust, modify, or reassign work tasks and responsibilities as needed to meet changing business needs, operational requirements, or other factors. New York Pay Range $68,040 — $81,000 USD Colorado Pay Range $63,000 — $75,000 USD</t>
-        </is>
-      </c>
-      <c r="L87" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>greenhouse|sumup|8596342002</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>SumUp</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>sumup</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>8596342002</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Data Analytics Engineer - Boulder, Colorado</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Boulder, Colorado, United States</t>
-        </is>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>https://sumup.com/careers/positions/8596342002?gh_jid=8596342002</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Data Analytics Engineer — Boulder, Colorado Full-time | Boulder, CO | No visa sponsorship available The US Analytics team is building the data foundations that power SumUp's US operations. We design reliable data models, keep our infrastructure clean, and turn complex datasets into insights the business can act on. You'll join at a point where there's real work to own — from shaping how data is structured to improving the tools and dashboards that teams rely on every day. If you're someone who's been close to data in an analytical role and is ready to go deeper into how it's built and maintained, this is a meaningful next step. 👉 Take a look at our Boulder office What you'll do Build, maintain, and document DBT models in a Snowflake environment, keeping data clean, reliable, and well-structured Develop and maintain Tableau dashboards and data sources that stakeholders across the business trust and use independently Rotate through day-to-day data operations support — handling ad hoc requests, troubleshooting reporting issues, and diagnosing pipeline problems Contribute to modernizing our data infrastructure, helping business stakeholders self-serve through AI-assisted tooling Own stakeholder relationships independently — gathering requirements, setting clear expectations, and communicating confidently with technical and non-technical audiences alike You'll be great for this role if… Strong experience building or structuring datasets — not just querying them based on others work Solid SQL and DBT Core skills, hands-on experience with Snowflake and Proven ability to build Tableau dashboards that stakeholders genuinely rely on Strong communicator who can own stakeholder conversations, gather requirements, manage expectations, and push back when a request isn't clearly defined High attention to data quality and the confidence to work through problems independently before escalating Familiarity with AI-assisted data tools such as GitHub Copilot or Cursor Familiarity with Salesforce Bonus points for: Advanced DBT experience Experience with self-serve or semantic data layers Contributions to an AI agent knowledge base or prompt engineering work Understanding of the limitations of LLMs when applied to data problems Previous experience in a fast paced, team environment Why you should join SumUp 🌍 Opportunity to work with SumUppers globally on large-scale fintech products used by millions of businesses worldwide, from our Boulder office. This involves an office-first setup 🚀 Enrollment onto our Virtual Stock Option program: you will own a stake in SumUp's future success 📚 A dedicated annual learning budget of $2,000 for your individual development, which can be used to attend conferences and/or advance your career through further education 🏖 Generous time off: 22 days of paid vacation, plus an extra day each year up to 28 days, public holidays, and special leaves 🏥 Health and life coverage: group medical coverage, plus life insurance 💼 Financial security: 401(k) retirement scheme with SumUp matching funds 🌴 Break4me: 1-month sabbatical after 3 years of service 🌈 Commitment to Diversity and Inclusion: be part of a workplace that values and promotes diversity, fostering an inclusive environment where everyone's perspectives are respected and embraced Compensation: $100,000–$120,000 base salary Virtual Stock Options Final compensation will be based on the candidate's experience and location About SumUp Be empowered to do more that matters. At SumUp, we're on a mission to empower small businesses across the globe by providing simple and affordable tools that allow them to thrive. Today, over 4 million businesses in 37 markets rely on SumUp as their financial partner to manage payments, finance and customer relationships. Our commitment to small businesses is reflected in our diverse team of over 4,000 SumUppers from over 90 nationalities, united by global collaboration and an innovative mindset. Our core values lay the foundation for who we are and what we stand for, shaping our work culture and driving our success. We foster inclusivity and a continuous learning culture, providing a safe space for personal and professional growth. Our differences make us unique and strong as we strive to create an environment where everyone belongs and feels supported, no matter how they identify. SumUp is proud to be an Equal Employment Opportunity employer, actively seeking and embracing diversity in our workforce. We don't make hiring or employment decisions based on race, colour, religion or religious belief, ethnic or national origin, nationality, sex, gender, gender identity, sexual orientation, disability, age or any other basis protected by applicable laws or prohibited by company policy. Our commitment extends beyond recruitment to creating a safe and respectful workplace where harassment of any form is strictly prohibited. Discover more about our culture and opportunities on our careers website , and follow our journey on LinkedIn , Instagram , and TikTok . Job Application Tip We recognise that candidates feel they need to meet 100% of the job criteria in order to apply for a job. Please note that this is only a guide. If you don’t tick every box, it’s ok too because it means you have room to learn and develop your career at SumUp.</t>
-        </is>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>greenhouse|sumup|8558683002</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>SumUp</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>sumup</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>8558683002</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Outside Sales Account Executive - Kansas City, MO</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Missouri, United States</t>
-        </is>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>https://sumup.com/careers/positions/8558683002?gh_jid=8558683002</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>SUMUP IS HIRING for the greater Kansas City Area... This is a Field Sales role Who You Are You are a sales professional with 1-5 years of experience, who is bright and driven, looking for a genuine opportunity where you can be with a company for a long time. In fact, you are GREAT, you are going places, so you are looking for a home where your commissions are uncapped, though you also need that base salary to pay immediate bills. You’re also looking for somewhere that allows you to move up internally, because you’ll need that, and to work with an interesting technical product that actually makes a real difference in the world. You care about helping others and your local neighborhood. You want a start-up atmosphere, but you also want stability in rocky times and good benefits, and you want to work with other great people who are fun and above all make you better than you ever thought you could be. SumUp supports a diverse community of professionals with various backgrounds and lived experiences. There is no “perfect candidate” for this role. We are simply searching for people that are driven to succeed in helping SumUp continue delivering on our values and making our customers successful. A Day In Your Life Armed with a good understanding of the product from training, you will build a sales pipeline by developing relationships with local businesses. We will show you how. You will make their life easier by selling a payment and loyalty solution that turns their small enterprise into the heartbeat of the block. Over 3 million merchants use us because our products are good. This is going to require research however, and cold calling, and knocking on doors, and above all empathy and kindness for your customer’s needs. The Role You Would Fill Full sales cycle management including territory based prospecting and canvassing Cold Calling for new business leads Research (play smarter not harder) Use our CRM to track performance and ensure communication and success Your Background 1-5 years of sales experience Reliable transportation Experience in retail, hospitality, B2B and/or SAAS sales is always a plus. If you don’t have this, please don’t let this stop you from applying Who we are SumUp is a fast-growing fintech firm that helps local families and businesses by allowing them to receive payments quickly and simply, both in-store and online. We are no small cheese because we have over 3000 employees and work in over 34 countries. But most importantly we are relied upon by merchants of all sizes from DHL to taxi drivers. A few details of the role include: Starting Compensation: On-target-earnings (OTE) $107,000 with uncapped commission. Opportunities for advancement and increased compensation based on performance. 22 days of annual PTO plus 11 paid holidays 401K matching Great medical, dental and vision benefits. #SumUpUSA Job Application Tip We recognise that candidates feel they need to meet 100% of the job criteria in order to apply for a job. Please note that this is only a guide. If you don’t tick every box, it’s ok too because it means you have room to learn and develop your career at SumUp.</t>
-        </is>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>ashby|photoroom|62fccba8-2ec8-4411-9b38-10db8055f69c</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Photoroom</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>photoroom</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>62fccba8-2ec8-4411-9b38-10db8055f69c</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Senior Software Engineer (FastAPI &amp; Async Python)</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Paris | Remote</t>
         </is>
       </c>
-      <c r="H90" t="n">
-        <v>1</v>
-      </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" t="inlineStr">
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/photoroom/62fccba8-2ec8-4411-9b38-10db8055f69c</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>ABOUT US
 Founded in 2019 and part of Y Combinator's 2020 cohort, Photoroom https://www.photoroom.com is the leading visual solution for e-commerce.
@@ -5804,338 +3516,338 @@
 All qualified applicants receive consideration for employment without regard to age, color, family, gender identity, marital status, national origin, physical or mental disability, sex (including pregnancy), sexual orientation, or any other characteristic protected by applicable laws.</t>
         </is>
       </c>
-      <c r="L90" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>greenhouse|isomorphic labs|5460704004</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Isomorphic Labs</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>isomorphiclabs</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>5460704004</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Research Scientist (Machine Learning), Lausanne</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" t="inlineStr">
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/isomorphiclabs/jobs/5460704004</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>Isomorphic Labs is applying frontier AI to help unlock deeper scientific insights, faster breakthroughs, and life-changing medicines with an ambition to solve all disease. The future is coming. A future enabled and enriched by the incredible power of machine learning. A future in which diseases are curtailed or cured starting with better and faster drug discovery. Come and be part of an interdisciplinary team driving groundbreaking innovation and play a meaningful role in contributing towards us achieving our ambitious goals, while being a part of an inspiring and collaborative culture. The world we want tomorrow is the one we’re building today. It starts with the culture at this company. It starts with you. About Iso Isomorphic Labs (IsoLabs) was launched in 2021 to advance human health by building on and beyond the Nobel-winning AlphaFold system. Since then, our interdisciplinary team of drug discovery experts and machine learning specialists has built powerful new predictive and generative AI models that accelerate scientific discovery at digital speed. Our name comes from the belief that there is an underlying symmetry between biology and information science. By harnessing AI’s powerful capabilities, we can use it to model complex biological phenomena to help design novel molecules, anticipate how drugs will perform and develop innovative medicines to treat and cure some of the world’s most devastating diseases. We have built a world-leading drug design engine comprising AI models that are capable of working across multiple therapeutic areas and drug modalities. We are continually innovating on model architecture and developing cutting-edge capabilities to advance rational drug design. Every day, and with each new breakthrough, we’re getting closer to the promise of digital biology, and achieving our ambitious mission to one day solve all disease with the help of AI. Research Scientist (Machine Learning), Lausanne Your impact As a Research Scientist in machine learning (ML), you will play an exciting role in building greenfield machine learning based models and algorithms that will power our platform to transform the drug discovery world as we know it. Working in a highly creative, fast-paced and interdisciplinary environment, you will be partnering with leading engineers and scientists to conceive, design, and develop cutting edge machine learning algorithms to unlock new modelling and predictive power which will be critical to the organisation’s success. You will draw upon your existing deep research experience whilst learning from those around you, to apply novel techniques and ideas to newly encountered computational biology and chemistry problems. Depending on your experience: You will create and lead projects, bringing together a variety of disciplined scientists and engineers to pursue some of the most ambitious modelling problems with deep learning - as well as providing technical mentorship and people management for others in the ML community at Isomorphic Labs You will be instrumental in leading greenfield machine learning based research projects, building the models, and algorithms that will power our platform to transform the drug discovery world as we know it. What you will do Contribute to our research directions in machine learning by using your extensive knowledge of the field to apply world-leading ML algorithms to drug discovery. Identify and create novel ML techniques and the required data to train. Develop the architectures and training algorithms of machine learning models. Analyse and tune experimental results to inform future experimental directions. Implement and scale training and inference engineering frameworks. Report and present research findings and developments clearly and efficiently, to both other ML scientists and scientists of different disciplines. Iterate collaboratively with scientists and domain experts, sharing your own domain experience. Suggest and engage in team collaborations to meet ambitious research goals. Depending on your experience: Provide technical mentorship and guidance to the ML research community, advising on projects, and shaping our research roadmap based on your deep technical expertise. Provide developmental support to other ML research scientists. Create, lead, and run ML research projects, fostering collaborative and diverse teams to solve high priority modelling problems.Cultivate a diverse and inclusive research culture. Skills and qualifications Essential PhD or equivalent practical experience in a technical field. A proven track record in machine learning using deep learning techniques, including designing new architectures, hands-on experimentation, analysis, and visualisation. Strong knowledge of linear algebra, calculus and statistics. Experience using ML frameworks such as JAX, PyTorch, or TensorFlow, and scientific software such as NumPy, SciPy, or Pandas. A passion for applying ML research to real world problems. Depending on your experience: project supervision, leadership, or management. Nice to have PhD in machine learning or computer science. Relevant research experience to the position such as post doctoral roles, a proven track record of publications, or contributions to machine learning codebases. Experience working in a scientific environment across disciplines (particularly biology, chemistry, physics). Experience working with biological or chemical data and biological or chemistry software. Experience working with real-world datasets. Experience with ML on accelerators. Experience in any of: large scale deep learning, generative models, graph neural networks, deep learning for drug discovery, deep learning for computer vision, 3D graphics/robotics, real-world applied RL. Culture and values We are guided by our shared values. It's not about finding people who think and act in the same way. These values help to guide our work and will continue to strengthen it. Thoughtful Thoughtful at Iso is about curiosity, creativity and care. It is about good people doing good, rigorous and future-making science every single day. Brave Brave at Iso is about fearlessness, but it’s also about initiative and integrity. The scale of the challenge demands nothing less. Determined Determined at Iso is the way we pursue our goal. It’s a confidence in our hypothesis, as well as the urgency and agility needed to deliver on it. Because disease won’t wait, so neither should we. Together Together at Iso is about connection, collaboration across fields and catalytic relationships. It’s knowing that transformation is a group project, and remembering that what we’re doing will have a real impact on real people everywhere. Creating an extraordinary company We believe that to be successful we need a team with a range of skills and talents. We're building an environment where collaboration is fundamental, learning is shared and every employee feels supported and able to thrive. We value unique experiences, knowledge, backgrounds, and perspectives, and harness these qualities to create extraordinary impact. We are committed to equal employment opportunities regardless of sex, race, religion or belief, ethnic or national origin, disability, age, citizenship, marital, domestic or civil partnership status, sexual orientation, gender identity, pregnancy or related condition (including breastfeeding) or any other basis protected by applicable law. If you have a disability or additional need that requires accommodation, please do not hesitate to let us know. Hybrid working It’s hugely important for us to share knowledge and build strong relationships with each other, and we find it easier to do this if we spend time together in person. This is why we follow a hybrid model, and would require you to be able to come into the office 3 days a week (currently Tuesday, Wednesday, and one other day depending on which team you’re in). If you have additional needs that would prevent you from following this hybrid approach, we’d be happy to talk through these if you’re selected for an initial screening call. Please note that when you submit an application, your data will be processed in line with our privacy policy . &gt;&gt; Click to view other open roles at Isomorphic Labs</t>
         </is>
       </c>
-      <c r="L91" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>greenhouse|physicsx|4880922101</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>PhysicsX</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>physicsx</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>4880922101</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>San Francisco, United States</t>
         </is>
       </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" t="inlineStr">
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/physicsx/jobs/4880922101</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>About us PhysicsX is a deep-tech company with roots in numerical physics and Formula One, dedicated to accelerating hardware innovation at the speed of software. We are building an AI-driven simulation software stack for engineering and manufacturing across advanced industries. By enabling high-fidelity, multi-physics simulation through AI inference across the entire engineering lifecycle, PhysicsX unlocks new levels of optimization and automation in design, manufacturing, and operations — empowering engineers to push the boundaries of possibility. Our customers include leading innovators in Aerospace &amp; Defense, Materials, Energy, Semiconductors, and Automotive. Who We're Looking For As a Data Scientist in Delivery, you are a problem solver and builder who is passionate about creating practical solutions that enable customers to make better engineering decisions. You are someone who can grasp advanced engineering concepts across multiple industries, and you excel at working directly with customers (and often side-by-side with them on-site) to transform cutting edge AI models into tools that are useful and used. You’ve worked on difficult problems that require strong foundations in data driven modelling and deep learning techniques, with hands-on experience in probabilistic methods and predictive modelling. Expertise in python, along with proficiency in libraries like NumPy, SciPy, Pandas, TensorFlow and PyTorch, is essential, with the ability to deploy scalable, production-ready models and data pipelines. With at least 1 year industry experience (post Masters or PhD) in a commercial, non-research environment, you’re ready to hit the ground running. You’re truly excited about growing your technical expertise and are naturally inclined to take ownership of data science work streams, continuously improving the systems and solutions you work on to ensure they are practical, impactful and meet the evolving needs of our customers. This Role In this role, you’ll work closely with our Simulation Engineers, Machine Learning Engineers, and customers to understand and define the engineering and physics challenges we are solving. You’ll build the foundations for successful, impactful solutions by: Pre-processing and analyzing data to prepare it for use in predictive modelling, building the foundation for machine learning algorithms to be developed. Developing and utilizing innovative deep learning models in combination with state-of-the-art optimization methods to predict and control the behaviour of physical systems. Taking full responsibility for the quality, accuracy and impact of your work. Designing, building and testing data pipelines that are reliable, scalable and easily deployable in production environments. Working closely with simulation engineers to ensure seamless integration of data science models with simulations. Contributing to internal R&amp;D and product development, helping to refine models and identify new areas of application. Engaging in open communication and presentation with both technical teams and customers, helping onboard users and co-develop with customers. You'll also have the opportunity to travel to customer sites in North America, Europe, Asia, Oceania, for an average of 3-4 weeks per quarter , where you'll collaborate closely with customers to build solutions on-site. As the role evolves, there are exciting opportunities for growth as an individual contributor or a technical lead, especially if you’re driven by taking ownership of more complex projects and leading the direction of future solutions. Our delivery teams drive innovation to turn AI models into practical solutions - read our blog to learn more about how you’ll contribute to this exciting journey! What we offer Build what actually matters Help shape an AI-native engineering company at a formative stage, tackling problems that genuinely matter for industry and society. This is work with real-world impact - and something you can be proud to stand behind. Learn alongside exceptional people Work with a high-caliber, collaborative team of engineers, scientists, and operators who care deeply about doing great work, and about helping each other get better. We come from diverse backgrounds, but we share a commitment to operating at the highest level and addressing some of the most complex challenges out there. If you’re ambitious, thoughtful, and driven by impact, you’ll feel at home. Influence over hierarchy We operate with a flat structure: good ideas win - wherever they come from. Questioning assumptions and challenging the status quo isn’t just welcomed, it’s expected. Sustainable pace, long-term ambition Building meaningful technology is a marathon, not a sprint. We believe in balancing focused, ambitious work with a life beyond it. Our hybrid model blends time together in our New York office with work-from-home days, giving you the flexibility to work sustainably while staying connected in person. And it doesn’t stop there … 🚀 Equity options - share meaningfully in the company you’re helping to build. 💰 5% contribution to 401(k) - build long-term security with a strong retirement plan. 🍽️ Free team lunch 1x/week - good food, great company, and space to connect. 🏥 Private health insurance – comprehensive cover for you, offering total peace of mind. 👶 Enhanced parental leave – 3 months full pay paternity and 6 months full pay maternity leave, to provide extra flexibility during the moments that matter most. ☀️ 20 days of Annual Leave (+ Public Holidays) - because taking time to rest matters. 📈 Personal development – dedicated support for learning, development, and leveling up over time. 💪 Gympass / Wellhub (subsidized) – for you and up to 3 family members, supporting both physical and mental wellbeing. 💳 Flexible Spending Account (FSA) – set aside pre-tax dollars for eligible healthcare expenses. 🔎 Watch this space, we’re continuing to build this as we grow… Salary Range $120,000 - 240,000 depending on experience Seniority will be assessed throughout our interview process We value diversity and are committed to equal employment opportunity regardless of sex, race, religion, ethnicity, nationality, disability, age, sexual orientation or gender identity. We strongly encourage individuals from groups traditionally underrepresented in tech to apply. To help make a change, we sponsor bright women from disadvantaged backgrounds through their university degrees in science and mathematics. We collect diversity and inclusion data solely for the purpose of monitoring the effectiveness of our equal opportunities policies and ensuring compliance with UK employment and equality legislation. This information is confidential, used only in aggregate form, and will not influence the outcome of your application.</t>
         </is>
       </c>
-      <c r="L92" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>greenhouse|physicsx|4849382101</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>PhysicsX</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>physicsx</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>4849382101</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">New York, United States </t>
         </is>
       </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" t="inlineStr">
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/physicsx/jobs/4849382101</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>About us PhysicsX is a deep-tech company with roots in numerical physics and Formula One, dedicated to accelerating hardware innovation at the speed of software. We are building an AI-driven simulation software stack for engineering and manufacturing across advanced industries. By enabling high-fidelity, multi-physics simulation through AI inference across the entire engineering lifecycle, PhysicsX unlocks new levels of optimization and automation in design, manufacturing, and operations — empowering engineers to push the boundaries of possibility. Our customers include leading innovators in Aerospace &amp; Defense, Materials, Energy, Semiconductors, and Automotive. Note: We are currently recruiting for multiple positions, however please only apply for the role that best aligns with your skillset and career goals. Who We're Looking For As a Machine Learning Engineer in Delivery, you are a problem solver who stays anchored to impact. You are someone who can grasp advanced engineering concepts across multiple industries, and excel at working directly with customers (and often side-by-side with them on-site) to embed cutting-edge AI models into tools that are useful and used. You’ve shipped ML systems end-to-end and at scale: you design, build and test reliable, scalable ML data pipelines; you know how to explore and manipulate 3D point-cloud and mesh data to enable geometry-aware modelling; you select the right libraries, frameworks and tools. Working at the intersection of data science and software engineering, you translate R&amp;D and project outputs into reusable libraries, tooling and products. With at least 2 years industry experience (post Masters or PhD) in a commercial, non-research environment. You're truly excited about taking ownership of complex work streams and guiding teams to success, while continuously improving the systems and solutions you work on to ensure they are practical, impactful and meet the evolving needs of our customers. Note: Due to the nature of our aerospace and defense work, this position is open to US citizens only. This Role As a Machine Learning Engineer, you'll work closely with our Data Scientists, Simulation Engineers, and customers to understand and define the engineering and physics challenges we are solving. You will iterate with customers and use your influence to drive decisions around reliable deployment with measurable outcomes. What you will do Work closely with our simulation engineers, data scientists and customers to develop an understanding of the physics and engineering challenges we are solving Design, build and test data pipelines for machine learning that are reliable, scalable and easily deployable Explore and manipulate 3D point cloud &amp; mesh data Own the delivery of technical workstreams Create analytics environments and resources in the cloud or on premise, spanning data engineering and science Identify the best libraries, frameworks and tools for a given task, make product design decisions to set us up for success Work at the intersection of data science and software engineering to translate the results of our R&amp;D and projects into re-usable libraries, tooling and products Continuously apply and improve engineering best practices and standards and coach your colleagues in their adoption You'll also have the opportunity to travel to customer sites in North America, Europe, Asia, Oceania, for an average of 3-4 weeks per quarter , where you'll collaborate closely with customers to build solutions on-site. What you bring to the table Experience applying Machine learning methods (including 3D graph/point cloud deep learning methods) to real-world engineering applications, with a focus on driving measurable impact in industry settings. Experience in ML/Computational statistics/Modelling use-cases in industrial settings (for example supply chain optimisation or manufacturing processes) is encouraged. A track record of scoping and delivering projects in a customer facing role 2+ years’ experience in a data-driven role, with exposure to software engineering concepts and best practices (e.g., versioning, testing, CI/CD, API design, MLOps) Building machine learning models and pipelines in Python, using common libraries and frameworks (e.g., TensorFlow, MLFlow) Distributed computing frameworks (e.g., Spark, Dask) Cloud platforms (e.g., AWS, Azure, GCP) and HP computing Containerization and orchestration (Docker, Kubernetes) Strong problem-solving skills and the ability to analyse issues, identify causes, and recommend solutions quickly Excellent collaboration and communication skills - with teams and customers alike A background in Physics, Engineering, or equivalent Our delivery teams drive innovation to turn AI models into practical solutions - read our blog to learn more about how you’ll contribute to this exciting journey! What we offer Build what actually matters Help shape an AI-native engineering company at a formative stage, tackling problems that genuinely matter for industry and society. This is work with real-world impact - and something you can be proud to stand behind. Learn alongside exceptional people Work with a high-caliber, collaborative team of engineers, scientists, and operators who care deeply about doing great work, and about helping each other get better. We come from diverse backgrounds, but we share a commitment to operating at the highest level and addressing some of the most complex challenges out there. If you’re ambitious, thoughtful, and driven by impact, you’ll feel at home. Influence over hierarchy We operate with a flat structure: good ideas win - wherever they come from. Questioning assumptions and challenging the status quo isn’t just welcomed, it’s expected. Sustainable pace, long-term ambition Building meaningful technology is a marathon, not a sprint. We believe in balancing focused, ambitious work with a life beyond it. Our hybrid model blends time together in our New York office with work-from-home days, giving you the flexibility to work sustainably while staying connected in person. And it doesn’t stop there … 🚀 Equity options - share meaningfully in the company you’re helping to build. 💰 5% contribution to 401(k) - build long-term security with a strong retirement plan. 🍽️ Free team lunch 1x/week - good food, great company, and space to connect. 🏥 Private health insurance – comprehensive cover for you, offering total peace of mind. 👶 Enhanced parental leave – 3 months full pay paternity and 6 months full pay maternity leave, to provide extra flexibility during the moments that matter most. ☀️ 20 days of Annual Leave (+ Public Holidays) - because taking time to rest matters. 📈 Personal development – dedicated support for learning, development, and leveling up over time. 💪 Gympass / Wellhub (subsidized) – for you and up to 3 family members, supporting both physical and mental wellbeing. 💳 Flexible Spending Account (FSA) – set aside pre-tax dollars for eligible healthcare expenses. 🔎 Watch this space, we’re continuing to build this as we grow… Salary range: $150,000 - $190,000 depending on experience Seniority will be assessed throughout our interview process We value diversity and are committed to equal employment opportunity regardless of sex, race, religion, ethnicity, nationality, disability, age, sexual orientation or gender identity. We strongly encourage individuals from groups traditionally underrepresented in tech to apply. To help make a change, we sponsor bright women from disadvantaged backgrounds through their university degrees in science and mathematics. We collect diversity and inclusion data solely for the purpose of monitoring the effectiveness of our equal opportunities policies and ensuring compliance with UK employment and equality legislation. This information is confidential, used only in aggregate form, and will not influence the outcome of your application.</t>
         </is>
       </c>
-      <c r="L93" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>greenhouse|physicsx|4852973101</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>PhysicsX</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>physicsx</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>4852973101</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Senior Computer Vision Data Scientist</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
       </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" t="inlineStr">
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/physicsx/jobs/4852973101</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>About us PhysicsX is a deep-tech company with roots in numerical physics and Formula One, dedicated to accelerating hardware innovation at the speed of software. We are building an AI-driven simulation software stack for engineering and manufacturing across advanced industries. By enabling high-fidelity, multi-physics simulation through AI inference across the entire engineering lifecycle, PhysicsX unlocks new levels of optimization and automation in design, manufacturing, and operations — empowering engineers to push the boundaries of possibility. Our customers include leading innovators in Aerospace &amp; Defense, Materials, Energy, Semiconductors, and Automotive. Senior Data Scientist — Computer Vision &amp; Predictive Maintenance We are looking for a Senior Data Scientist with deep computer vision expertise to lead the development of physics-informed predictive maintenance systems for high-value industrial equipment. Working directly with major industrial customers, you will build pipelines that fuse periodic inspection imagery with equipment operating history and physics-based inputs to predict remaining component life — helping operators reduce costly unplanned interventions and optimise asset availability. Who we're looking for You have a strong research foundation in computer vision and applied deep learning, and you know how to take that foundation into production on real-world industrial problems. You are energised by the challenge of building models that actually work under difficult conditions — sparse data, inconsistent image quality, and high stakes for getting it wrong. You can move fluidly between designing the right architecture and debugging a broken data pipeline. You are comfortable working directly with domain experts and customers to translate physical intuition into modelling decisions, and you care about producing outputs that engineers can trust and operators can act on. What you bring Deep expertise in selecting, adapting, and fine-tuning pretrained vision encoders (ViT, DINOv3, ResNet-family or equivalent) for industrial or scientific imaging problems where data is sparse and capture conditions are variable Strong command of gradient-based interpretability methods (Grad-CAM, integrated gradients) and the ability to produce sensitivity maps that make model behaviour reviewable by non-ML domain experts Proven ability to build joint models that combine visual features with heterogeneous inputs including tabular metadata, time-series operating history, and physics-derived signals Hands-on experience with probabilistic or Bayesian output modelling and calibrated uncertainty quantification Production ML mindset - you architect and ship reliable, scalable pipelines deployable within enterprise cloud environments, not just notebooks Comfort with messy, real-world industrial datasets: sparse time series, noisy labels, irregular collection intervals, and data linkage challenges Strong communication skills across technical and non-technical audiences, including the ability to co-develop solutions on-site with customers PhD or equivalent research experience in computer vision, machine learning, or a related field strongly preferred Experience with physics-informed or hybrid ML approaches is a significant plus Domain experience in aerospace, energy, heavy industry, mining, or MRO is helpful but not required — genuine curiosity about engineering domains and asset-intensive operations is essential And it doesn’t stop there … 🚀 Equity options - share meaningfully in the company you’re helping to build. 💰 5% contribution to 401(k) - build long-term security with a strong retirement plan. 🍽️ Free team lunch 1x/week - good food, great company, and space to connect. 🏥 Private health insurance – comprehensive cover for you, offering total peace of mind. 👶 Enhanced parental leave – 3 months full pay paternity and 6 months full pay maternity leave, to provide extra flexibility during the moments that matter most. ☀️ 20 days of Annual Leave (+ Public Holidays) - because taking time to rest matters. 📈 Personal development – dedicated support for learning, development, and leveling up over time. 💪 Gympass / Wellhub (subsidized) – for you and up to 3 family members, supporting both physical and mental wellbeing. 💳 Flexible Spending Account (FSA) – set aside pre-tax dollars for eligible healthcare expenses. 🔎 Watch this space, we’re continuing to build this as we grow… Salary Range $120,000 - 240,000 depending on experience Seniority will be assessed throughout our interview process We value diversity and are committed to equal employment opportunity regardless of sex, race, religion, ethnicity, nationality, disability, age, sexual orientation or gender identity. We strongly encourage individuals from groups traditionally underrepresented in tech to apply. To help make a change, we sponsor bright women from disadvantaged backgrounds through their university degrees in science and mathematics. We collect diversity and inclusion data solely for the purpose of monitoring the effectiveness of our equal opportunities policies and ensuring compliance with UK employment and equality legislation. This information is confidential, used only in aggregate form, and will not influence the outcome of your application.</t>
         </is>
       </c>
-      <c r="L94" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>greenhouse|physicsx|4678291101</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>PhysicsX</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>physicsx</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>4678291101</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">New York, United States </t>
         </is>
       </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" t="inlineStr">
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/physicsx/jobs/4678291101</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>About us PhysicsX is a deep-tech company with roots in numerical physics and Formula One, dedicated to accelerating hardware innovation at the speed of software. We are building an AI-driven simulation software stack for engineering and manufacturing across advanced industries. By enabling high-fidelity, multi-physics simulation through AI inference across the entire engineering lifecycle, PhysicsX unlocks new levels of optimization and automation in design, manufacturing, and operations — empowering engineers to push the boundaries of possibility. Our customers include leading innovators in Aerospace &amp; Defense, Materials, Energy, Semiconductors, and Automotive. Note: We are currently recruiting for multiple positions, however please only apply for the role that best aligns with your skillset and career goals. Who We're Looking For As a Senior Machine Learning Engineer in Delivery, you are an experienced problem solver and technical leader who stays anchored to impact. You are someone who can grasp advanced engineering concepts across multiple industries, lead technical initiatives, and excel at working directly with customers (and often side-by-side with them on-site) to embed cutting-edge AI models into tools that are useful and used. You’ve shipped ML systems end-to-end and at scale: you design, build and test reliable, scalable ML data pipelines; you know how to explore and manipulate 3D point-cloud and mesh data to enable geometry-aware modelling; you select the right libraries, frameworks and tools and make pragmatic product decisions that set Delivery up for success. Working at the intersection of data science and software engineering, you translate R&amp;D and project outputs into reusable libraries, tooling and products. With at least 3 years industry experience (post Masters or PhD) in a commercial, non-research environment, you're ready to not only execute but also lead and mentor others. You're truly excited about taking ownership of complex work streams and guiding teams to success, while continuously improving the systems and solutions you work on to ensure they are practical, impactful and meet the evolving needs of our customers. Note: Due to the nature of our aerospace and defense work, this position is open to US citizens only. This Role As a Senior MLE, you'll work closely with our Data Scientists, Simulation Engineers, and customers to understand and define the engineering and physics challenges we are solving. You will iterate with customers and use your influence to drive decisions around reliable deployment with measurable outcomes. You'll: Own the deployment of ML models and engineering surrogates (e.g., deep learning on CAE/CFD/FEA data, time‑series forecasting, anomaly detection, optimization &amp; control) to customer production environments. Communicate results and trade‑offs to senior stakeholders; steer roadmaps and influence product direction with evidence. Lead scoping and architecture design for data/ML systems; define success metrics, delivery plans and quality bars. Excel at building robust and scalable ML systems, training and inference pipelines and APIs, running both on cloud and on-prem environments. The tech stack you will use for this includes: Python, PyTorch, Pandas, fastAPI, Scipy, Kubeflow, among others. Mentor and develop engineers and data scientists; provide technical direction and clear, calm decision‑making under pressure. Travel to customer sites in North America, Europe, Asia, Oceania, for an average of 3-4 weeks per quarter , where you'll collaborate closely with customers to build solutions on-site. Own the scoping of new projects and work-streams with existing customers and taking part in bringing new customers to PhysicsX. As a senior member of the team, you’ll significantly influence our technical direction and will be involved in shaping future solutions and products, while developing your skills as a technical leader. Our delivery teams drive innovation to turn AI models into practical solutions - read our blog to learn more about how you’ll contribute to this exciting journey! What we offer Build what actually matters Help shape an AI-native engineering company at a formative stage, tackling problems that genuinely matter for industry and society. This is work with real-world impact - and something you can be proud to stand behind. Learn alongside exceptional people Work with a high-caliber, collaborative team of engineers, scientists, and operators who care deeply about doing great work, and about helping each other get better. We come from diverse backgrounds, but we share a commitment to operating at the highest level and addressing some of the most complex challenges out there. If you’re ambitious, thoughtful, and driven by impact, you’ll feel at home. Influence over hierarchy We operate with a flat structure: good ideas win - wherever they come from. Questioning assumptions and challenging the status quo isn’t just welcomed, it’s expected. Sustainable pace, long-term ambition Building meaningful technology is a marathon, not a sprint. We believe in balancing focused, ambitious work with a life beyond it. Our hybrid model blends time together in our New York office with work-from-home days, giving you the flexibility to work sustainably while staying connected in person. And it doesn’t stop there … 🚀 Equity options - share meaningfully in the company you’re helping to build. 💰 5% contribution to 401(k) - build long-term security with a strong retirement plan. 🍽️ Free team lunch 1x/week - good food, great company, and space to connect. 🏥 Private health insurance – comprehensive cover for you, offering total peace of mind. 👶 Enhanced parental leave – 3 months full pay paternity and 6 months full pay maternity leave, to provide extra flexibility during the moments that matter most. ☀️ 20 days of Annual Leave (+ Public Holidays) - because taking time to rest matters. 📈 Personal development – dedicated support for learning, development, and leveling up over time. 💪 Gympass / Wellhub (subsidized) – for you and up to 3 family members, supporting both physical and mental wellbeing. 💳 Flexible Spending Account (FSA) – set aside pre-tax dollars for eligible healthcare expenses. 🔎 Watch this space, we’re continuing to build this as we grow… Salary range: $200,000 - $250,000 depending on experience Seniority will be assessed throughout our interview process We value diversity and are committed to equal employment opportunity regardless of sex, race, religion, ethnicity, nationality, disability, age, sexual orientation or gender identity. We strongly encourage individuals from groups traditionally underrepresented in tech to apply. To help make a change, we sponsor bright women from disadvantaged backgrounds through their university degrees in science and mathematics. We collect diversity and inclusion data solely for the purpose of monitoring the effectiveness of our equal opportunities policies and ensuring compliance with UK employment and equality legislation. This information is confidential, used only in aggregate form, and will not influence the outcome of your application.</t>
         </is>
       </c>
-      <c r="L95" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>ashby|faculty|064b8c9e-eddc-486f-a013-1560fc4b6254</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>064b8c9e-eddc-486f-a013-1560fc4b6254</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Senior Data Scientist</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>UK - London</t>
         </is>
       </c>
-      <c r="H96" t="n">
-        <v>1</v>
-      </c>
-      <c r="I96" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="inlineStr">
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/064b8c9e-eddc-486f-a013-1560fc4b6254</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -6179,58 +3891,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L96" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>ashby|faculty|07967907-b88f-4a1c-8a7b-adebb0f7d58b</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>07967907-b88f-4a1c-8a7b-adebb0f7d58b</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t xml:space="preserve">Senior Machine Learning Engineer </t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>UK - London</t>
         </is>
       </c>
-      <c r="H97" t="n">
-        <v>1</v>
-      </c>
-      <c r="I97" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" t="inlineStr">
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/07967907-b88f-4a1c-8a7b-adebb0f7d58b</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -6275,58 +3987,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L97" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>ashby|faculty|168cb0e1-daea-42d5-ac09-e12a61cf72ca</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>168cb0e1-daea-42d5-ac09-e12a61cf72ca</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t xml:space="preserve">Machine Learning Engineer </t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>UK - Remote</t>
         </is>
       </c>
-      <c r="H98" t="n">
-        <v>1</v>
-      </c>
-      <c r="I98" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" t="inlineStr">
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/168cb0e1-daea-42d5-ac09-e12a61cf72ca</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -6373,58 +4085,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L98" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="L55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>ashby|faculty|27dee06f-ffaa-462e-9b91-888272ba5989</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>27dee06f-ffaa-462e-9b91-888272ba5989</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Machine learning Engineer</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>UK - London</t>
         </is>
       </c>
-      <c r="H99" t="n">
-        <v>1</v>
-      </c>
-      <c r="I99" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" t="inlineStr">
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/27dee06f-ffaa-462e-9b91-888272ba5989</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -6470,58 +4182,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L99" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="L56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>ashby|faculty|27e13461-0792-4c98-94e5-a989cf4b8701</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>27e13461-0792-4c98-94e5-a989cf4b8701</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t xml:space="preserve">Senior Machine Learning Engineer </t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>UK - Remote</t>
         </is>
       </c>
-      <c r="H100" t="n">
-        <v>1</v>
-      </c>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" t="inlineStr">
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/27e13461-0792-4c98-94e5-a989cf4b8701</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -6567,58 +4279,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L100" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>ashby|faculty|3c808ef2-1d15-4352-bf87-93fef11027d1</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>3c808ef2-1d15-4352-bf87-93fef11027d1</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Lead Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>UK - London</t>
         </is>
       </c>
-      <c r="H101" t="n">
-        <v>1</v>
-      </c>
-      <c r="I101" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" t="inlineStr">
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/3c808ef2-1d15-4352-bf87-93fef11027d1</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -6667,58 +4379,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L101" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>ashby|faculty|536bd41c-0588-48df-aba3-1ed5e7afcb55</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>536bd41c-0588-48df-aba3-1ed5e7afcb55</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t xml:space="preserve">Senior Data Scientist </t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>UK - London</t>
         </is>
       </c>
-      <c r="H102" t="n">
-        <v>1</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" t="inlineStr">
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/536bd41c-0588-48df-aba3-1ed5e7afcb55</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -6764,58 +4476,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L102" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>ashby|faculty|553927aa-2c38-4257-99af-4c0255327006</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>553927aa-2c38-4257-99af-4c0255327006</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t xml:space="preserve">Lead Machine Learning Engineer </t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>UK - Remote</t>
         </is>
       </c>
-      <c r="H103" t="n">
-        <v>1</v>
-      </c>
-      <c r="I103" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" t="inlineStr">
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/553927aa-2c38-4257-99af-4c0255327006</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -6863,58 +4575,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L103" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="L60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>ashby|faculty|6637dc01-5a7c-40cd-94a0-91d9c4006b4a</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>6637dc01-5a7c-40cd-94a0-91d9c4006b4a</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>UK - London</t>
         </is>
       </c>
-      <c r="H104" t="n">
-        <v>1</v>
-      </c>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" t="inlineStr">
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/6637dc01-5a7c-40cd-94a0-91d9c4006b4a</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -6958,58 +4670,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L104" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="L61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>ashby|faculty|70340093-7182-4d2c-b0d4-f383190856bf</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>70340093-7182-4d2c-b0d4-f383190856bf</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t xml:space="preserve">Lead Machine Learning Engineer </t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>UK - London</t>
         </is>
       </c>
-      <c r="H105" t="n">
-        <v>1</v>
-      </c>
-      <c r="I105" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" t="inlineStr">
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/70340093-7182-4d2c-b0d4-f383190856bf</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -7056,58 +4768,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L105" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>ashby|faculty|76c7b295-da94-4e83-813b-25b1766f92a0</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>76c7b295-da94-4e83-813b-25b1766f92a0</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t xml:space="preserve">Lead Data Scientist </t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>UK - London</t>
         </is>
       </c>
-      <c r="H106" t="n">
-        <v>1</v>
-      </c>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" t="inlineStr">
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/76c7b295-da94-4e83-813b-25b1766f92a0</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -7155,58 +4867,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L106" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="L63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>ashby|faculty|7a6e49b5-3f14-4d23-9abe-ec285ce7ee2e</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>7a6e49b5-3f14-4d23-9abe-ec285ce7ee2e</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>UK - London</t>
         </is>
       </c>
-      <c r="H107" t="n">
-        <v>1</v>
-      </c>
-      <c r="I107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" t="inlineStr">
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/7a6e49b5-3f14-4d23-9abe-ec285ce7ee2e</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -7253,58 +4965,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L107" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="L64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>ashby|faculty|8c211ad2-133d-413f-b65f-31d02f672113</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>8c211ad2-133d-413f-b65f-31d02f672113</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>UK - London</t>
         </is>
       </c>
-      <c r="H108" t="n">
-        <v>1</v>
-      </c>
-      <c r="I108" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" t="inlineStr">
+      <c r="H65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/8c211ad2-133d-413f-b65f-31d02f672113</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -7349,58 +5061,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L108" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="L65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>ashby|faculty|92c892cd-1f6c-443d-9cd8-e4902f9b7fb6</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>92c892cd-1f6c-443d-9cd8-e4902f9b7fb6</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t xml:space="preserve">Lead Data Scientist </t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>UK - Remote</t>
         </is>
       </c>
-      <c r="H109" t="n">
-        <v>1</v>
-      </c>
-      <c r="I109" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" t="inlineStr">
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/92c892cd-1f6c-443d-9cd8-e4902f9b7fb6</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -7448,58 +5160,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L109" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="L66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>ashby|faculty|a8ad6158-52b2-46b6-889b-7112d0f3b952</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>a8ad6158-52b2-46b6-889b-7112d0f3b952</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Principal Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>UK - London</t>
         </is>
       </c>
-      <c r="H110" t="n">
-        <v>1</v>
-      </c>
-      <c r="I110" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" t="inlineStr">
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/a8ad6158-52b2-46b6-889b-7112d0f3b952</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -7544,58 +5256,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L110" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="L67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>ashby|faculty|aafc6889-c160-4172-b5ae-87a3557830d8</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>aafc6889-c160-4172-b5ae-87a3557830d8</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t xml:space="preserve">Senior Data Scientist </t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>UK - Remote</t>
         </is>
       </c>
-      <c r="H111" t="n">
-        <v>1</v>
-      </c>
-      <c r="I111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" t="inlineStr">
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/aafc6889-c160-4172-b5ae-87a3557830d8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -7641,58 +5353,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L111" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="L68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>ashby|faculty|b72b42b6-4fdf-4c6e-bee0-96e3cba3a84f</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>b72b42b6-4fdf-4c6e-bee0-96e3cba3a84f</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t xml:space="preserve">Senior Machine Learning Engineer </t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>UK - London</t>
         </is>
       </c>
-      <c r="H112" t="n">
-        <v>1</v>
-      </c>
-      <c r="I112" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" t="inlineStr">
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/b72b42b6-4fdf-4c6e-bee0-96e3cba3a84f</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -7738,58 +5450,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L112" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="L69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>ashby|faculty|bdbba013-af29-4028-addc-6f3d87ad657a</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>bdbba013-af29-4028-addc-6f3d87ad657a</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Principal Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>UK - London</t>
         </is>
       </c>
-      <c r="H113" t="n">
-        <v>1</v>
-      </c>
-      <c r="I113" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" t="inlineStr">
+      <c r="H70" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/bdbba013-af29-4028-addc-6f3d87ad657a</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -7833,58 +5545,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L113" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="L70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>ashby|faculty|c049f0ee-e6fc-43a3-9d45-6dace70ad06a</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>c049f0ee-e6fc-43a3-9d45-6dace70ad06a</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t xml:space="preserve">Lead Data Scientist </t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>UK - London</t>
         </is>
       </c>
-      <c r="H114" t="n">
-        <v>1</v>
-      </c>
-      <c r="I114" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" t="inlineStr">
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/c049f0ee-e6fc-43a3-9d45-6dace70ad06a</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -7932,58 +5644,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L114" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="L71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>ashby|faculty|c601a9d6-deea-4a17-b11c-32a99b9275a4</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>c601a9d6-deea-4a17-b11c-32a99b9275a4</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t xml:space="preserve">Machine Learning Engineer </t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>UK - London</t>
         </is>
       </c>
-      <c r="H115" t="n">
-        <v>1</v>
-      </c>
-      <c r="I115" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" t="inlineStr">
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/c601a9d6-deea-4a17-b11c-32a99b9275a4</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -8030,58 +5742,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L115" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="L72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>ashby|faculty|c61dad1a-ac89-4802-9bcc-4e31726a04e0</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>c61dad1a-ac89-4802-9bcc-4e31726a04e0</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>UK - London</t>
         </is>
       </c>
-      <c r="H116" t="n">
-        <v>1</v>
-      </c>
-      <c r="I116" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" t="inlineStr">
+      <c r="H73" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/c61dad1a-ac89-4802-9bcc-4e31726a04e0</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -8126,58 +5838,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L116" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="L73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>ashby|faculty|ddaee792-5e2b-4f87-aa60-761798762de5</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>ddaee792-5e2b-4f87-aa60-761798762de5</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t xml:space="preserve">Machine Learning Engineer </t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>UK - London</t>
         </is>
       </c>
-      <c r="H117" t="n">
-        <v>1</v>
-      </c>
-      <c r="I117" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" t="inlineStr">
+      <c r="H74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/ddaee792-5e2b-4f87-aa60-761798762de5</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -8222,58 +5934,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L117" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="L74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>ashby|faculty|efa8d13e-5166-4ae2-bf10-b1392afd3528</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>efa8d13e-5166-4ae2-bf10-b1392afd3528</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t xml:space="preserve">Principal Data Scientist </t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>UK - London</t>
         </is>
       </c>
-      <c r="H118" t="n">
-        <v>1</v>
-      </c>
-      <c r="I118" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" t="inlineStr">
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/efa8d13e-5166-4ae2-bf10-b1392afd3528</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -8319,58 +6031,58 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L118" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="L75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>ashby|faculty|fd216949-66f6-4258-9e52-f2067503b75f</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>faculty</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>fd216949-66f6-4258-9e52-f2067503b75f</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t xml:space="preserve">Data Scientist </t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>UK - Remote</t>
         </is>
       </c>
-      <c r="H119" t="n">
-        <v>1</v>
-      </c>
-      <c r="I119" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" t="inlineStr">
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/faculty/fd216949-66f6-4258-9e52-f2067503b75f</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>WHY FACULTY?
 We established Faculty in 2014 because we thought that AI would be the most important technology of our time. Since then, we’ve worked with over 350 global customers to transform their performance through human-centric AI. You can read about our real-world impact here https://faculty.ai/impact.
@@ -8415,114 +6127,114 @@
 If you don’t feel you meet all the requirements, but are excited by the role and know you bring some key strengths, please don't hesitate in applying as you might be right for this role, or other roles. We are open to conversations about part-time hours.</t>
         </is>
       </c>
-      <c r="L119" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>greenhouse|amplemarket|4108094101</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Amplemarket</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>amplemarket</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>4108094101</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Spontaneous Application - Data Engineer</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Remote, EMEA/LATAM</t>
         </is>
       </c>
-      <c r="H120" t="n">
-        <v>1</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" t="inlineStr">
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/amplemarket/jobs/4108094101</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>What is Amplemarket all about? Amplemarket's premise is that a lot of the playbooks used by B2B sales teams that worked 5 years ago don't cut it anymore. In today's environment, sales teams need to have a tremendous amount of information about their prospects to decide when is the best moment and channel to reach out in the most relevant way. You can't do this with 5 different data/sales enablement point solutions that don't share the same data schema and barely communicate with each other. Amplemarket is the all-in-one compound solution that enables this. Our AI-powered sales platform helps B2B companies generate more opportunities thanks to our advanced lead generation engine, hyper-personalized sequencing, omnichannel outreach, and AI-powered smart actions. We are backed by Y Combinator, and we are powering the sales teams at some of the fastest-growing companies in the world like Deel, Moveworks, H1 and Vanta. Important Notice: Beware of Recruitment Scams It has come to our attention that there are fraudulent activities targeting job seekers, where individuals are impersonating Amplemarket by using fake profiles, domains, and emails. Please be informed that Amplemarket always uses our main domain (amplemarket.com) for all hiring and recruitment purposes. Any communication or offer not originating from an amplemarket.com email address should be regarded as suspicious. We will never request personal financial information (such as bank account details) during the initial application or interview process. Our hiring process does not involve transferring money or making payments of any kind to secure a position. Amplemarket is not responsible for any loss or damage incurred as a result of job scams or fraudulent activity by third parties misusing our company name. If you have any doubts about the legitimacy of a job opportunity with Amplemarket, please contact our HR department directly. We advise you to verify the authenticity of any job-related communications claiming to be from Amplemarket. If you have any concerns or doubts, please contact us directly through our official channels. Your security is our priority. Thank you for your vigilance and understanding. Are you up for a challenge? Amplemarket welcomes spontaneous applications from talented people who are eager to join our team. We are always on the lookout for exceptional Data Engineers who want to revolutionize the future of sales, while thriving in an incredible Engineering environment. While we may not be prioritizing this opening at the moment - and, therefore, might take a bit longer to get back to you - we review spontaneous applications regularly and if your profile stands out, we’ll definitely want to get to know you 🙂 About the Engineering Team The three co-founders have an engineering background (João, Luís and Mica studied Physics &amp; Computer Science in university) and deeply value the work that engineers are responsible for. Our main goal is to build a sales platform that helps companies grow. Our product requires us to solve a myriad of difficult engineering problems very diverse in nature: from working on NLP models that can extract information from a thread of emails to scaling an Elasticsearch cluster holding terabytes of data. We are deeply aware of the importance of our tool to our customers and look for people that share that vision. In this role, you will be responsible for designing, building, and maintaining the infrastructure and processes necessary for the collection, storage, and analysis of large datasets. You will work closely with our development, product, and data teams to ensure that our data is accurate, reliable, and accessible to support business decision-making, machine learning models, and drive product innovation. You will: Design and implement data pipelines for the collection, storage, and transformation of data from a variety of sources Develop and maintain data models and schema to support data analysis and reporting Write and maintain ETL jobs to extract, transform, and load data into our data warehouse Collaborate with ML engineers, data analysts, and other stakeholders to understand data requirements and develop solutions to support data-driven decision-making Monitor and optimize data pipelines and processes to ensure data quality and performance About you: Bachelor's or Master's degree in Computer Science, Data Science, or a related field 3+ years of experience as a Data Engineer or similar role Strong programming skills in Python, Java, or a similar language Experience with SQL and data modeling concepts Experience with cloud-based data warehousing solutions such as Redshift, BigQuery, or similar Experience with ETL tools such as Spark, Flink, Databricks, Snowflake, etc. Experience with messaging systems such as RabbitMQ, Kafka, etc. Knowledge of the underlying cloud infrastructure on how the various data pipeline component fit together Excellent problem-solving and communication skills Based somewhere between the GMT-3 and GMT+2 timezones Some more about Amplemarket: We are a post-Series A start-up Backed by YCombinator Strong technical founding team from MIT and IST (also founders of https://fermatslibrary.com/ ) Fast growing startup with product market fit Great team spirit We offer: Nice work environment Competitive Salary Health Insurance Stock Options Annual Company Trip in a secret location and more Amplemarket is committed to creating an inclusive employee experience for all. Regardless of race, gender, religion, sexual orientation, age, disability, or if you’re parenting the next generation of innovators, we firmly believe that what truly matters is how your skills, knowledge and personality fit our company. So bring your best professional version of yourself, and apply - we'd like to hear from you!</t>
         </is>
       </c>
-      <c r="L120" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="L77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>ashby|perplexity|0190699f-010b-44f2-8399-278899fef018</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Perplexity</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>perplexity</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>0190699f-010b-44f2-8399-278899fef018</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Member of Technical Staff (Machine Learning Engineer, Search)</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Belgrade</t>
         </is>
       </c>
-      <c r="H121" t="n">
-        <v>1</v>
-      </c>
-      <c r="I121" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" t="inlineStr">
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/perplexity/0190699f-010b-44f2-8399-278899fef018</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>Perplexity is seeking an experienced Machine Learning Engineer to help build the next generation of advanced search technologies, with a focus on retrieval and ranking.
 Responsibilities
@@ -8539,58 +6251,58 @@
  - Minimum of 5 years of working on search or recsys-related projects</t>
         </is>
       </c>
-      <c r="L121" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>ashby|perplexity|4615ca06-bea7-47e3-9e57-f5cee52b75e6</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Perplexity</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>perplexity</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>4615ca06-bea7-47e3-9e57-f5cee52b75e6</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Member of Technical Staff (Data Scientist, Evals)</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="H122" t="n">
-        <v>1</v>
-      </c>
-      <c r="I122" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" t="inlineStr">
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/perplexity/4615ca06-bea7-47e3-9e57-f5cee52b75e6</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>Perplexity serves tens of millions of users daily with reliable, high-quality answers grounded in an LLM-first search engine and our specialized data sources. We aim to use the latest models as they are released, but the intelligence frontier is a jagged one, and popular benchmarks do not effectively cover our use cases. In this role, you will build specialized evals to improve answer quality across Perplexity, covering search-based LLM answers and other scenarios popular with our users.
 RESPONSIBILITIES
@@ -8612,58 +6324,58 @@
  - Experience defining evaluation metrics (e.g., factual consistency, hallucination rate, retrieval precision) and building ground truth datasets</t>
         </is>
       </c>
-      <c r="L122" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="L79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>ashby|perplexity|768efd34-3854-4c9b-9686-2a128ab35405</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Perplexity</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>perplexity</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>768efd34-3854-4c9b-9686-2a128ab35405</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Member of Technical Staff (Data Scientist/Engineer, Online Metrics)</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>New York City</t>
         </is>
       </c>
-      <c r="H123" t="n">
-        <v>1</v>
-      </c>
-      <c r="I123" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" t="inlineStr">
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/perplexity/768efd34-3854-4c9b-9686-2a128ab35405</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>Perplexity serves tens of millions of users daily with reliable, high-quality answers grounded in an LLM-first search engine and specialized data sources. The Answer Quality team ensures that our prompts, tools, search, and specialized datasets, combined with both frontier and in-house models, create the best possible experience for our users. As a Data Scientist/Engineer on this team, you will derive online signals from user interactions to bridge the gap between changes in answer quality and observed user behavior.
 RESPONSIBILITIES
@@ -8687,58 +6399,58 @@
  - Prior work supporting customer-facing products at scale</t>
         </is>
       </c>
-      <c r="L123" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="L80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>ashby|clay labs|31d3597f-400e-4c12-9692-a5fb6f5e0d03</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Clay Labs</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>claylabs</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>31d3597f-400e-4c12-9692-a5fb6f5e0d03</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="H124" t="n">
-        <v>1</v>
-      </c>
-      <c r="I124" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" t="inlineStr">
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/claylabs/31d3597f-400e-4c12-9692-a5fb6f5e0d03</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>ABOUT CLAY
 Our mission is to help organizations turn any growth idea into reality.
@@ -8782,170 +6494,170 @@
  - Prior experience in a product-led or B2B SaaS environment</t>
         </is>
       </c>
-      <c r="L124" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="L81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>greenhouse|hightouch|5718912004</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Hightouch</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>hightouch</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>5718912004</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Forward Deployed Marketing Data Scientist</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Remote (North America)</t>
         </is>
       </c>
-      <c r="H125" t="n">
-        <v>1</v>
-      </c>
-      <c r="I125" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" t="inlineStr">
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/hightouch/jobs/5718912004</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>About Hightouch Hightouch is an Agentic Marketing Platform powered by the industry-leading Composable CDP. With complete brand context, customer data, and performance history in one place, every marketer finally has the power to build and ship end-to-end campaigns themselves. Teams move faster, stay on brand, and get AI marketing that actually works. Founded in 2019 and headquartered in San Francisco, Hightouch enables marketing teams to analyze performance, brainstorm ideas, and generate creative at a speed and quality that wasn't previously possible. Named a Leader in the 2026 Gartner® Magic Quadrant™ for Customer Data Platforms, Hightouch is trusted by leading enterprises like Domino's, Spotify, Aritzia, Cars.com, Ramp, and PetSmart. At Hightouch, our mission is to help our customers leverage data and AI to grow their businesses. The team is ambitious, impact-driven, efficient — and we believe humility, kindness, and compassion are essential to our success. If you're energized by velocity, obsessed with raising the bar, and want to build alongside people who care deeply about each other and our customers, we'd love to meet you. About the Role We’re looking for a Forward Deployed Marketing Data Scientist to partner closely with our AI Decisioning customers and internal engineering teams to ensure that AI-driven marketing campaigns deliver measurable, compounding impact. This role is uniquely cross-functional: you’ll spend time diagnosing model behavior, tuning ML levers, analyzing incrementality, exploring customer data, and explaining insights to marketers and executives. Marketing teams come to Hightouch to transform how they operate. Instead of planning campaigns weeks ahead on a calendar, AI Decisioning continuously learns customer preferences and executes 1:1 messaging that adapts in real time. Your mission is to make sure that these AI agents perform at their best—and to help customers understand why they are performing the way they are. You’ll work alongside ML engineers, product managers, Solutions Consultants, and some of the world’s most recognizable brands to improve campaign performance, debug experiments, and identify opportunities for additional lift. Roughly 30% of your time will be customer-facing and 70% deep analytical and modeling work. No two days are the same, but you can expect to: Own diagnostics, insights, and tuning for AI Decisioning campaigns Explain why AI Decisioning is driving lift using counterfactuals, incrementality breakdowns, and cohort analysis. Debug performance issues, iterate on reward functions, and ensure the agent’s recommendations align with customer goals. Investigate experiment setups (send volumes, reachability, channel constraints) and surface actionable recommendations. Work deeply with data in notebooks and customer warehouses Pull down historical data to run exploratory analyses using Polars / Pandas in Jupyter notebooks Modify and improve customer feature matrices to unlock deep personalization. Conduct deeper warehouse-level SQL analyses when insights aren’t available in the UI. Build lightweight tooling that enables scale Create templates, notebooks, scripts, and repeatable workflows that improve how we analyze performance across customers. Identify systemic gaps and influence the direction of ML reporting and introspection. Communicate ML concepts clearly to non-technical stakeholders Present model insights and recommendations to marketers, analysts, and executives. Explain how the decision engine handles cold start, message transfer learning, exploration vs. exploitation, and more. Partner closely with Solutions Consultants to identify and drive new opportunities for uplift. What We’re Looking For Strong ability to perform deep exploratory data analysis in Python (Polars / Pandas, Jupyter notebooks). Ability to write and interpret SQL for customer warehouse analysis. High-level understanding of ML modeling concepts (features, hyperparameters, reward functions, training windows). Excellent communication skills; able to explain technical reasoning simply and confidently to marketers. A customer-first attitude with high ownership and urgency when resolving issues. Bonus Points Experience setting up and analyzing marketing experiments such as A/B, multivariate tests. Prior experience in an applied ML, data science, analytics engineering, or forward-deployed role. Experience building lightweight internal tools or scripting solutions. We are looking for talented, intellectually curious, and motivated individuals who are interested in tackling the problems above. We focus on impact and potential for growth more than years of experience. The salary range for this position is $140,000 - $220,000 USD per year, which is location independent in accordance with our remote-first policy. Interview Process We have limited inbound applications to one application per candidate. You will be auto-rejected if you apply to multiple roles. Please only apply to the position you are most qualified for. Our interview process evaluates the most important dimensions of the role: analytical depth, customer communication, first-principles problem solving, and alignment with Hightouch’s values. Intro Call [15–30m] Introductory call with either a member of our recruiting team or the hiring manager to get to know each other and see if the role could be a good mutual fit. Take Home Data Analysis Exercise + Review Session [45m] You’ll complete a short take-home assignment focused on exploratory data analysis of an example dataset. In the live review, you’ll walk through your approach, explain your reasoning, and present your findings as if you were guiding a customer through your analysis. We’re looking for clarity of communication, rigor of thinking, and the ability to turn data into actionable insights. Experiment Design &amp; Analysis Session [90m] A hands-on session where we collaboratively design and evaluate an experiment end-to-end. This includes: Defining the experimental goal and how success should be measured Identifying the most relevant context and features to use in modeling Interpreting example results and diagnosing performance patterns Recommending next steps and communicating tradeoffs Hiring Manager Interview [30m] Chat with hiring manager about past experiences and future operating preferences to assess fit on company values and operating principles. E-Verify Statement Hightouch participates in E-Verify. After you join the team, we'll verify your eligibility to work in the U.S. by submitting information from your Form I-9 to the Social Security Administration and, if needed, the Department of Homeland Security. This process happens post-hire only — we never use E-Verify to pre-screen applicants. E-Verify Notice E-Verify Notice (Spanish) Right to Work Notice Right to Work Notice (Spanish)</t>
         </is>
       </c>
-      <c r="L125" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="L82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>greenhouse|hightouch|5775517004</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Hightouch</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>hightouch</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>5775517004</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Head of Machine Learning</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Remote (North America)</t>
         </is>
       </c>
-      <c r="H126" t="n">
-        <v>1</v>
-      </c>
-      <c r="I126" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" t="inlineStr">
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/hightouch/jobs/5775517004</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>About Hightouch Hightouch is an Agentic Marketing Platform powered by the industry-leading Composable CDP. With complete brand context, customer data, and performance history in one place, every marketer finally has the power to build and ship end-to-end campaigns themselves. Teams move faster, stay on brand, and get AI marketing that actually works. Founded in 2019 and headquartered in San Francisco, Hightouch enables marketing teams to analyze performance, brainstorm ideas, and generate creative at a speed and quality that wasn't previously possible. Named a Leader in the 2026 Gartner® Magic Quadrant™ for Customer Data Platforms, Hightouch is trusted by leading enterprises like Domino's, Spotify, Aritzia, Cars.com, Ramp, and PetSmart. At Hightouch, our mission is to help our customers leverage data and AI to grow their businesses. The team is ambitious, impact-driven, efficient — and we believe humility, kindness, and compassion are essential to our success. If you're energized by velocity, obsessed with raising the bar, and want to build alongside people who care deeply about each other and our customers, we'd love to meet you. About the Role We are looking for an engineering leader to lead machine learning efforts across Hightouch. While hundreds of companies use Hightouch today to sync data into their SaaS systems to automate and improve operations, there’s a lot of surface area we haven’t touched in helping companies figuring out which customers to message, what content to put in messages, and when to send messages. A lot of this work today is done manually through intuition and guesswork, and we believe that adding machine learning could have a step function impact for our customers. And given our access to data warehouses and databases, Hightouch is perfectly placed to make use of a company’s customer data in building a powerful intelligence layer. At Hightouch, our engineering leaders serve as both active technical voices and strong people managers. The key outcomes we are looking for from this role include: Product Development: Lead the team in roadmapping and executing successful development of significant features and products as required to drive the business forward. Uphold a high technical bar, while making pragmatic tradeoffs Pace: Through a combination of leadership and technical expertise, improve the pace of execution of the team Recruiting: Be responsible for growing the team, including identifying needs, deciding how to evaluate candidates, and ensuring we hire high impact team members Reliability: Against the uphill battle of high growth/scale, up-level the team on reliability, resulting in fewer incidents, catching our own issues before our customers do, and a strong incident management hygiene People: Foster growth of team members and ensure strong engagement and motivation Some of the problems we’ll be working on include: Personalization and Product Recommendation : There are often many options for what content a company could message a user with, including which products to show from catalogues. Given this large state space, how can Hightouch help personalize messages with the most relevant content for each user? Probabilistic Identity Resolution: Many of our customers have multiple datasets and sources of information on their users. How do we stitch these datasets together and decide which profiles are from the same user or household? Content Generation : Particularly with recent advances in LLMs, how can we help marketers generate text, images, and creatives that are compelling to their customers? ML Infrastructure: Building the infrastructure to support model training and inference at scale for some of the largest companies in the world. What We Offer We are looking for talented, intellectually curious, and motivated individuals who are interested in tackling the problems above. This is a senior role, but we focus on impact and potential for growth more than years of experience. The salary range for this position is $230,000 - $400,000 USD per year, which is location independent in accordance with our remote-first policy. We also offer meaningful equity compensation in the form of ISO options, and offer early exercise and a 10 year post-termination exercise window. We have limited inbound applications to one application per candidate. You will be auto-rejected if you apply to multiple roles. Please only apply to the position you are most qualified for. E-Verify Statement Hightouch participates in E-Verify. After you join the team, we'll verify your eligibility to work in the U.S. by submitting information from your Form I-9 to the Social Security Administration and, if needed, the Department of Homeland Security. This process happens post-hire only — we never use E-Verify to pre-screen applicants. E-Verify Notice E-Verify Notice (Spanish) Right to Work Notice Right to Work Notice (Spanish)</t>
         </is>
       </c>
-      <c r="L126" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="L83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>ashby|supabase|e7e19db2-8735-428b-bf22-c7109a3e336a</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Supabase</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>supabase</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>e7e19db2-8735-428b-bf22-c7109a3e336a</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Staff Data Analyst, GTM</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="H127" t="n">
-        <v>1</v>
-      </c>
-      <c r="I127" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" t="inlineStr">
+      <c r="H84" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/supabase/e7e19db2-8735-428b-bf22-c7109a3e336a</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>ABOUT SUPABASE
 Supabase is the Postgres development platform, built by developers for developers. We provide a complete backend solution including Database, Auth, Storage, Edge Functions, Realtime, and Vector Search. All services are deeply integrated and designed for growth.
@@ -9014,58 +6726,58 @@
 All communication is remote and we aim to move fast.</t>
         </is>
       </c>
-      <c r="L127" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="L84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>ashby|supabase|44f6de1c-0fdc-4d46-aa3e-7d57b8be38b2</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>ashby</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Supabase</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>supabase</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>44f6de1c-0fdc-4d46-aa3e-7d57b8be38b2</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Senior Data Engineer</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="H128" t="n">
-        <v>1</v>
-      </c>
-      <c r="I128" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" t="inlineStr">
+      <c r="H85" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/supabase/44f6de1c-0fdc-4d46-aa3e-7d57b8be38b2</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>ABOUT SUPABASE
 Supabase is the Postgres development platform, built by developers for developers. We provide a complete backend solution including Database, Auth, Storage, Edge Functions, Realtime, and Vector Search. All services are deeply integrated and designed for growth.
@@ -9126,7 +6838,7 @@
 All communication is remote and we aim to move fast.</t>
         </is>
       </c>
-      <c r="L128" t="n">
+      <c r="L85" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Excel/new_jobsnew.xlsx
+++ b/Excel/new_jobsnew.xlsx
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1676,7 +1676,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3050,7 +3050,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4868,7 +4868,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4966,7 +4966,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5062,7 +5062,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -5257,7 +5257,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -5451,7 +5451,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -6252,7 +6252,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
